--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$70</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -106,241 +106,238 @@
     <t>VENCIDO ACIMA DE 90 DIAS</t>
   </si>
   <si>
-    <t>FA-10150</t>
+    <t>ND-11056</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>PRISSILLA CRISLLEY JESSUS DE ALENCAR SIQUEIRA</t>
+    <t>LENILDO DE LIMA</t>
   </si>
   <si>
     <t>VENCIDO</t>
   </si>
   <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>VENCIDO ATÉ 30 DIAS</t>
+  </si>
+  <si>
+    <t>FA-11240</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
     <t>FATURA</t>
   </si>
   <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t>ND-11056</t>
-  </si>
-  <si>
-    <t>LENILDO DE LIMA</t>
-  </si>
-  <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
-    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>VENCIDO ATÉ 30 DIAS</t>
-  </si>
-  <si>
-    <t>FA-11240</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
+    <t>FA-11155</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11447</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11421</t>
+  </si>
+  <si>
+    <t>FA-11406</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11383</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11419</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11189</t>
+  </si>
+  <si>
+    <t>FA-11182</t>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>FA-11069</t>
+  </si>
+  <si>
+    <t>ALBERTO MANOEL DOS REIS</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>ND-11305</t>
+  </si>
+  <si>
+    <t>FA-11113</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11426</t>
+  </si>
+  <si>
+    <t>FA-11455</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11244</t>
+  </si>
+  <si>
+    <t>FA-11390</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>FA-11115</t>
+  </si>
+  <si>
+    <t>FA-11256</t>
+  </si>
+  <si>
+    <t>FA-11407</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>FA-11183</t>
+  </si>
+  <si>
+    <t>FA-11361</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11346</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>FA-11456</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
   </si>
   <si>
     <t>FA-11253</t>
   </si>
   <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-10569</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11495</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11155</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11423</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11447</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11512</t>
-  </si>
-  <si>
-    <t>ALBERTO MANOEL DOS REIS</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11421</t>
-  </si>
-  <si>
-    <t>FA-11406</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11383</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11419</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11189</t>
-  </si>
-  <si>
-    <t>ND-11376</t>
-  </si>
-  <si>
-    <t>FA-11182</t>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>FA-11069</t>
-  </si>
-  <si>
-    <t>ND-11305</t>
-  </si>
-  <si>
-    <t>FA-11113</t>
+    <t>HOJE</t>
   </si>
   <si>
     <t>FA-11387</t>
   </si>
   <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11426</t>
-  </si>
-  <si>
-    <t>FA-11244</t>
-  </si>
-  <si>
-    <t>FA-11455</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11390</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>FA-11115</t>
-  </si>
-  <si>
-    <t>FA-11187</t>
-  </si>
-  <si>
-    <t>FA-11256</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>FA-11407</t>
-  </si>
-  <si>
-    <t>FA-11514</t>
-  </si>
-  <si>
-    <t>FA-11183</t>
-  </si>
-  <si>
-    <t>FA-11361</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11346</t>
-  </si>
-  <si>
-    <t>FA-11456</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>A VENCER</t>
   </si>
   <si>
     <t>FA-11147</t>
   </si>
   <si>
+    <t>FA-11516</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11392</t>
+  </si>
+  <si>
     <t>FA-11458</t>
   </si>
   <si>
-    <t>FA-11392</t>
-  </si>
-  <si>
-    <t>FA-11516</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
+    <t>FA-11153</t>
   </si>
   <si>
     <t>FA-11462</t>
   </si>
   <si>
-    <t>FA-11153</t>
+    <t>FA-11517</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11350</t>
+  </si>
+  <si>
+    <t>FA-11485</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
   </si>
   <si>
     <t>FA-11391</t>
@@ -349,28 +346,16 @@
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11350</t>
-  </si>
-  <si>
     <t>FA-11393</t>
   </si>
   <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11517</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11485</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
+    <t>FA-11369</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
   </si>
   <si>
     <t>FA-11500</t>
@@ -379,27 +364,18 @@
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-11460</t>
+    <t>FA-11276</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11111</t>
   </si>
   <si>
     <t>FA-11497</t>
   </si>
   <si>
-    <t>FA-11369</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11276</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11111</t>
-  </si>
-  <si>
     <t>FA-11430</t>
   </si>
   <si>
@@ -415,31 +391,31 @@
     <t>ANDERSON QUEIROZ PINHEIRO</t>
   </si>
   <si>
+    <t>FA-11459</t>
+  </si>
+  <si>
+    <t>FA-11518</t>
+  </si>
+  <si>
     <t>FA-11463</t>
   </si>
   <si>
     <t>LUCAS NAJA MOURA RODRIGUES</t>
   </si>
   <si>
-    <t>FA-11518</t>
-  </si>
-  <si>
-    <t>FA-11459</t>
+    <t>FA-11325</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11265</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
     <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11325</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11265</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
     <t>FA-11545</t>
@@ -603,7 +579,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -617,8 +593,8 @@
     <col min="9" max="9" width="36.28671646118164" customWidth="1" style="1"/>
     <col min="10" max="10" width="25.261001586914062" customWidth="1" style="1"/>
     <col min="11" max="11" width="15.191652297973633" customWidth="1" style="1"/>
-    <col min="12" max="12" width="48.1286506652832" customWidth="1" style="1"/>
-    <col min="13" max="13" width="48.1286506652832" customWidth="1" style="1"/>
+    <col min="12" max="12" width="45.98413848876953" customWidth="1" style="1"/>
+    <col min="13" max="13" width="38.53249740600586" customWidth="1" style="1"/>
     <col min="14" max="14" width="31.09708023071289" customWidth="1" style="1"/>
     <col min="15" max="15" width="24.68001365661621" customWidth="1" style="1"/>
     <col min="16" max="16" width="14.40988826751709" customWidth="1" style="1"/>
@@ -708,22 +684,22 @@
         <v>22</v>
       </c>
       <c r="B6" s="7">
-        <v>45901</v>
+        <v>46030</v>
       </c>
       <c r="C6" s="7">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="D6" s="7">
-        <v>45901</v>
+        <v>46030</v>
       </c>
       <c r="E6" s="7">
-        <v>45861</v>
+        <v>46044</v>
       </c>
       <c r="F6" s="8">
-        <v>-235</v>
+        <v>-106</v>
       </c>
       <c r="G6" s="8">
-        <v>-235</v>
+        <v>-106</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -741,7 +717,7 @@
         <v>26</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>27</v>
@@ -759,7 +735,7 @@
         <v>29</v>
       </c>
       <c r="S6" s="9">
-        <v>600</v>
+        <v>195.23</v>
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
@@ -767,31 +743,31 @@
         <v>22</v>
       </c>
       <c r="B7" s="7">
-        <v>46030</v>
+        <v>46052</v>
       </c>
       <c r="C7" s="7">
-        <v>45992</v>
+        <v>45930</v>
       </c>
       <c r="D7" s="7">
-        <v>46030</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46044</v>
+        <v>46052</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F7" s="8">
-        <v>-106</v>
+        <v>-84</v>
       </c>
       <c r="G7" s="8">
-        <v>-106</v>
+        <v>-84</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>25</v>
@@ -812,13 +788,13 @@
         <v>25</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S7" s="9">
-        <v>195.23</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
@@ -826,31 +802,31 @@
         <v>22</v>
       </c>
       <c r="B8" s="7">
-        <v>46052</v>
+        <v>46118</v>
       </c>
       <c r="C8" s="7">
-        <v>45930</v>
+        <v>46118</v>
       </c>
       <c r="D8" s="7">
-        <v>46052</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
+        <v>46118</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46086</v>
       </c>
       <c r="F8" s="8">
-        <v>-84</v>
+        <v>-18</v>
       </c>
       <c r="G8" s="8">
-        <v>-84</v>
+        <v>-18</v>
       </c>
       <c r="H8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>25</v>
@@ -859,7 +835,7 @@
         <v>34</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>27</v>
@@ -871,13 +847,13 @@
         <v>25</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S8" s="9">
-        <v>185.5</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
@@ -885,28 +861,28 @@
         <v>22</v>
       </c>
       <c r="B9" s="7">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="C9" s="7">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="D9" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E9" s="7">
-        <v>46086</v>
+        <v>46104</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F9" s="8">
-        <v>-18</v>
+        <v>-32</v>
       </c>
       <c r="G9" s="8">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>36</v>
@@ -918,7 +894,7 @@
         <v>37</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>27</v>
@@ -930,13 +906,13 @@
         <v>25</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S9" s="9">
-        <v>620</v>
+        <v>165.25</v>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
@@ -944,28 +920,28 @@
         <v>22</v>
       </c>
       <c r="B10" s="7">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="C10" s="7">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="D10" s="7">
-        <v>46111</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>25</v>
+        <v>46125</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46122</v>
       </c>
       <c r="F10" s="8">
-        <v>-25</v>
+        <v>-11</v>
       </c>
       <c r="G10" s="8">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>38</v>
@@ -989,13 +965,13 @@
         <v>25</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S10" s="9">
-        <v>280</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1">
@@ -1006,55 +982,55 @@
         <v>46125</v>
       </c>
       <c r="C11" s="7">
-        <v>45971</v>
+        <v>46125</v>
       </c>
       <c r="D11" s="7">
-        <v>45971</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>25</v>
+        <v>46125</v>
+      </c>
+      <c r="E11" s="7">
+        <v>46119</v>
       </c>
       <c r="F11" s="8">
-        <v>-165</v>
+        <v>-11</v>
       </c>
       <c r="G11" s="8">
         <v>-11</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S11" s="9">
-        <v>130</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
@@ -1065,55 +1041,55 @@
         <v>46125</v>
       </c>
       <c r="C12" s="7">
+        <v>46125</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46125</v>
+      </c>
+      <c r="E12" s="7">
         <v>46118</v>
       </c>
-      <c r="D12" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="F12" s="8">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="G12" s="8">
         <v>-11</v>
       </c>
       <c r="H12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R12" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S12" s="9">
-        <v>150</v>
+        <v>680</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1124,55 +1100,55 @@
         <v>46125</v>
       </c>
       <c r="C13" s="7">
-        <v>46104</v>
+        <v>46125</v>
       </c>
       <c r="D13" s="7">
-        <v>46104</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>25</v>
+        <v>46125</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46113</v>
       </c>
       <c r="F13" s="8">
-        <v>-32</v>
+        <v>-11</v>
       </c>
       <c r="G13" s="8">
         <v>-11</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S13" s="9">
-        <v>165.25</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1189,7 +1165,7 @@
         <v>46125</v>
       </c>
       <c r="E14" s="7">
-        <v>46118</v>
+        <v>46087</v>
       </c>
       <c r="F14" s="8">
         <v>-11</v>
@@ -1198,40 +1174,40 @@
         <v>-11</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="R14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S14" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1239,40 +1215,40 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C15" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D15" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46119</v>
+        <v>46118</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F15" s="8">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="G15" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="M15" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1284,13 +1260,13 @@
         <v>25</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S15" s="9">
-        <v>650</v>
+        <v>130.16</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1298,38 +1274,38 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C16" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D16" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46057</v>
+        <v>46118</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F16" s="8">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="G16" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="M16" s="6" t="s">
         <v>25</v>
       </c>
@@ -1343,13 +1319,13 @@
         <v>25</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S16" s="9">
-        <v>650</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1357,37 +1333,37 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="C17" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D17" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E17" s="7">
-        <v>46122</v>
+        <v>46118</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F17" s="8">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="G17" s="8">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>25</v>
@@ -1402,13 +1378,13 @@
         <v>25</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S17" s="9">
-        <v>650</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1416,40 +1392,40 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46125</v>
+        <v>46128</v>
       </c>
       <c r="C18" s="7">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="D18" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46127</v>
+        <v>46111</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="G18" s="8">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>27</v>
@@ -1458,16 +1434,16 @@
         <v>27</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S18" s="9">
-        <v>680</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1475,37 +1451,37 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="C19" s="7">
-        <v>46125</v>
+        <v>46104</v>
       </c>
       <c r="D19" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46087</v>
+        <v>46104</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F19" s="8">
-        <v>-11</v>
+        <v>-32</v>
       </c>
       <c r="G19" s="8">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>25</v>
@@ -1520,13 +1496,13 @@
         <v>25</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S19" s="9">
-        <v>680</v>
+        <v>357.49</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1534,58 +1510,58 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="C20" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D20" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E20" s="7">
         <v>46118</v>
       </c>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="F20" s="8">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="G20" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="Q20" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>680</v>
+        <v>91.54</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1593,28 +1569,28 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="C21" s="7">
-        <v>46125</v>
+        <v>46082</v>
       </c>
       <c r="D21" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="E21" s="7">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G21" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>59</v>
@@ -1623,10 +1599,10 @@
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="N21" s="6" t="s">
         <v>27</v>
@@ -1641,10 +1617,10 @@
         <v>28</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S21" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1652,7 +1628,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="C22" s="7">
         <v>46118</v>
@@ -1667,25 +1643,25 @@
         <v>-18</v>
       </c>
       <c r="G22" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="M22" s="6" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1703,7 +1679,7 @@
         <v>29</v>
       </c>
       <c r="S22" s="9">
-        <v>130.16</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1711,38 +1687,38 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="C23" s="7">
-        <v>46118</v>
+        <v>45901</v>
       </c>
       <c r="D23" s="7">
-        <v>46118</v>
+        <v>45938</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="8">
-        <v>-18</v>
+        <v>-198</v>
       </c>
       <c r="G23" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="K23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="M23" s="6" t="s">
         <v>25</v>
       </c>
@@ -1762,7 +1738,7 @@
         <v>29</v>
       </c>
       <c r="S23" s="9">
-        <v>400</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1770,58 +1746,58 @@
         <v>22</v>
       </c>
       <c r="B24" s="7">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C24" s="7">
+        <v>46132</v>
+      </c>
+      <c r="D24" s="7">
+        <v>46132</v>
+      </c>
+      <c r="E24" s="7">
         <v>46118</v>
       </c>
-      <c r="D24" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>25</v>
-      </c>
       <c r="F24" s="8">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="8">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="H24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q24" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R24" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S24" s="9">
-        <v>260</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1829,28 +1805,28 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C25" s="7">
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="D25" s="7">
-        <v>46111</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E25" s="7">
+        <v>46119</v>
       </c>
       <c r="F25" s="8">
-        <v>-25</v>
+        <v>-4</v>
       </c>
       <c r="G25" s="8">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>65</v>
@@ -1859,10 +1835,10 @@
         <v>25</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1874,13 +1850,13 @@
         <v>25</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S25" s="9">
-        <v>119.57</v>
+        <v>620</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1888,58 +1864,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C26" s="7">
-        <v>46082</v>
+        <v>46132</v>
       </c>
       <c r="D26" s="7">
-        <v>46101</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E26" s="7">
+        <v>46086</v>
       </c>
       <c r="F26" s="8">
-        <v>-35</v>
+        <v>-4</v>
       </c>
       <c r="G26" s="8">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J26" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R26" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S26" s="9">
-        <v>242.72</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1947,58 +1923,58 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C27" s="7">
-        <v>46104</v>
+        <v>46132</v>
       </c>
       <c r="D27" s="7">
-        <v>46104</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E27" s="7">
+        <v>46112</v>
       </c>
       <c r="F27" s="8">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="G27" s="8">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I27" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J27" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R27" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>357.49</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2009,55 +1985,55 @@
         <v>46132</v>
       </c>
       <c r="C28" s="7">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="D28" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="G28" s="8">
         <v>-4</v>
       </c>
       <c r="H28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q28" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R28" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S28" s="9">
-        <v>91.54</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2068,13 +2044,13 @@
         <v>46132</v>
       </c>
       <c r="C29" s="7">
-        <v>46082</v>
+        <v>46132</v>
       </c>
       <c r="D29" s="7">
         <v>46132</v>
       </c>
       <c r="E29" s="7">
-        <v>46097</v>
+        <v>46057</v>
       </c>
       <c r="F29" s="8">
         <v>-4</v>
@@ -2083,40 +2059,40 @@
         <v>-4</v>
       </c>
       <c r="H29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="R29" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>146.55</v>
+        <v>650</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2127,55 +2103,55 @@
         <v>46132</v>
       </c>
       <c r="C30" s="7">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="D30" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46087</v>
       </c>
       <c r="F30" s="8">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="G30" s="8">
         <v>-4</v>
       </c>
       <c r="H30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q30" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>200</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2186,55 +2162,55 @@
         <v>46132</v>
       </c>
       <c r="C31" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="D31" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46113</v>
       </c>
       <c r="F31" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G31" s="8">
         <v>-4</v>
       </c>
       <c r="H31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P31" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q31" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R31" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S31" s="9">
-        <v>430</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2245,55 +2221,55 @@
         <v>46132</v>
       </c>
       <c r="C32" s="7">
-        <v>45901</v>
+        <v>46132</v>
       </c>
       <c r="D32" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E32" s="7">
+        <v>46118</v>
       </c>
       <c r="F32" s="8">
-        <v>-198</v>
+        <v>-4</v>
       </c>
       <c r="G32" s="8">
         <v>-4</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J32" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q32" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R32" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>546</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2301,28 +2277,28 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C33" s="7">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="D33" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E33" s="7">
-        <v>46118</v>
+        <v>46111</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F33" s="8">
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="G33" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>75</v>
@@ -2331,7 +2307,7 @@
         <v>25</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>25</v>
@@ -2346,13 +2322,13 @@
         <v>25</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S33" s="9">
-        <v>620</v>
+        <v>321.17</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2360,28 +2336,28 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C34" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D34" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="E34" s="7">
-        <v>46086</v>
+        <v>46100</v>
       </c>
       <c r="F34" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>76</v>
@@ -2390,10 +2366,10 @@
         <v>25</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2405,13 +2381,13 @@
         <v>25</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S34" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2419,40 +2395,40 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C35" s="7">
-        <v>46132</v>
+        <v>46082</v>
       </c>
       <c r="D35" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E35" s="7">
-        <v>46119</v>
+        <v>46125</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F35" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G35" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2464,13 +2440,13 @@
         <v>25</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="S35" s="9">
-        <v>620</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2478,7 +2454,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C36" s="7">
         <v>46132</v>
@@ -2486,32 +2462,32 @@
       <c r="D36" s="7">
         <v>46132</v>
       </c>
-      <c r="E36" s="7">
-        <v>46112</v>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F36" s="8">
         <v>-4</v>
       </c>
       <c r="G36" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K36" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="M36" s="6" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2523,13 +2499,13 @@
         <v>25</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>630</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2537,7 +2513,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C37" s="7">
         <v>46132</v>
@@ -2545,20 +2521,20 @@
       <c r="D37" s="7">
         <v>46132</v>
       </c>
-      <c r="E37" s="7">
-        <v>46119</v>
+      <c r="E37" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F37" s="8">
         <v>-4</v>
       </c>
       <c r="G37" s="8">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>80</v>
@@ -2567,10 +2543,10 @@
         <v>25</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2582,13 +2558,13 @@
         <v>25</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>650</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2596,28 +2572,28 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="C38" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D38" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46057</v>
+        <v>46125</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F38" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G38" s="8">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>81</v>
@@ -2626,7 +2602,7 @@
         <v>25</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>25</v>
@@ -2641,13 +2617,13 @@
         <v>25</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2655,28 +2631,28 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="C39" s="7">
         <v>46132</v>
       </c>
       <c r="D39" s="7">
-        <v>46104</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46063</v>
+        <v>46132</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F39" s="8">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="G39" s="8">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>82</v>
@@ -2685,10 +2661,10 @@
         <v>25</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2697,10 +2673,10 @@
         <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>29</v>
@@ -2714,37 +2690,37 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="C40" s="7">
-        <v>46132</v>
+        <v>46111</v>
       </c>
       <c r="D40" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46087</v>
+        <v>46111</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F40" s="8">
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="G40" s="8">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>25</v>
@@ -2753,19 +2729,19 @@
         <v>27</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>680</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2773,37 +2749,37 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="C41" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D41" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E41" s="7">
-        <v>46118</v>
+        <v>46125</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F41" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G41" s="8">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>25</v>
@@ -2812,19 +2788,19 @@
         <v>27</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>680</v>
+        <v>302.72</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2832,46 +2808,46 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C42" s="7">
-        <v>46132</v>
+        <v>46082</v>
       </c>
       <c r="D42" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E42" s="7">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="F42" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>25</v>
@@ -2880,10 +2856,10 @@
         <v>28</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S42" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2891,37 +2867,37 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C43" s="7">
-        <v>46132</v>
+        <v>46111</v>
       </c>
       <c r="D43" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46127</v>
+        <v>46083</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F43" s="8">
-        <v>-4</v>
+        <v>-53</v>
       </c>
       <c r="G43" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>25</v>
@@ -2930,19 +2906,19 @@
         <v>27</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>680</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2950,58 +2926,58 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="C44" s="7">
-        <v>46118</v>
+        <v>46139</v>
       </c>
       <c r="D44" s="7">
-        <v>46111</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E44" s="7">
+        <v>46127</v>
       </c>
       <c r="F44" s="8">
-        <v>-25</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="H44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I44" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q44" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R44" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>321.17</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3009,58 +2985,58 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="C45" s="7">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="D45" s="7">
-        <v>46133</v>
+        <v>46139</v>
       </c>
       <c r="E45" s="7">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="F45" s="8">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="G45" s="8">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I45" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q45" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="R45" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S45" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3068,58 +3044,58 @@
         <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="C46" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D46" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46119</v>
       </c>
       <c r="F46" s="8">
-        <v>-11</v>
+        <v>3</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I46" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q46" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R46" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>79.05</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3127,58 +3103,58 @@
         <v>22</v>
       </c>
       <c r="B47" s="7">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="C47" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="D47" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>25</v>
+        <v>46104</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46057</v>
       </c>
       <c r="F47" s="8">
-        <v>-4</v>
+        <v>-32</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I47" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P47" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q47" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R47" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>200</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3186,58 +3162,58 @@
         <v>22</v>
       </c>
       <c r="B48" s="7">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="C48" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="D48" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46119</v>
       </c>
       <c r="F48" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I48" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q48" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R48" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S48" s="9">
-        <v>200</v>
+        <v>620</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3245,58 +3221,58 @@
         <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="C49" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="D49" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46127</v>
       </c>
       <c r="F49" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I49" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O49" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P49" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q49" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R49" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3307,13 +3283,13 @@
         <v>46139</v>
       </c>
       <c r="C50" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D50" s="7">
         <v>46139</v>
       </c>
       <c r="E50" s="7">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="F50" s="8">
         <v>3</v>
@@ -3328,34 +3304,34 @@
         <v>25</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>146.55</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3366,55 +3342,55 @@
         <v>46139</v>
       </c>
       <c r="C51" s="7">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="D51" s="7">
-        <v>46083</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46100</v>
       </c>
       <c r="F51" s="8">
-        <v>-53</v>
+        <v>3</v>
       </c>
       <c r="G51" s="8">
         <v>3</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S51" s="9">
-        <v>320</v>
+        <v>630</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3446,34 +3422,34 @@
         <v>25</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S52" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3505,34 +3481,34 @@
         <v>25</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S53" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3549,7 +3525,7 @@
         <v>46139</v>
       </c>
       <c r="E54" s="7">
-        <v>46127</v>
+        <v>46112</v>
       </c>
       <c r="F54" s="8">
         <v>3</v>
@@ -3564,34 +3540,34 @@
         <v>25</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S54" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3608,7 +3584,7 @@
         <v>46139</v>
       </c>
       <c r="E55" s="7">
-        <v>46119</v>
+        <v>46101</v>
       </c>
       <c r="F55" s="8">
         <v>3</v>
@@ -3623,34 +3599,34 @@
         <v>25</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S55" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3664,52 +3640,52 @@
         <v>46139</v>
       </c>
       <c r="D56" s="7">
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="E56" s="7">
-        <v>46057</v>
+        <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>-32</v>
+        <v>3</v>
       </c>
       <c r="G56" s="8">
         <v>3</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3726,7 +3702,7 @@
         <v>46139</v>
       </c>
       <c r="E57" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F57" s="8">
         <v>3</v>
@@ -3741,34 +3717,34 @@
         <v>25</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3785,7 +3761,7 @@
         <v>46139</v>
       </c>
       <c r="E58" s="7">
-        <v>46100</v>
+        <v>46092</v>
       </c>
       <c r="F58" s="8">
         <v>3</v>
@@ -3800,34 +3776,34 @@
         <v>25</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S58" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3841,52 +3817,52 @@
         <v>46139</v>
       </c>
       <c r="D59" s="7">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="E59" s="7">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="F59" s="8">
-        <v>3</v>
+        <v>-32</v>
       </c>
       <c r="G59" s="8">
         <v>3</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S59" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3900,52 +3876,52 @@
         <v>46139</v>
       </c>
       <c r="D60" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E60" s="7">
-        <v>46100</v>
+        <v>46122</v>
       </c>
       <c r="F60" s="8">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G60" s="8">
         <v>3</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S60" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3962,7 +3938,7 @@
         <v>46139</v>
       </c>
       <c r="E61" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F61" s="8">
         <v>3</v>
@@ -3977,34 +3953,34 @@
         <v>25</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>630</v>
+        <v>670</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4021,7 +3997,7 @@
         <v>46139</v>
       </c>
       <c r="E62" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F62" s="8">
         <v>3</v>
@@ -4036,34 +4012,34 @@
         <v>25</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S62" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4080,7 +4056,7 @@
         <v>46139</v>
       </c>
       <c r="E63" s="7">
-        <v>46127</v>
+        <v>46100</v>
       </c>
       <c r="F63" s="8">
         <v>3</v>
@@ -4095,34 +4071,34 @@
         <v>25</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S63" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4154,34 +4130,34 @@
         <v>25</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S64" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4195,52 +4171,52 @@
         <v>46139</v>
       </c>
       <c r="D65" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E65" s="7">
-        <v>46122</v>
+        <v>46127</v>
       </c>
       <c r="F65" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G65" s="8">
         <v>3</v>
       </c>
       <c r="H65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q65" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="I65" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M65" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N65" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O65" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P65" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q65" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="R65" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S65" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4257,7 +4233,7 @@
         <v>46139</v>
       </c>
       <c r="E66" s="7">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="F66" s="8">
         <v>3</v>
@@ -4272,34 +4248,34 @@
         <v>25</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S66" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4316,7 +4292,7 @@
         <v>46139</v>
       </c>
       <c r="E67" s="7">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="F67" s="8">
         <v>3</v>
@@ -4331,34 +4307,34 @@
         <v>25</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S67" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4372,52 +4348,52 @@
         <v>46139</v>
       </c>
       <c r="D68" s="7">
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="E68" s="7">
-        <v>46057</v>
+        <v>46092</v>
       </c>
       <c r="F68" s="8">
-        <v>-32</v>
+        <v>3</v>
       </c>
       <c r="G68" s="8">
         <v>3</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S68" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4449,34 +4425,34 @@
         <v>25</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S69" s="9">
-        <v>670</v>
+        <v>700</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4493,7 +4469,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="7">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="F70" s="8">
         <v>3</v>
@@ -4508,34 +4484,34 @@
         <v>25</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="S70" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4543,58 +4519,58 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C71" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D71" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E71" s="7">
-        <v>46100</v>
+        <v>46132</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F71" s="8">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G71" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S71" s="9">
-        <v>680</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4602,58 +4578,58 @@
         <v>22</v>
       </c>
       <c r="B72" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C72" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D72" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E72" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F72" s="8">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G72" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S72" s="9">
-        <v>680</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4661,31 +4637,31 @@
         <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C73" s="7">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="D73" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E73" s="7">
-        <v>46127</v>
+        <v>46125</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F73" s="8">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="G73" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>25</v>
@@ -4697,22 +4673,22 @@
         <v>25</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S73" s="9">
-        <v>680</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4720,22 +4696,22 @@
         <v>22</v>
       </c>
       <c r="B74" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C74" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="D74" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="E74" s="7">
-        <v>46119</v>
+        <v>46100</v>
       </c>
       <c r="F74" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>25</v>
@@ -4744,31 +4720,31 @@
         <v>25</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="S74" s="9">
         <v>680</v>
@@ -4779,22 +4755,22 @@
         <v>22</v>
       </c>
       <c r="B75" s="7">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="C75" s="7">
-        <v>46139</v>
+        <v>45930</v>
       </c>
       <c r="D75" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E75" s="7">
-        <v>46119</v>
+        <v>46142</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F75" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G75" s="8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>25</v>
@@ -4803,565 +4779,93 @@
         <v>25</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S75" s="9">
-        <v>700</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="76" ht="23" customHeight="1">
-      <c r="A76" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B76" s="7">
-        <v>46139</v>
-      </c>
-      <c r="C76" s="7">
-        <v>46139</v>
-      </c>
-      <c r="D76" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E76" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F76" s="8">
-        <v>3</v>
-      </c>
-      <c r="G76" s="8">
-        <v>3</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="M76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N76" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q76" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R76" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S76" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="77" ht="23" customHeight="1">
-      <c r="A77" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B77" s="7">
-        <v>46139</v>
-      </c>
-      <c r="C77" s="7">
-        <v>46139</v>
-      </c>
-      <c r="D77" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E77" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F77" s="8">
-        <v>3</v>
-      </c>
-      <c r="G77" s="8">
-        <v>3</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L77" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N77" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="O77" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q77" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R77" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S77" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="78" ht="23" customHeight="1">
-      <c r="A78" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B78" s="7">
-        <v>46139</v>
-      </c>
-      <c r="C78" s="7">
-        <v>46139</v>
-      </c>
-      <c r="D78" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E78" s="7">
-        <v>46129</v>
-      </c>
-      <c r="F78" s="8">
-        <v>3</v>
-      </c>
-      <c r="G78" s="8">
-        <v>3</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J78" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="K78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q78" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R78" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="S78" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="79" ht="23" customHeight="1">
-      <c r="A79" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" s="7">
-        <v>46140</v>
-      </c>
-      <c r="C79" s="7">
-        <v>46132</v>
-      </c>
-      <c r="D79" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G79" s="8">
-        <v>4</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="M79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N79" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O79" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R79" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S79" s="9">
-        <v>110.69</v>
-      </c>
-    </row>
-    <row r="80" ht="23" customHeight="1">
-      <c r="A80" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" s="7">
-        <v>46140</v>
-      </c>
-      <c r="C80" s="7">
-        <v>46132</v>
-      </c>
-      <c r="D80" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G80" s="8">
-        <v>4</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R80" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S80" s="9">
-        <v>124.25</v>
-      </c>
-    </row>
-    <row r="81" ht="23" customHeight="1">
-      <c r="A81" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="7">
-        <v>46140</v>
-      </c>
-      <c r="C81" s="7">
-        <v>46125</v>
-      </c>
-      <c r="D81" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" s="8">
-        <v>-11</v>
-      </c>
-      <c r="G81" s="8">
-        <v>4</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L81" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N81" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O81" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S81" s="9">
-        <v>408.24</v>
-      </c>
-    </row>
-    <row r="82" ht="23" customHeight="1">
-      <c r="A82" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B82" s="7">
-        <v>46140</v>
-      </c>
-      <c r="C82" s="7">
-        <v>46140</v>
-      </c>
-      <c r="D82" s="7">
-        <v>46140</v>
-      </c>
-      <c r="E82" s="7">
-        <v>46100</v>
-      </c>
-      <c r="F82" s="8">
-        <v>4</v>
-      </c>
-      <c r="G82" s="8">
-        <v>4</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q82" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S82" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="83" ht="23" customHeight="1">
-      <c r="A83" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C83" s="7">
-        <v>45930</v>
-      </c>
-      <c r="D83" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F83" s="8">
-        <v>6</v>
-      </c>
-      <c r="G83" s="8">
-        <v>6</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N83" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="O83" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="S83" s="9">
-        <v>185.5</v>
-      </c>
-    </row>
-    <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="P84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R84" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="S84" s="13">
-        <f>SUM(S6:S83)</f>
+      <c r="A76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="R76" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S76" s="13">
+        <f>SUM(S6:S75)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$68</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -103,340 +103,334 @@
     <t>1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
   </si>
   <si>
+    <t>VENCIDO ATÉ 30 DIAS</t>
+  </si>
+  <si>
+    <t>FA-11240</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>VENCIDO</t>
+  </si>
+  <si>
+    <t>FATURA</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+  </si>
+  <si>
+    <t>FA-11155</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11447</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11421</t>
+  </si>
+  <si>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11406</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11383</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11419</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11189</t>
+  </si>
+  <si>
+    <t>FA-11182</t>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>FA-11069</t>
+  </si>
+  <si>
+    <t>ALBERTO MANOEL DOS REIS</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>ND-11305</t>
+  </si>
+  <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
+    <t>FA-11113</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
     <t>VENCIDO ACIMA DE 90 DIAS</t>
   </si>
   <si>
-    <t>ND-11056</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>LENILDO DE LIMA</t>
-  </si>
-  <si>
-    <t>VENCIDO</t>
-  </si>
-  <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11455</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11426</t>
+  </si>
+  <si>
+    <t>FA-11244</t>
+  </si>
+  <si>
+    <t>FA-11390</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>FA-11115</t>
+  </si>
+  <si>
+    <t>FA-11256</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>FA-11407</t>
+  </si>
+  <si>
+    <t>FA-11183</t>
+  </si>
+  <si>
+    <t>FA-11361</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11346</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>FA-11456</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11253</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11387</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11147</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>FA-11392</t>
+  </si>
+  <si>
+    <t>FA-11516</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11462</t>
+  </si>
+  <si>
+    <t>FA-11153</t>
+  </si>
+  <si>
+    <t>FA-11393</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11350</t>
+  </si>
+  <si>
+    <t>FA-11391</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11485</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11517</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11500</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
+  </si>
+  <si>
+    <t>FA-11369</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11111</t>
+  </si>
+  <si>
+    <t>FA-11276</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11430</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11463</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11408</t>
+  </si>
+  <si>
+    <t>FA-11352</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11459</t>
+  </si>
+  <si>
+    <t>FA-11518</t>
+  </si>
+  <si>
+    <t>FA-11325</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11265</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FA-11545</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11348</t>
+  </si>
+  <si>
+    <t>FA-11347</t>
+  </si>
+  <si>
+    <t>FA-11446</t>
+  </si>
+  <si>
+    <t>FA-11362</t>
   </si>
   <si>
     <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>VENCIDO ATÉ 30 DIAS</t>
-  </si>
-  <si>
-    <t>FA-11240</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FATURA</t>
-  </si>
-  <si>
-    <t>FA-11155</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11447</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11421</t>
-  </si>
-  <si>
-    <t>FA-11406</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11383</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11419</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11189</t>
-  </si>
-  <si>
-    <t>FA-11182</t>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>FA-11069</t>
-  </si>
-  <si>
-    <t>ALBERTO MANOEL DOS REIS</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>ND-11305</t>
-  </si>
-  <si>
-    <t>FA-11113</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11426</t>
-  </si>
-  <si>
-    <t>FA-11455</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11244</t>
-  </si>
-  <si>
-    <t>FA-11390</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>FA-11115</t>
-  </si>
-  <si>
-    <t>FA-11256</t>
-  </si>
-  <si>
-    <t>FA-11407</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>FA-11183</t>
-  </si>
-  <si>
-    <t>FA-11361</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11346</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>FA-11456</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11253</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11387</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11147</t>
-  </si>
-  <si>
-    <t>FA-11516</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11392</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>FA-11153</t>
-  </si>
-  <si>
-    <t>FA-11462</t>
-  </si>
-  <si>
-    <t>FA-11517</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11350</t>
-  </si>
-  <si>
-    <t>FA-11485</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11391</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11393</t>
-  </si>
-  <si>
-    <t>FA-11369</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>FA-11500</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11276</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11111</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>FA-11430</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11408</t>
-  </si>
-  <si>
-    <t>FA-11352</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11459</t>
-  </si>
-  <si>
-    <t>FA-11518</t>
-  </si>
-  <si>
-    <t>FA-11463</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11325</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11265</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11545</t>
-  </si>
-  <si>
-    <t>REGINALDO BENTO DA SILVA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11348</t>
-  </si>
-  <si>
-    <t>FA-11347</t>
-  </si>
-  <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>FA-11362</t>
   </si>
 </sst>
 </file>
@@ -579,7 +573,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:S74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -684,22 +678,22 @@
         <v>22</v>
       </c>
       <c r="B6" s="7">
-        <v>46030</v>
+        <v>46118</v>
       </c>
       <c r="C6" s="7">
-        <v>45992</v>
+        <v>46118</v>
       </c>
       <c r="D6" s="7">
-        <v>46030</v>
+        <v>46118</v>
       </c>
       <c r="E6" s="7">
-        <v>46044</v>
+        <v>46086</v>
       </c>
       <c r="F6" s="8">
-        <v>-106</v>
+        <v>-18</v>
       </c>
       <c r="G6" s="8">
-        <v>-106</v>
+        <v>-18</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -717,7 +711,7 @@
         <v>26</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>27</v>
@@ -735,7 +729,7 @@
         <v>29</v>
       </c>
       <c r="S6" s="9">
-        <v>195.23</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
@@ -743,37 +737,37 @@
         <v>22</v>
       </c>
       <c r="B7" s="7">
-        <v>46052</v>
+        <v>46125</v>
       </c>
       <c r="C7" s="7">
-        <v>45930</v>
+        <v>46104</v>
       </c>
       <c r="D7" s="7">
-        <v>46052</v>
+        <v>46104</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F7" s="8">
-        <v>-84</v>
+        <v>-32</v>
       </c>
       <c r="G7" s="8">
-        <v>-84</v>
+        <v>-11</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>25</v>
@@ -791,10 +785,10 @@
         <v>25</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S7" s="9">
-        <v>185.5</v>
+        <v>165.25</v>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
@@ -802,28 +796,28 @@
         <v>22</v>
       </c>
       <c r="B8" s="7">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="C8" s="7">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="D8" s="7">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="E8" s="7">
-        <v>46086</v>
+        <v>46122</v>
       </c>
       <c r="F8" s="8">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="G8" s="8">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>33</v>
@@ -835,7 +829,7 @@
         <v>34</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>27</v>
@@ -847,13 +841,13 @@
         <v>25</v>
       </c>
       <c r="Q8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R8" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S8" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
@@ -864,25 +858,25 @@
         <v>46125</v>
       </c>
       <c r="C9" s="7">
-        <v>46104</v>
+        <v>46125</v>
       </c>
       <c r="D9" s="7">
-        <v>46104</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>25</v>
+        <v>46125</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46119</v>
       </c>
       <c r="F9" s="8">
-        <v>-32</v>
+        <v>-11</v>
       </c>
       <c r="G9" s="8">
         <v>-11</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>36</v>
@@ -894,7 +888,7 @@
         <v>37</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>27</v>
@@ -906,13 +900,13 @@
         <v>25</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S9" s="9">
-        <v>165.25</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
@@ -929,7 +923,7 @@
         <v>46125</v>
       </c>
       <c r="E10" s="7">
-        <v>46122</v>
+        <v>46118</v>
       </c>
       <c r="F10" s="8">
         <v>-11</v>
@@ -938,10 +932,10 @@
         <v>-11</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>38</v>
@@ -950,7 +944,7 @@
         <v>25</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>25</v>
@@ -965,13 +959,13 @@
         <v>25</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S10" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1">
@@ -988,7 +982,7 @@
         <v>46125</v>
       </c>
       <c r="E11" s="7">
-        <v>46119</v>
+        <v>46087</v>
       </c>
       <c r="F11" s="8">
         <v>-11</v>
@@ -997,22 +991,22 @@
         <v>-11</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>27</v>
@@ -1024,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S11" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
@@ -1047,7 +1041,7 @@
         <v>46125</v>
       </c>
       <c r="E12" s="7">
-        <v>46118</v>
+        <v>46113</v>
       </c>
       <c r="F12" s="8">
         <v>-11</v>
@@ -1056,22 +1050,22 @@
         <v>-11</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>27</v>
@@ -1083,7 +1077,7 @@
         <v>25</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1097,40 +1091,40 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C13" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D13" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46113</v>
+        <v>46118</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F13" s="8">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="G13" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="M13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>27</v>
@@ -1142,13 +1136,13 @@
         <v>25</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S13" s="9">
-        <v>680</v>
+        <v>130.16</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1156,38 +1150,38 @@
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C14" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D14" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46087</v>
+        <v>46118</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F14" s="8">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="G14" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="M14" s="6" t="s">
         <v>25</v>
       </c>
@@ -1201,13 +1195,13 @@
         <v>25</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S14" s="9">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1215,7 +1209,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C15" s="7">
         <v>46118</v>
@@ -1230,25 +1224,25 @@
         <v>-18</v>
       </c>
       <c r="G15" s="8">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1266,7 +1260,7 @@
         <v>29</v>
       </c>
       <c r="S15" s="9">
-        <v>130.16</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1274,40 +1268,40 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="C16" s="7">
-        <v>46118</v>
+        <v>46111</v>
       </c>
       <c r="D16" s="7">
-        <v>46118</v>
+        <v>46111</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="8">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="G16" s="8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>27</v>
@@ -1325,7 +1319,7 @@
         <v>29</v>
       </c>
       <c r="S16" s="9">
-        <v>400</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1333,37 +1327,37 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="C17" s="7">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="D17" s="7">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="8">
-        <v>-18</v>
+        <v>-32</v>
       </c>
       <c r="G17" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>25</v>
@@ -1381,10 +1375,10 @@
         <v>25</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S17" s="9">
-        <v>260</v>
+        <v>357.49</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1392,50 +1386,50 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C18" s="7">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="D18" s="7">
-        <v>46111</v>
+        <v>46118</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="G18" s="8">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="Q18" s="6" t="s">
         <v>25</v>
       </c>
@@ -1443,7 +1437,7 @@
         <v>29</v>
       </c>
       <c r="S18" s="9">
-        <v>119.57</v>
+        <v>91.54</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1451,28 +1445,28 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C19" s="7">
-        <v>46104</v>
+        <v>46082</v>
       </c>
       <c r="D19" s="7">
-        <v>46104</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46097</v>
       </c>
       <c r="F19" s="8">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="G19" s="8">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>54</v>
@@ -1481,28 +1475,28 @@
         <v>25</v>
       </c>
       <c r="L19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R19" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S19" s="9">
-        <v>357.49</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1528,10 +1522,10 @@
         <v>-4</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>56</v>
@@ -1552,7 +1546,7 @@
         <v>27</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>25</v>
@@ -1561,7 +1555,7 @@
         <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>91.54</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1572,25 +1566,25 @@
         <v>46132</v>
       </c>
       <c r="C21" s="7">
-        <v>46082</v>
+        <v>45901</v>
       </c>
       <c r="D21" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46097</v>
+        <v>45938</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F21" s="8">
-        <v>-4</v>
+        <v>-198</v>
       </c>
       <c r="G21" s="8">
         <v>-4</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>59</v>
@@ -1599,7 +1593,7 @@
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>25</v>
@@ -1614,13 +1608,13 @@
         <v>25</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S21" s="9">
-        <v>146.55</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1631,37 +1625,37 @@
         <v>46132</v>
       </c>
       <c r="C22" s="7">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="D22" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46119</v>
       </c>
       <c r="F22" s="8">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="8">
         <v>-4</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1673,13 +1667,13 @@
         <v>25</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S22" s="9">
-        <v>200</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1690,16 +1684,16 @@
         <v>46132</v>
       </c>
       <c r="C23" s="7">
-        <v>45901</v>
+        <v>46132</v>
       </c>
       <c r="D23" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E23" s="7">
+        <v>46118</v>
       </c>
       <c r="F23" s="8">
-        <v>-198</v>
+        <v>-4</v>
       </c>
       <c r="G23" s="8">
         <v>-4</v>
@@ -1708,16 +1702,16 @@
         <v>23</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>25</v>
@@ -1732,13 +1726,13 @@
         <v>25</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S23" s="9">
-        <v>546</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1755,7 +1749,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="7">
-        <v>46118</v>
+        <v>46086</v>
       </c>
       <c r="F24" s="8">
         <v>-4</v>
@@ -1764,10 +1758,10 @@
         <v>-4</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>64</v>
@@ -1776,10 +1770,10 @@
         <v>25</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1791,7 +1785,7 @@
         <v>25</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>29</v>
@@ -1814,7 +1808,7 @@
         <v>46132</v>
       </c>
       <c r="E25" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F25" s="8">
         <v>-4</v>
@@ -1823,10 +1817,10 @@
         <v>-4</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>65</v>
@@ -1838,7 +1832,7 @@
         <v>66</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1850,13 +1844,13 @@
         <v>25</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S25" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1873,7 +1867,7 @@
         <v>46132</v>
       </c>
       <c r="E26" s="7">
-        <v>46086</v>
+        <v>46119</v>
       </c>
       <c r="F26" s="8">
         <v>-4</v>
@@ -1882,10 +1876,10 @@
         <v>-4</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>67</v>
@@ -1894,10 +1888,10 @@
         <v>25</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1909,13 +1903,13 @@
         <v>25</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S26" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1932,7 +1926,7 @@
         <v>46132</v>
       </c>
       <c r="E27" s="7">
-        <v>46112</v>
+        <v>46057</v>
       </c>
       <c r="F27" s="8">
         <v>-4</v>
@@ -1941,10 +1935,10 @@
         <v>-4</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>68</v>
@@ -1953,7 +1947,7 @@
         <v>25</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>25</v>
@@ -1968,13 +1962,13 @@
         <v>25</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1991,7 +1985,7 @@
         <v>46132</v>
       </c>
       <c r="E28" s="7">
-        <v>46119</v>
+        <v>46087</v>
       </c>
       <c r="F28" s="8">
         <v>-4</v>
@@ -2000,22 +1994,22 @@
         <v>-4</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2027,13 +2021,13 @@
         <v>25</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S28" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2050,7 +2044,7 @@
         <v>46132</v>
       </c>
       <c r="E29" s="7">
-        <v>46057</v>
+        <v>46118</v>
       </c>
       <c r="F29" s="8">
         <v>-4</v>
@@ -2059,20 +2053,20 @@
         <v>-4</v>
       </c>
       <c r="H29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="M29" s="6" t="s">
         <v>25</v>
       </c>
@@ -2086,13 +2080,13 @@
         <v>25</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2109,7 +2103,7 @@
         <v>46132</v>
       </c>
       <c r="E30" s="7">
-        <v>46087</v>
+        <v>46113</v>
       </c>
       <c r="F30" s="8">
         <v>-4</v>
@@ -2118,22 +2112,22 @@
         <v>-4</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2145,7 +2139,7 @@
         <v>25</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>29</v>
@@ -2159,40 +2153,40 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C31" s="7">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="D31" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E31" s="7">
-        <v>46113</v>
+        <v>46111</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F31" s="8">
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="G31" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2204,13 +2198,13 @@
         <v>25</v>
       </c>
       <c r="Q31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R31" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R31" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S31" s="9">
-        <v>680</v>
+        <v>321.17</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2218,38 +2212,38 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C32" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D32" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="E32" s="7">
-        <v>46118</v>
+        <v>46100</v>
       </c>
       <c r="F32" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G32" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="M32" s="6" t="s">
         <v>25</v>
       </c>
@@ -2263,10 +2257,10 @@
         <v>25</v>
       </c>
       <c r="Q32" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="R32" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="S32" s="9">
         <v>680</v>
@@ -2277,37 +2271,37 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="C33" s="7">
-        <v>46118</v>
+        <v>46082</v>
       </c>
       <c r="D33" s="7">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="8">
-        <v>-25</v>
+        <v>-11</v>
       </c>
       <c r="G33" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>25</v>
@@ -2325,10 +2319,10 @@
         <v>25</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S33" s="9">
-        <v>321.17</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2336,40 +2330,40 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="C34" s="7">
-        <v>46133</v>
+        <v>46132</v>
       </c>
       <c r="D34" s="7">
-        <v>46133</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46100</v>
+        <v>46132</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F34" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G34" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K34" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="M34" s="6" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2381,13 +2375,13 @@
         <v>25</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>680</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2398,34 +2392,34 @@
         <v>46134</v>
       </c>
       <c r="C35" s="7">
-        <v>46082</v>
+        <v>46132</v>
       </c>
       <c r="D35" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G35" s="8">
         <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>25</v>
@@ -2443,10 +2437,10 @@
         <v>25</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>79.05</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2454,28 +2448,28 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C36" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D36" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G36" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>78</v>
@@ -2484,10 +2478,10 @@
         <v>25</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2505,7 +2499,7 @@
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>200</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2513,7 +2507,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="C37" s="7">
         <v>46132</v>
@@ -2528,23 +2522,23 @@
         <v>-4</v>
       </c>
       <c r="G37" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="M37" s="6" t="s">
         <v>25</v>
       </c>
@@ -2555,7 +2549,7 @@
         <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>25</v>
@@ -2564,7 +2558,7 @@
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2572,28 +2566,28 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C38" s="7">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="D38" s="7">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F38" s="8">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="G38" s="8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>81</v>
@@ -2602,7 +2596,7 @@
         <v>25</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>25</v>
@@ -2611,7 +2605,7 @@
         <v>27</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>25</v>
@@ -2623,7 +2617,7 @@
         <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>550</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2631,49 +2625,49 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C39" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D39" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G39" s="8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="P39" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>25</v>
@@ -2682,7 +2676,7 @@
         <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>650</v>
+        <v>302.72</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2690,58 +2684,58 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C40" s="7">
-        <v>46111</v>
+        <v>46082</v>
       </c>
       <c r="D40" s="7">
-        <v>46111</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46097</v>
       </c>
       <c r="F40" s="8">
-        <v>-25</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S40" s="9">
-        <v>180</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2749,37 +2743,37 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C41" s="7">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="D41" s="7">
-        <v>46125</v>
+        <v>46083</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="8">
-        <v>-11</v>
+        <v>-53</v>
       </c>
       <c r="G41" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>25</v>
@@ -2788,7 +2782,7 @@
         <v>27</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>25</v>
@@ -2800,7 +2794,7 @@
         <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>302.72</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2811,13 +2805,13 @@
         <v>46139</v>
       </c>
       <c r="C42" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D42" s="7">
         <v>46139</v>
       </c>
       <c r="E42" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F42" s="8">
         <v>3</v>
@@ -2832,22 +2826,22 @@
         <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>25</v>
@@ -2856,10 +2850,10 @@
         <v>28</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S42" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2870,55 +2864,55 @@
         <v>46139</v>
       </c>
       <c r="C43" s="7">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="D43" s="7">
-        <v>46083</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46112</v>
       </c>
       <c r="F43" s="8">
-        <v>-53</v>
+        <v>3</v>
       </c>
       <c r="G43" s="8">
         <v>3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>320</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2950,28 +2944,28 @@
         <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="M44" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>29</v>
@@ -2994,7 +2988,7 @@
         <v>46139</v>
       </c>
       <c r="E45" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F45" s="8">
         <v>3</v>
@@ -3009,34 +3003,34 @@
         <v>25</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R45" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R45" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S45" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3050,52 +3044,52 @@
         <v>46139</v>
       </c>
       <c r="D46" s="7">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="E46" s="7">
-        <v>46119</v>
+        <v>46057</v>
       </c>
       <c r="F46" s="8">
-        <v>3</v>
+        <v>-32</v>
       </c>
       <c r="G46" s="8">
         <v>3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3109,52 +3103,52 @@
         <v>46139</v>
       </c>
       <c r="D47" s="7">
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="E47" s="7">
-        <v>46057</v>
+        <v>46112</v>
       </c>
       <c r="F47" s="8">
-        <v>-32</v>
+        <v>3</v>
       </c>
       <c r="G47" s="8">
         <v>3</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3171,7 +3165,7 @@
         <v>46139</v>
       </c>
       <c r="E48" s="7">
-        <v>46119</v>
+        <v>46100</v>
       </c>
       <c r="F48" s="8">
         <v>3</v>
@@ -3186,34 +3180,34 @@
         <v>25</v>
       </c>
       <c r="J48" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K48" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="M48" s="6" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S48" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3230,7 +3224,7 @@
         <v>46139</v>
       </c>
       <c r="E49" s="7">
-        <v>46127</v>
+        <v>46100</v>
       </c>
       <c r="F49" s="8">
         <v>3</v>
@@ -3251,22 +3245,22 @@
         <v>25</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>29</v>
@@ -3289,7 +3283,7 @@
         <v>46139</v>
       </c>
       <c r="E50" s="7">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="F50" s="8">
         <v>3</v>
@@ -3304,28 +3298,28 @@
         <v>25</v>
       </c>
       <c r="J50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="M50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>29</v>
@@ -3348,7 +3342,7 @@
         <v>46139</v>
       </c>
       <c r="E51" s="7">
-        <v>46100</v>
+        <v>46119</v>
       </c>
       <c r="F51" s="8">
         <v>3</v>
@@ -3363,28 +3357,28 @@
         <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="M51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>29</v>
@@ -3407,7 +3401,7 @@
         <v>46139</v>
       </c>
       <c r="E52" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F52" s="8">
         <v>3</v>
@@ -3434,16 +3428,16 @@
         <v>25</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>29</v>
@@ -3466,7 +3460,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F53" s="8">
         <v>3</v>
@@ -3493,22 +3487,22 @@
         <v>25</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S53" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3522,19 +3516,19 @@
         <v>46139</v>
       </c>
       <c r="D54" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E54" s="7">
-        <v>46112</v>
+        <v>46122</v>
       </c>
       <c r="F54" s="8">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G54" s="8">
         <v>3</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>25</v>
@@ -3546,28 +3540,28 @@
         <v>25</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q54" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R54" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R54" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S54" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3584,7 +3578,7 @@
         <v>46139</v>
       </c>
       <c r="E55" s="7">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="F55" s="8">
         <v>3</v>
@@ -3605,22 +3599,22 @@
         <v>25</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>29</v>
@@ -3643,7 +3637,7 @@
         <v>46139</v>
       </c>
       <c r="E56" s="7">
-        <v>46119</v>
+        <v>46101</v>
       </c>
       <c r="F56" s="8">
         <v>3</v>
@@ -3658,28 +3652,28 @@
         <v>25</v>
       </c>
       <c r="J56" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="M56" s="6" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>29</v>
@@ -3699,19 +3693,19 @@
         <v>46139</v>
       </c>
       <c r="D57" s="7">
-        <v>46139</v>
+        <v>46104</v>
       </c>
       <c r="E57" s="7">
-        <v>46127</v>
+        <v>46057</v>
       </c>
       <c r="F57" s="8">
-        <v>3</v>
+        <v>-32</v>
       </c>
       <c r="G57" s="8">
         <v>3</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>25</v>
@@ -3723,22 +3717,22 @@
         <v>25</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>29</v>
@@ -3776,28 +3770,28 @@
         <v>25</v>
       </c>
       <c r="J58" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="M58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>29</v>
@@ -3817,52 +3811,52 @@
         <v>46139</v>
       </c>
       <c r="D59" s="7">
-        <v>46104</v>
+        <v>46139</v>
       </c>
       <c r="E59" s="7">
-        <v>46057</v>
+        <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>-32</v>
+        <v>3</v>
       </c>
       <c r="G59" s="8">
         <v>3</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="K59" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="M59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S59" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3876,19 +3870,19 @@
         <v>46139</v>
       </c>
       <c r="D60" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E60" s="7">
-        <v>46122</v>
+        <v>46119</v>
       </c>
       <c r="F60" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G60" s="8">
         <v>3</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>25</v>
@@ -3900,28 +3894,28 @@
         <v>25</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S60" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3938,7 +3932,7 @@
         <v>46139</v>
       </c>
       <c r="E61" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F61" s="8">
         <v>3</v>
@@ -3953,34 +3947,34 @@
         <v>25</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -3997,7 +3991,7 @@
         <v>46139</v>
       </c>
       <c r="E62" s="7">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="F62" s="8">
         <v>3</v>
@@ -4018,22 +4012,22 @@
         <v>25</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>29</v>
@@ -4056,7 +4050,7 @@
         <v>46139</v>
       </c>
       <c r="E63" s="7">
-        <v>46100</v>
+        <v>46119</v>
       </c>
       <c r="F63" s="8">
         <v>3</v>
@@ -4071,31 +4065,31 @@
         <v>25</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R63" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="R63" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="S63" s="9">
         <v>680</v>
@@ -4115,7 +4109,7 @@
         <v>46139</v>
       </c>
       <c r="E64" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F64" s="8">
         <v>3</v>
@@ -4136,25 +4130,25 @@
         <v>25</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S64" s="9">
         <v>680</v>
@@ -4174,7 +4168,7 @@
         <v>46139</v>
       </c>
       <c r="E65" s="7">
-        <v>46127</v>
+        <v>46099</v>
       </c>
       <c r="F65" s="8">
         <v>3</v>
@@ -4195,28 +4189,28 @@
         <v>25</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Q65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R65" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="R65" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S65" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4233,7 +4227,7 @@
         <v>46139</v>
       </c>
       <c r="E66" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F66" s="8">
         <v>3</v>
@@ -4248,34 +4242,34 @@
         <v>25</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S66" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4292,7 +4286,7 @@
         <v>46139</v>
       </c>
       <c r="E67" s="7">
-        <v>46099</v>
+        <v>46119</v>
       </c>
       <c r="F67" s="8">
         <v>3</v>
@@ -4307,31 +4301,31 @@
         <v>25</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S67" s="9">
         <v>700</v>
@@ -4351,7 +4345,7 @@
         <v>46139</v>
       </c>
       <c r="E68" s="7">
-        <v>46092</v>
+        <v>46129</v>
       </c>
       <c r="F68" s="8">
         <v>3</v>
@@ -4378,22 +4372,22 @@
         <v>25</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="S68" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4401,58 +4395,58 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C69" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D69" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E69" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F69" s="8">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G69" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S69" s="9">
-        <v>700</v>
+        <v>110.69</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4460,58 +4454,58 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C70" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D70" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E70" s="7">
-        <v>46129</v>
+        <v>46132</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F70" s="8">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G70" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="S70" s="9">
-        <v>800</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4522,34 +4516,34 @@
         <v>46140</v>
       </c>
       <c r="C71" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D71" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F71" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G71" s="8">
         <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>25</v>
@@ -4558,7 +4552,7 @@
         <v>27</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>25</v>
@@ -4567,10 +4561,10 @@
         <v>25</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S71" s="9">
-        <v>110.69</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4581,55 +4575,55 @@
         <v>46140</v>
       </c>
       <c r="C72" s="7">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="D72" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>25</v>
+        <v>46140</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46100</v>
       </c>
       <c r="F72" s="8">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8">
         <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S72" s="9">
-        <v>124.25</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4637,46 +4631,46 @@
         <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="C73" s="7">
-        <v>46125</v>
+        <v>45930</v>
       </c>
       <c r="D73" s="7">
-        <v>46125</v>
+        <v>46142</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F73" s="8">
-        <v>-11</v>
+        <v>6</v>
       </c>
       <c r="G73" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>25</v>
@@ -4685,187 +4679,69 @@
         <v>25</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="S73" s="9">
-        <v>408.24</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
-      <c r="A74" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B74" s="7">
-        <v>46140</v>
-      </c>
-      <c r="C74" s="7">
-        <v>46140</v>
-      </c>
-      <c r="D74" s="7">
-        <v>46140</v>
-      </c>
-      <c r="E74" s="7">
-        <v>46100</v>
-      </c>
-      <c r="F74" s="8">
-        <v>4</v>
-      </c>
-      <c r="G74" s="8">
-        <v>4</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q74" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R74" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="S74" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="75" ht="23" customHeight="1">
-      <c r="A75" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B75" s="7">
-        <v>46142</v>
-      </c>
-      <c r="C75" s="7">
-        <v>45930</v>
-      </c>
-      <c r="D75" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75" s="8">
-        <v>6</v>
-      </c>
-      <c r="G75" s="8">
-        <v>6</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N75" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="O75" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="P75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="S75" s="9">
-        <v>185.5</v>
-      </c>
-    </row>
-    <row r="76" ht="23" customHeight="1">
-      <c r="A76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="P76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R76" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="S76" s="13">
-        <f>SUM(S6:S75)</f>
+      <c r="A74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="R74" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S74" s="13">
+        <f>SUM(S6:S73)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 29 de abril de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 30 de abril de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -106,15 +106,18 @@
     <t/>
   </si>
   <si>
+    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>VENCIDO</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>VENCIDO</t>
-  </si>
-  <si>
     <t>FA-11240</t>
   </si>
   <si>
@@ -337,22 +340,16 @@
     <t>RAMON TALLES BARBALHO DE FRANÇA</t>
   </si>
   <si>
-    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
-  </si>
-  <si>
     <t>FA-11155</t>
   </si>
   <si>
+    <t>FA-11419</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
     <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11419</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
   </si>
 </sst>
 </file>
@@ -612,10 +609,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G6" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -671,28 +668,28 @@
         <v>46086</v>
       </c>
       <c r="F7" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G7" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>26</v>
@@ -704,10 +701,10 @@
         <v>23</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S7" s="9">
         <v>620</v>
@@ -730,28 +727,28 @@
         <v>46113</v>
       </c>
       <c r="F8" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G8" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>26</v>
@@ -763,10 +760,10 @@
         <v>23</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="9">
         <v>680</v>
@@ -789,16 +786,16 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G9" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>23</v>
@@ -807,7 +804,7 @@
         <v>23</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>23</v>
@@ -825,7 +822,7 @@
         <v>23</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S9" s="9">
         <v>260</v>
@@ -848,25 +845,25 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G10" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>23</v>
@@ -878,13 +875,13 @@
         <v>26</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>23</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S10" s="9">
         <v>91.54</v>
@@ -907,25 +904,25 @@
         <v>46118</v>
       </c>
       <c r="F11" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G11" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>23</v>
@@ -940,10 +937,10 @@
         <v>23</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S11" s="9">
         <v>620</v>
@@ -966,28 +963,28 @@
         <v>46086</v>
       </c>
       <c r="F12" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>26</v>
@@ -999,10 +996,10 @@
         <v>23</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S12" s="9">
         <v>620</v>
@@ -1025,28 +1022,28 @@
         <v>46119</v>
       </c>
       <c r="F13" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G13" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>26</v>
@@ -1058,10 +1055,10 @@
         <v>23</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S13" s="9">
         <v>620</v>
@@ -1084,25 +1081,25 @@
         <v>46057</v>
       </c>
       <c r="F14" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G14" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>23</v>
@@ -1117,10 +1114,10 @@
         <v>23</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S14" s="9">
         <v>650</v>
@@ -1143,25 +1140,25 @@
         <v>46118</v>
       </c>
       <c r="F15" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G15" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>23</v>
@@ -1176,10 +1173,10 @@
         <v>23</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S15" s="9">
         <v>680</v>
@@ -1202,28 +1199,28 @@
         <v>46113</v>
       </c>
       <c r="F16" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G16" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>26</v>
@@ -1235,10 +1232,10 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S16" s="9">
         <v>680</v>
@@ -1261,25 +1258,25 @@
         <v>46087</v>
       </c>
       <c r="F17" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G17" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1294,10 +1291,10 @@
         <v>23</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S17" s="9">
         <v>680</v>
@@ -1320,25 +1317,25 @@
         <v>46127</v>
       </c>
       <c r="F18" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G18" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
@@ -1350,13 +1347,13 @@
         <v>26</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S18" s="9">
         <v>680</v>
@@ -1379,25 +1376,25 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
+        <v>-10</v>
+      </c>
+      <c r="G19" s="8">
         <v>-9</v>
       </c>
-      <c r="G19" s="8">
-        <v>-8</v>
-      </c>
       <c r="H19" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>23</v>
@@ -1415,7 +1412,7 @@
         <v>23</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S19" s="9">
         <v>107.71</v>
@@ -1438,25 +1435,25 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G20" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>23</v>
@@ -1474,7 +1471,7 @@
         <v>23</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S20" s="9">
         <v>321.17</v>
@@ -1497,26 +1494,26 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
       </c>
@@ -1533,7 +1530,7 @@
         <v>23</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S21" s="9">
         <v>79.05</v>
@@ -1556,28 +1553,28 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>26</v>
@@ -1592,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S22" s="9">
         <v>200</v>
@@ -1615,25 +1612,25 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G23" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1651,7 +1648,7 @@
         <v>23</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S23" s="9">
         <v>550</v>
@@ -1674,25 +1671,25 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G24" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1704,13 +1701,13 @@
         <v>26</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S24" s="9">
         <v>650</v>
@@ -1733,25 +1730,25 @@
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G25" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -1769,7 +1766,7 @@
         <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S25" s="9">
         <v>100</v>
@@ -1792,25 +1789,25 @@
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G26" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1828,7 +1825,7 @@
         <v>23</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S26" s="9">
         <v>180</v>
@@ -1851,25 +1848,25 @@
         <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G27" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1887,7 +1884,7 @@
         <v>23</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S27" s="9">
         <v>302.72</v>
@@ -1910,25 +1907,25 @@
         <v>46127</v>
       </c>
       <c r="F28" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G28" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -1940,13 +1937,13 @@
         <v>26</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S28" s="9">
         <v>97.15</v>
@@ -1969,26 +1966,26 @@
         <v>46097</v>
       </c>
       <c r="F29" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G29" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K29" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
       </c>
@@ -2002,10 +1999,10 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S29" s="9">
         <v>146.55</v>
@@ -2028,25 +2025,25 @@
         <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G30" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2064,7 +2061,7 @@
         <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S30" s="9">
         <v>154.92</v>
@@ -2087,25 +2084,25 @@
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-203</v>
+        <v>-204</v>
       </c>
       <c r="G31" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2123,7 +2120,7 @@
         <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S31" s="9">
         <v>426</v>
@@ -2146,25 +2143,25 @@
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G32" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2182,7 +2179,7 @@
         <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S32" s="9">
         <v>500</v>
@@ -2205,28 +2202,28 @@
         <v>46127</v>
       </c>
       <c r="F33" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G33" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>26</v>
@@ -2238,10 +2235,10 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S33" s="9">
         <v>600</v>
@@ -2264,28 +2261,28 @@
         <v>46119</v>
       </c>
       <c r="F34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>26</v>
@@ -2297,10 +2294,10 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S34" s="9">
         <v>600</v>
@@ -2323,28 +2320,28 @@
         <v>46141</v>
       </c>
       <c r="F35" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G35" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>26</v>
@@ -2356,10 +2353,10 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S35" s="9">
         <v>620</v>
@@ -2382,25 +2379,25 @@
         <v>46141</v>
       </c>
       <c r="F36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2415,10 +2412,10 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S36" s="9">
         <v>620</v>
@@ -2441,28 +2438,28 @@
         <v>46119</v>
       </c>
       <c r="F37" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G37" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>26</v>
@@ -2474,10 +2471,10 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S37" s="9">
         <v>620</v>
@@ -2500,25 +2497,25 @@
         <v>46100</v>
       </c>
       <c r="F38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2533,10 +2530,10 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S38" s="9">
         <v>630</v>
@@ -2559,25 +2556,25 @@
         <v>46112</v>
       </c>
       <c r="F39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2592,10 +2589,10 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S39" s="9">
         <v>630</v>
@@ -2618,28 +2615,28 @@
         <v>46119</v>
       </c>
       <c r="F40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>26</v>
@@ -2651,10 +2648,10 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S40" s="9">
         <v>650</v>
@@ -2677,25 +2674,25 @@
         <v>46122</v>
       </c>
       <c r="F41" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2710,10 +2707,10 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S41" s="9">
         <v>650</v>
@@ -2736,25 +2733,25 @@
         <v>46119</v>
       </c>
       <c r="F42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2769,10 +2766,10 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S42" s="9">
         <v>680</v>
@@ -2795,25 +2792,25 @@
         <v>46141</v>
       </c>
       <c r="F43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
@@ -2828,10 +2825,10 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S43" s="9">
         <v>680</v>
@@ -2854,28 +2851,28 @@
         <v>46113</v>
       </c>
       <c r="F44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>26</v>
@@ -2887,10 +2884,10 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S44" s="9">
         <v>680</v>
@@ -2913,25 +2910,25 @@
         <v>46119</v>
       </c>
       <c r="F45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -2946,10 +2943,10 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S45" s="9">
         <v>680</v>
@@ -2972,25 +2969,25 @@
         <v>46119</v>
       </c>
       <c r="F46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3002,13 +2999,13 @@
         <v>26</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S46" s="9">
         <v>700</v>
@@ -3031,26 +3028,26 @@
         <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G47" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J47" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
       </c>
@@ -3067,7 +3064,7 @@
         <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S47" s="9">
         <v>104.04</v>
@@ -3090,25 +3087,25 @@
         <v>23</v>
       </c>
       <c r="F48" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G48" s="8">
         <v>-2</v>
       </c>
-      <c r="G48" s="8">
-        <v>-1</v>
-      </c>
       <c r="H48" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3126,7 +3123,7 @@
         <v>23</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S48" s="9">
         <v>120</v>
@@ -3149,25 +3146,25 @@
         <v>23</v>
       </c>
       <c r="F49" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G49" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3185,7 +3182,7 @@
         <v>23</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S49" s="9">
         <v>124.25</v>
@@ -3208,26 +3205,26 @@
         <v>23</v>
       </c>
       <c r="F50" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G50" s="8">
         <v>-2</v>
       </c>
-      <c r="G50" s="8">
-        <v>-1</v>
-      </c>
       <c r="H50" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J50" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
       </c>
@@ -3244,7 +3241,7 @@
         <v>23</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S50" s="9">
         <v>202.27</v>
@@ -3267,25 +3264,25 @@
         <v>23</v>
       </c>
       <c r="F51" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G51" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3303,7 +3300,7 @@
         <v>23</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S51" s="9">
         <v>350</v>
@@ -3326,25 +3323,25 @@
         <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3362,7 +3359,7 @@
         <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S52" s="9">
         <v>408.24</v>
@@ -3385,25 +3382,25 @@
         <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3421,7 +3418,7 @@
         <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S53" s="9">
         <v>580</v>
@@ -3444,25 +3441,25 @@
         <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3480,7 +3477,7 @@
         <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S54" s="9">
         <v>590</v>
@@ -3503,16 +3500,16 @@
         <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>102</v>
@@ -3521,7 +3518,7 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3530,7 +3527,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
@@ -3539,7 +3536,7 @@
         <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S55" s="9">
         <v>151.25</v>
@@ -3562,25 +3559,25 @@
         <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3589,7 +3586,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3598,7 +3595,7 @@
         <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S56" s="9">
         <v>200</v>
@@ -3621,34 +3618,34 @@
         <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3657,7 +3654,7 @@
         <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S57" s="9">
         <v>626.62</v>
@@ -3680,10 +3677,10 @@
         <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3704,10 +3701,10 @@
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$146</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 30/04/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 30 de abril de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 4 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -148,48 +148,48 @@
     <t>PRIVADO</t>
   </si>
   <si>
+    <t>FA-11455</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11244</t>
+  </si>
+  <si>
     <t>FA-11426</t>
   </si>
   <si>
     <t>YURI BATISTA DA COSTA</t>
   </si>
   <si>
-    <t>FA-11244</t>
-  </si>
-  <si>
-    <t>FA-11455</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
     <t>FA-11115</t>
   </si>
   <si>
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
   </si>
   <si>
+    <t>FA-11514</t>
+  </si>
+  <si>
+    <t>FA-11407</t>
+  </si>
+  <si>
     <t>FA-11424</t>
   </si>
   <si>
     <t>OLIZIEL DA SILVA CARDOSO</t>
   </si>
   <si>
-    <t>FA-11407</t>
-  </si>
-  <si>
     <t>FA-11256</t>
   </si>
   <si>
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11514</t>
-  </si>
-  <si>
     <t>FA-11348</t>
   </si>
   <si>
@@ -262,12 +262,12 @@
     <t>FA-11458</t>
   </si>
   <si>
+    <t>FA-11550</t>
+  </si>
+  <si>
     <t>FA-11552</t>
   </si>
   <si>
-    <t>FA-11550</t>
-  </si>
-  <si>
     <t>FA-11462</t>
   </si>
   <si>
@@ -298,15 +298,15 @@
     <t>ELSON VIEIRA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11463</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
     <t>FA-11408</t>
   </si>
   <si>
-    <t>FA-11463</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
     <t>FA-11461</t>
   </si>
   <si>
@@ -349,7 +349,307 @@
     <t>FA-11453</t>
   </si>
   <si>
+    <t>ND-11574</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
     <t>HOJE</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11189</t>
+  </si>
+  <si>
+    <t>FA-11395</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11519</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11416</t>
+  </si>
+  <si>
+    <t>FA-11467</t>
+  </si>
+  <si>
+    <t>FA-11555</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>FA-11490</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11520</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11394</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11354</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>FA-11370</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11277</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11501</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11431</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11469</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>FA-11409</t>
+  </si>
+  <si>
+    <t>FA-11554</t>
+  </si>
+  <si>
+    <t>FA-11465</t>
+  </si>
+  <si>
+    <t>FA-11454</t>
+  </si>
+  <si>
+    <t>FA-11326</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11266</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>FA-11397</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>FA-11398</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>FA-11492</t>
+  </si>
+  <si>
+    <t>FA-11502</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FA-11371</t>
+  </si>
+  <si>
+    <t>FA-11432</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>FA-11410</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11327</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
+  </si>
+  <si>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>FA-11372</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FA-11433</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>FA-11268</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>FA-11494</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11373</t>
+  </si>
+  <si>
+    <t>FA-11434</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11329</t>
   </si>
 </sst>
 </file>
@@ -492,7 +792,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -512,7 +812,7 @@
     <col min="15" max="15" width="24.68001365661621" customWidth="1" style="1"/>
     <col min="16" max="16" width="14.40988826751709" customWidth="1" style="1"/>
     <col min="17" max="17" width="16.712258338928223" customWidth="1" style="1"/>
-    <col min="18" max="18" width="23.309049606323242" customWidth="1" style="1"/>
+    <col min="18" max="18" width="26.100889205932617" customWidth="1" style="1"/>
     <col min="19" max="19" width="15" customWidth="1" style="1"/>
     <col min="20" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
@@ -609,10 +909,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="G6" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -668,10 +968,10 @@
         <v>46086</v>
       </c>
       <c r="F7" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G7" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>27</v>
@@ -727,10 +1027,10 @@
         <v>46113</v>
       </c>
       <c r="F8" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G8" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>27</v>
@@ -786,10 +1086,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G9" s="8">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>27</v>
@@ -845,10 +1145,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G10" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>27</v>
@@ -901,13 +1201,13 @@
         <v>46132</v>
       </c>
       <c r="E11" s="7">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="F11" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G11" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>27</v>
@@ -925,7 +1225,7 @@
         <v>39</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>26</v>
@@ -940,7 +1240,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="S11" s="9">
         <v>620</v>
@@ -963,10 +1263,10 @@
         <v>46086</v>
       </c>
       <c r="F12" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G12" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>27</v>
@@ -975,7 +1275,7 @@
         <v>27</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>23</v>
@@ -1019,13 +1319,13 @@
         <v>46132</v>
       </c>
       <c r="E13" s="7">
-        <v>46119</v>
+        <v>46118</v>
       </c>
       <c r="F13" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G13" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>27</v>
@@ -1034,16 +1334,16 @@
         <v>27</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>26</v>
@@ -1058,7 +1358,7 @@
         <v>30</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="S13" s="9">
         <v>620</v>
@@ -1081,10 +1381,10 @@
         <v>46057</v>
       </c>
       <c r="F14" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G14" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>27</v>
@@ -1137,13 +1437,13 @@
         <v>46132</v>
       </c>
       <c r="E15" s="7">
-        <v>46118</v>
+        <v>46127</v>
       </c>
       <c r="F15" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G15" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>27</v>
@@ -1158,7 +1458,7 @@
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>23</v>
@@ -1170,7 +1470,7 @@
         <v>26</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>30</v>
@@ -1199,10 +1499,10 @@
         <v>46113</v>
       </c>
       <c r="F16" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G16" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>27</v>
@@ -1211,7 +1511,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
@@ -1255,13 +1555,13 @@
         <v>46132</v>
       </c>
       <c r="E17" s="7">
-        <v>46087</v>
+        <v>46118</v>
       </c>
       <c r="F17" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G17" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>27</v>
@@ -1270,13 +1570,13 @@
         <v>27</v>
       </c>
       <c r="J17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1314,13 +1614,13 @@
         <v>46132</v>
       </c>
       <c r="E18" s="7">
-        <v>46127</v>
+        <v>46087</v>
       </c>
       <c r="F18" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G18" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>27</v>
@@ -1329,14 +1629,14 @@
         <v>27</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
       </c>
@@ -1347,7 +1647,7 @@
         <v>26</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
         <v>30</v>
@@ -1376,10 +1676,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G19" s="8">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>27</v>
@@ -1435,10 +1735,10 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="G20" s="8">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>24</v>
@@ -1471,7 +1771,7 @@
         <v>23</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S20" s="9">
         <v>321.17</v>
@@ -1494,10 +1794,10 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G21" s="8">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>27</v>
@@ -1530,7 +1830,7 @@
         <v>23</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S21" s="9">
         <v>79.05</v>
@@ -1553,10 +1853,10 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G22" s="8">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>27</v>
@@ -1612,10 +1912,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G23" s="8">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>27</v>
@@ -1671,10 +1971,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G24" s="8">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>27</v>
@@ -1730,10 +2030,10 @@
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G25" s="8">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>27</v>
@@ -1789,10 +2089,10 @@
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="G26" s="8">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>24</v>
@@ -1807,7 +2107,7 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1848,10 +2148,10 @@
         <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G27" s="8">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>27</v>
@@ -1907,10 +2207,10 @@
         <v>46127</v>
       </c>
       <c r="F28" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G28" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>27</v>
@@ -1966,10 +2266,10 @@
         <v>46097</v>
       </c>
       <c r="F29" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G29" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>27</v>
@@ -2002,7 +2302,7 @@
         <v>67</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S29" s="9">
         <v>146.55</v>
@@ -2025,10 +2325,10 @@
         <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G30" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>27</v>
@@ -2084,10 +2384,10 @@
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-204</v>
+        <v>-208</v>
       </c>
       <c r="G31" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>69</v>
@@ -2143,10 +2443,10 @@
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G32" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>27</v>
@@ -2202,10 +2502,10 @@
         <v>46127</v>
       </c>
       <c r="F33" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G33" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>27</v>
@@ -2261,10 +2561,10 @@
         <v>46119</v>
       </c>
       <c r="F34" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G34" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>27</v>
@@ -2320,10 +2620,10 @@
         <v>46141</v>
       </c>
       <c r="F35" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G35" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>27</v>
@@ -2338,10 +2638,10 @@
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>26</v>
@@ -2379,10 +2679,10 @@
         <v>46141</v>
       </c>
       <c r="F36" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G36" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>27</v>
@@ -2397,10 +2697,10 @@
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>26</v>
@@ -2438,10 +2738,10 @@
         <v>46119</v>
       </c>
       <c r="F37" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G37" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>27</v>
@@ -2456,10 +2756,10 @@
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>26</v>
@@ -2474,7 +2774,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S37" s="9">
         <v>620</v>
@@ -2497,10 +2797,10 @@
         <v>46100</v>
       </c>
       <c r="F38" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G38" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>27</v>
@@ -2556,10 +2856,10 @@
         <v>46112</v>
       </c>
       <c r="F39" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>27</v>
@@ -2615,10 +2915,10 @@
         <v>46119</v>
       </c>
       <c r="F40" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
@@ -2674,10 +2974,10 @@
         <v>46122</v>
       </c>
       <c r="F41" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>27</v>
@@ -2710,7 +3010,7 @@
         <v>30</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S41" s="9">
         <v>650</v>
@@ -2733,10 +3033,10 @@
         <v>46119</v>
       </c>
       <c r="F42" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G42" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>27</v>
@@ -2769,7 +3069,7 @@
         <v>30</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S42" s="9">
         <v>680</v>
@@ -2792,10 +3092,10 @@
         <v>46141</v>
       </c>
       <c r="F43" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G43" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>27</v>
@@ -2828,7 +3128,7 @@
         <v>30</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S43" s="9">
         <v>680</v>
@@ -2848,13 +3148,13 @@
         <v>46139</v>
       </c>
       <c r="E44" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F44" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>27</v>
@@ -2869,10 +3169,10 @@
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>26</v>
@@ -2907,13 +3207,13 @@
         <v>46139</v>
       </c>
       <c r="E45" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F45" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G45" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>27</v>
@@ -2922,16 +3222,16 @@
         <v>27</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>26</v>
@@ -2969,10 +3269,10 @@
         <v>46119</v>
       </c>
       <c r="F46" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G46" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>27</v>
@@ -3028,10 +3328,10 @@
         <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>27</v>
@@ -3064,7 +3364,7 @@
         <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S47" s="9">
         <v>104.04</v>
@@ -3087,10 +3387,10 @@
         <v>23</v>
       </c>
       <c r="F48" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>27</v>
@@ -3146,10 +3446,10 @@
         <v>23</v>
       </c>
       <c r="F49" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>27</v>
@@ -3205,10 +3505,10 @@
         <v>23</v>
       </c>
       <c r="F50" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G50" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>27</v>
@@ -3264,10 +3564,10 @@
         <v>23</v>
       </c>
       <c r="F51" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G51" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>27</v>
@@ -3300,7 +3600,7 @@
         <v>23</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S51" s="9">
         <v>350</v>
@@ -3323,10 +3623,10 @@
         <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G52" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
@@ -3359,7 +3659,7 @@
         <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S52" s="9">
         <v>408.24</v>
@@ -3382,10 +3682,10 @@
         <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G53" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>27</v>
@@ -3400,7 +3700,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3441,10 +3741,10 @@
         <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="G54" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>27</v>
@@ -3477,7 +3777,7 @@
         <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S54" s="9">
         <v>590</v>
@@ -3500,10 +3800,10 @@
         <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-38</v>
+        <v>-42</v>
       </c>
       <c r="G55" s="8">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>24</v>
@@ -3518,7 +3818,7 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3559,10 +3859,10 @@
         <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G56" s="8">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>27</v>
@@ -3577,7 +3877,7 @@
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3618,10 +3918,10 @@
         <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G57" s="8">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>27</v>
@@ -3677,16 +3977,16 @@
         <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G58" s="8">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>23</v>
@@ -3701,10 +4001,10 @@
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -3720,62 +4020,5549 @@
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
-      <c r="A59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R59" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S59" s="13">
-        <f>SUM(S6:S58)</f>
+      <c r="A59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D59" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F59" s="8">
+        <v>4</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="S59" s="9">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="60" ht="23" customHeight="1">
+      <c r="A60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46111</v>
+      </c>
+      <c r="D60" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="8">
+        <v>-35</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S60" s="9">
+        <v>104.67</v>
+      </c>
+    </row>
+    <row r="61" ht="23" customHeight="1">
+      <c r="A61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D61" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S61" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="62" ht="23" customHeight="1">
+      <c r="A62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D62" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F62" s="8">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S62" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63" ht="23" customHeight="1">
+      <c r="A63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D63" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F63" s="8">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S63" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="64" ht="23" customHeight="1">
+      <c r="A64" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C64" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D64" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S64" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="65" ht="23" customHeight="1">
+      <c r="A65" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C65" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46111</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46118</v>
+      </c>
+      <c r="F65" s="8">
+        <v>-35</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S65" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="66" ht="23" customHeight="1">
+      <c r="A66" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D66" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F66" s="8">
+        <v>0</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S66" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="67" ht="23" customHeight="1">
+      <c r="A67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0</v>
+      </c>
+      <c r="G67" s="8">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S67" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="68" ht="23" customHeight="1">
+      <c r="A68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C68" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F68" s="8">
+        <v>0</v>
+      </c>
+      <c r="G68" s="8">
+        <v>0</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S68" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="69" ht="23" customHeight="1">
+      <c r="A69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O69" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q69" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S69" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="70" ht="23" customHeight="1">
+      <c r="A70" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F70" s="8">
+        <v>0</v>
+      </c>
+      <c r="G70" s="8">
+        <v>0</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q70" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S70" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="71" ht="23" customHeight="1">
+      <c r="A71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F71" s="8">
+        <v>0</v>
+      </c>
+      <c r="G71" s="8">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O71" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q71" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S71" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="72" ht="23" customHeight="1">
+      <c r="A72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C72" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D72" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F72" s="8">
+        <v>0</v>
+      </c>
+      <c r="G72" s="8">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S72" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="73" ht="23" customHeight="1">
+      <c r="A73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C73" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D73" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46100</v>
+      </c>
+      <c r="F73" s="8">
+        <v>0</v>
+      </c>
+      <c r="G73" s="8">
+        <v>0</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O73" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q73" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S73" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="74" ht="23" customHeight="1">
+      <c r="A74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C74" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46100</v>
+      </c>
+      <c r="F74" s="8">
+        <v>0</v>
+      </c>
+      <c r="G74" s="8">
+        <v>0</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q74" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S74" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="75" ht="23" customHeight="1">
+      <c r="A75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46101</v>
+      </c>
+      <c r="F75" s="8">
+        <v>0</v>
+      </c>
+      <c r="G75" s="8">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q75" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S75" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="76" ht="23" customHeight="1">
+      <c r="A76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F76" s="8">
+        <v>0</v>
+      </c>
+      <c r="G76" s="8">
+        <v>0</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q76" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S76" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="77" ht="23" customHeight="1">
+      <c r="A77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C77" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F77" s="8">
+        <v>0</v>
+      </c>
+      <c r="G77" s="8">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O77" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q77" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S77" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="78" ht="23" customHeight="1">
+      <c r="A78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F78" s="8">
+        <v>0</v>
+      </c>
+      <c r="G78" s="8">
+        <v>0</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S78" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="79" ht="23" customHeight="1">
+      <c r="A79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F79" s="8">
+        <v>0</v>
+      </c>
+      <c r="G79" s="8">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S79" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="80" ht="23" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F80" s="8">
+        <v>0</v>
+      </c>
+      <c r="G80" s="8">
+        <v>0</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S80" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="81" ht="23" customHeight="1">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46100</v>
+      </c>
+      <c r="F81" s="8">
+        <v>0</v>
+      </c>
+      <c r="G81" s="8">
+        <v>0</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S81" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="82" ht="23" customHeight="1">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F82" s="8">
+        <v>0</v>
+      </c>
+      <c r="G82" s="8">
+        <v>0</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S82" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="83" ht="23" customHeight="1">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F83" s="8">
+        <v>0</v>
+      </c>
+      <c r="G83" s="8">
+        <v>0</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S83" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F84" s="8">
+        <v>0</v>
+      </c>
+      <c r="G84" s="8">
+        <v>0</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S84" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46132</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F85" s="8">
+        <v>-14</v>
+      </c>
+      <c r="G85" s="8">
+        <v>0</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S85" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="86" ht="23" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F86" s="8">
+        <v>0</v>
+      </c>
+      <c r="G86" s="8">
+        <v>0</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S86" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F87" s="8">
+        <v>0</v>
+      </c>
+      <c r="G87" s="8">
+        <v>0</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S87" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46146</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46146</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46146</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F88" s="8">
+        <v>0</v>
+      </c>
+      <c r="G88" s="8">
+        <v>0</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S88" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="89" ht="23" customHeight="1">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F89" s="8">
+        <v>7</v>
+      </c>
+      <c r="G89" s="8">
+        <v>7</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S89" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="90" ht="23" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F90" s="8">
+        <v>7</v>
+      </c>
+      <c r="G90" s="8">
+        <v>7</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S90" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="91" ht="23" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F91" s="8">
+        <v>7</v>
+      </c>
+      <c r="G91" s="8">
+        <v>7</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S91" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="92" ht="23" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F92" s="8">
+        <v>7</v>
+      </c>
+      <c r="G92" s="8">
+        <v>7</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S92" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E93" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F93" s="8">
+        <v>7</v>
+      </c>
+      <c r="G93" s="8">
+        <v>7</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S93" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="94" ht="23" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F94" s="8">
+        <v>7</v>
+      </c>
+      <c r="G94" s="8">
+        <v>7</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S94" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="95" ht="23" customHeight="1">
+      <c r="A95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C95" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D95" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E95" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F95" s="8">
+        <v>7</v>
+      </c>
+      <c r="G95" s="8">
+        <v>7</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S95" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="96" ht="23" customHeight="1">
+      <c r="A96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C96" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D96" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E96" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F96" s="8">
+        <v>7</v>
+      </c>
+      <c r="G96" s="8">
+        <v>7</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S96" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="97" ht="23" customHeight="1">
+      <c r="A97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C97" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D97" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F97" s="8">
+        <v>7</v>
+      </c>
+      <c r="G97" s="8">
+        <v>7</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S97" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="98" ht="23" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C98" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D98" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E98" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F98" s="8">
+        <v>7</v>
+      </c>
+      <c r="G98" s="8">
+        <v>7</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S98" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="99" ht="23" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C99" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D99" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E99" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F99" s="8">
+        <v>7</v>
+      </c>
+      <c r="G99" s="8">
+        <v>7</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q99" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S99" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="100" ht="23" customHeight="1">
+      <c r="A100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C100" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D100" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E100" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F100" s="8">
+        <v>7</v>
+      </c>
+      <c r="G100" s="8">
+        <v>7</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S100" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="101" ht="23" customHeight="1">
+      <c r="A101" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B101" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C101" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D101" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E101" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F101" s="8">
+        <v>7</v>
+      </c>
+      <c r="G101" s="8">
+        <v>7</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N101" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S101" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="102" ht="23" customHeight="1">
+      <c r="A102" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C102" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D102" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E102" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F102" s="8">
+        <v>7</v>
+      </c>
+      <c r="G102" s="8">
+        <v>7</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q102" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S102" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="103" ht="23" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C103" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D103" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E103" s="7">
+        <v>46101</v>
+      </c>
+      <c r="F103" s="8">
+        <v>7</v>
+      </c>
+      <c r="G103" s="8">
+        <v>7</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N103" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S103" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="104" ht="23" customHeight="1">
+      <c r="A104" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C104" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D104" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E104" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F104" s="8">
+        <v>7</v>
+      </c>
+      <c r="G104" s="8">
+        <v>7</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S104" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="105" ht="23" customHeight="1">
+      <c r="A105" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C105" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D105" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E105" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F105" s="8">
+        <v>7</v>
+      </c>
+      <c r="G105" s="8">
+        <v>7</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N105" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O105" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S105" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="106" ht="23" customHeight="1">
+      <c r="A106" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C106" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D106" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E106" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F106" s="8">
+        <v>7</v>
+      </c>
+      <c r="G106" s="8">
+        <v>7</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q106" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R106" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S106" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="107" ht="23" customHeight="1">
+      <c r="A107" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C107" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D107" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E107" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F107" s="8">
+        <v>7</v>
+      </c>
+      <c r="G107" s="8">
+        <v>7</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N107" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O107" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P107" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q107" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R107" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S107" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="108" ht="23" customHeight="1">
+      <c r="A108" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C108" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D108" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E108" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F108" s="8">
+        <v>7</v>
+      </c>
+      <c r="G108" s="8">
+        <v>7</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q108" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R108" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S108" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="109" ht="23" customHeight="1">
+      <c r="A109" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C109" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D109" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E109" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F109" s="8">
+        <v>7</v>
+      </c>
+      <c r="G109" s="8">
+        <v>7</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N109" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O109" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q109" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R109" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S109" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="110" ht="23" customHeight="1">
+      <c r="A110" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C110" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D110" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E110" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F110" s="8">
+        <v>7</v>
+      </c>
+      <c r="G110" s="8">
+        <v>7</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q110" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R110" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S110" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="111" ht="23" customHeight="1">
+      <c r="A111" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C111" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D111" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E111" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F111" s="8">
+        <v>7</v>
+      </c>
+      <c r="G111" s="8">
+        <v>7</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="K111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N111" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O111" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q111" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R111" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S111" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="112" ht="23" customHeight="1">
+      <c r="A112" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C112" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D112" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E112" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F112" s="8">
+        <v>14</v>
+      </c>
+      <c r="G112" s="8">
+        <v>14</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J112" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K112" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P112" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q112" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R112" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S112" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="113" ht="23" customHeight="1">
+      <c r="A113" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C113" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D113" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E113" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F113" s="8">
+        <v>14</v>
+      </c>
+      <c r="G113" s="8">
+        <v>14</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K113" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M113" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N113" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O113" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P113" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q113" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R113" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S113" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="114" ht="23" customHeight="1">
+      <c r="A114" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C114" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D114" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E114" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F114" s="8">
+        <v>14</v>
+      </c>
+      <c r="G114" s="8">
+        <v>14</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q114" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R114" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S114" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="115" ht="23" customHeight="1">
+      <c r="A115" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C115" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D115" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E115" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F115" s="8">
+        <v>14</v>
+      </c>
+      <c r="G115" s="8">
+        <v>14</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M115" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="N115" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O115" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q115" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S115" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="116" ht="23" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C116" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D116" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E116" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F116" s="8">
+        <v>14</v>
+      </c>
+      <c r="G116" s="8">
+        <v>14</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q116" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R116" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S116" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="117" ht="23" customHeight="1">
+      <c r="A117" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B117" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C117" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D117" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E117" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F117" s="8">
+        <v>14</v>
+      </c>
+      <c r="G117" s="8">
+        <v>14</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M117" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N117" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O117" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q117" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R117" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S117" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="118" ht="23" customHeight="1">
+      <c r="A118" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C118" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D118" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E118" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F118" s="8">
+        <v>14</v>
+      </c>
+      <c r="G118" s="8">
+        <v>14</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K118" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M118" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q118" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R118" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S118" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="119" ht="23" customHeight="1">
+      <c r="A119" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C119" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D119" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E119" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F119" s="8">
+        <v>14</v>
+      </c>
+      <c r="G119" s="8">
+        <v>14</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="K119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L119" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N119" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O119" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P119" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q119" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R119" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S119" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="120" ht="23" customHeight="1">
+      <c r="A120" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C120" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D120" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E120" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F120" s="8">
+        <v>14</v>
+      </c>
+      <c r="G120" s="8">
+        <v>14</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L120" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q120" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R120" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S120" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="121" ht="23" customHeight="1">
+      <c r="A121" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B121" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C121" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D121" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E121" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F121" s="8">
+        <v>14</v>
+      </c>
+      <c r="G121" s="8">
+        <v>14</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J121" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L121" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N121" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O121" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q121" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R121" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S121" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="122" ht="23" customHeight="1">
+      <c r="A122" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B122" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C122" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D122" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E122" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F122" s="8">
+        <v>14</v>
+      </c>
+      <c r="G122" s="8">
+        <v>14</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I122" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J122" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K122" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N122" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P122" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R122" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S122" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="123" ht="23" customHeight="1">
+      <c r="A123" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C123" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D123" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E123" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F123" s="8">
+        <v>14</v>
+      </c>
+      <c r="G123" s="8">
+        <v>14</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="K123" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M123" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N123" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O123" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P123" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q123" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R123" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S123" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="124" ht="23" customHeight="1">
+      <c r="A124" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B124" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C124" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D124" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E124" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F124" s="8">
+        <v>14</v>
+      </c>
+      <c r="G124" s="8">
+        <v>14</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="K124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P124" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q124" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R124" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S124" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="125" ht="23" customHeight="1">
+      <c r="A125" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C125" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D125" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E125" s="7">
+        <v>46101</v>
+      </c>
+      <c r="F125" s="8">
+        <v>14</v>
+      </c>
+      <c r="G125" s="8">
+        <v>14</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N125" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O125" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q125" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R125" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S125" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="126" ht="23" customHeight="1">
+      <c r="A126" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B126" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C126" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D126" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E126" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F126" s="8">
+        <v>14</v>
+      </c>
+      <c r="G126" s="8">
+        <v>14</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I126" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J126" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K126" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N126" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P126" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q126" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R126" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S126" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="127" ht="23" customHeight="1">
+      <c r="A127" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C127" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D127" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E127" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F127" s="8">
+        <v>14</v>
+      </c>
+      <c r="G127" s="8">
+        <v>14</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="K127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N127" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O127" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q127" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R127" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S127" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="128" ht="23" customHeight="1">
+      <c r="A128" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B128" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C128" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D128" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E128" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F128" s="8">
+        <v>14</v>
+      </c>
+      <c r="G128" s="8">
+        <v>14</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K128" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N128" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O128" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P128" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q128" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R128" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S128" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="129" ht="23" customHeight="1">
+      <c r="A129" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C129" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D129" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E129" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F129" s="8">
+        <v>14</v>
+      </c>
+      <c r="G129" s="8">
+        <v>14</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="K129" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M129" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N129" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O129" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P129" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q129" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R129" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S129" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="130" ht="23" customHeight="1">
+      <c r="A130" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C130" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D130" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E130" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F130" s="8">
+        <v>14</v>
+      </c>
+      <c r="G130" s="8">
+        <v>14</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J130" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K130" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M130" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N130" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O130" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P130" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q130" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R130" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S130" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="131" ht="23" customHeight="1">
+      <c r="A131" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B131" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C131" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D131" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E131" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F131" s="8">
+        <v>14</v>
+      </c>
+      <c r="G131" s="8">
+        <v>14</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N131" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O131" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q131" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R131" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S131" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="132" ht="23" customHeight="1">
+      <c r="A132" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C132" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D132" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E132" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F132" s="8">
+        <v>14</v>
+      </c>
+      <c r="G132" s="8">
+        <v>14</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J132" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K132" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M132" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N132" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P132" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q132" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R132" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S132" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="133" ht="23" customHeight="1">
+      <c r="A133" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B133" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C133" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D133" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E133" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F133" s="8">
+        <v>14</v>
+      </c>
+      <c r="G133" s="8">
+        <v>14</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L133" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N133" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O133" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q133" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R133" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S133" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="134" ht="23" customHeight="1">
+      <c r="A134" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C134" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D134" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E134" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F134" s="8">
+        <v>14</v>
+      </c>
+      <c r="G134" s="8">
+        <v>14</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J134" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K134" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L134" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M134" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N134" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O134" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P134" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q134" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R134" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S134" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="135" ht="23" customHeight="1">
+      <c r="A135" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B135" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C135" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D135" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E135" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F135" s="8">
+        <v>21</v>
+      </c>
+      <c r="G135" s="8">
+        <v>21</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J135" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L135" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N135" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O135" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q135" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R135" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S135" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="136" ht="23" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B136" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C136" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D136" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E136" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F136" s="8">
+        <v>21</v>
+      </c>
+      <c r="G136" s="8">
+        <v>21</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J136" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K136" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M136" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N136" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P136" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q136" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R136" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S136" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="137" ht="23" customHeight="1">
+      <c r="A137" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B137" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C137" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D137" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E137" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F137" s="8">
+        <v>21</v>
+      </c>
+      <c r="G137" s="8">
+        <v>21</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J137" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K137" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L137" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M137" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N137" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O137" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P137" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q137" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R137" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S137" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="138" ht="23" customHeight="1">
+      <c r="A138" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B138" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C138" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D138" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E138" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F138" s="8">
+        <v>21</v>
+      </c>
+      <c r="G138" s="8">
+        <v>21</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I138" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J138" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K138" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L138" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M138" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N138" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O138" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P138" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q138" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R138" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S138" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="139" ht="23" customHeight="1">
+      <c r="A139" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B139" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C139" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D139" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E139" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F139" s="8">
+        <v>21</v>
+      </c>
+      <c r="G139" s="8">
+        <v>21</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J139" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="K139" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L139" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M139" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N139" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O139" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P139" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q139" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R139" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S139" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="140" ht="23" customHeight="1">
+      <c r="A140" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B140" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C140" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D140" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E140" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F140" s="8">
+        <v>21</v>
+      </c>
+      <c r="G140" s="8">
+        <v>21</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I140" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K140" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L140" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M140" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N140" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O140" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P140" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q140" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R140" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S140" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="141" ht="23" customHeight="1">
+      <c r="A141" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C141" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D141" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E141" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F141" s="8">
+        <v>21</v>
+      </c>
+      <c r="G141" s="8">
+        <v>21</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J141" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="K141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L141" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M141" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N141" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O141" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q141" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R141" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S141" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="142" ht="23" customHeight="1">
+      <c r="A142" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B142" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C142" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D142" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E142" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F142" s="8">
+        <v>21</v>
+      </c>
+      <c r="G142" s="8">
+        <v>21</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K142" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L142" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M142" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N142" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O142" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P142" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q142" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R142" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S142" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="143" ht="23" customHeight="1">
+      <c r="A143" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B143" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C143" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D143" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E143" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F143" s="8">
+        <v>21</v>
+      </c>
+      <c r="G143" s="8">
+        <v>21</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="K143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L143" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N143" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O143" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q143" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R143" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S143" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="144" ht="23" customHeight="1">
+      <c r="A144" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B144" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C144" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D144" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E144" s="7">
+        <v>46101</v>
+      </c>
+      <c r="F144" s="8">
+        <v>21</v>
+      </c>
+      <c r="G144" s="8">
+        <v>21</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I144" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J144" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="K144" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L144" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M144" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N144" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O144" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P144" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q144" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R144" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S144" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="145" ht="23" customHeight="1">
+      <c r="A145" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B145" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C145" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D145" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E145" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F145" s="8">
+        <v>21</v>
+      </c>
+      <c r="G145" s="8">
+        <v>21</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="K145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L145" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N145" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O145" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q145" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R145" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S145" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="146" ht="23" customHeight="1">
+      <c r="A146" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B146" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C146" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D146" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E146" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F146" s="8">
+        <v>21</v>
+      </c>
+      <c r="G146" s="8">
+        <v>21</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I146" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J146" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K146" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L146" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M146" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N146" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O146" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P146" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q146" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R146" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S146" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="147" ht="23" customHeight="1">
+      <c r="A147" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B147" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C147" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D147" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E147" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F147" s="8">
+        <v>21</v>
+      </c>
+      <c r="G147" s="8">
+        <v>21</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I147" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J147" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="K147" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L147" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M147" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N147" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O147" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P147" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q147" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R147" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S147" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="148" ht="23" customHeight="1">
+      <c r="A148" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B148" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C148" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D148" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E148" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F148" s="8">
+        <v>21</v>
+      </c>
+      <c r="G148" s="8">
+        <v>21</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I148" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K148" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L148" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M148" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N148" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O148" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P148" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q148" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R148" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S148" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="149" ht="23" customHeight="1">
+      <c r="A149" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B149" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C149" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D149" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E149" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F149" s="8">
+        <v>21</v>
+      </c>
+      <c r="G149" s="8">
+        <v>21</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J149" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L149" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N149" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O149" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P149" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q149" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R149" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S149" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="150" ht="23" customHeight="1">
+      <c r="A150" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B150" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C150" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D150" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E150" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F150" s="8">
+        <v>21</v>
+      </c>
+      <c r="G150" s="8">
+        <v>21</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J150" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="K150" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L150" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M150" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N150" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O150" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P150" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q150" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R150" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S150" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="151" ht="23" customHeight="1">
+      <c r="A151" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B151" s="7">
+        <v>46172</v>
+      </c>
+      <c r="C151" s="7">
+        <v>45930</v>
+      </c>
+      <c r="D151" s="7">
+        <v>46172</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F151" s="8">
+        <v>26</v>
+      </c>
+      <c r="G151" s="8">
+        <v>26</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L151" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N151" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O151" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R151" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S151" s="9">
+        <v>185.5</v>
+      </c>
+    </row>
+    <row r="152" ht="23" customHeight="1">
+      <c r="A152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G152" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R152" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S152" s="13">
+        <f>SUM(S6:S151)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$73</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 06/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em terça-feira, 5 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quarta-feira, 6 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -235,24 +235,24 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
+    <t>FA-11408</t>
+  </si>
+  <si>
+    <t>FA-11463</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11551</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11459</t>
   </si>
   <si>
-    <t>FA-11551</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11408</t>
-  </si>
-  <si>
-    <t>FA-11463</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
     <t>FA-11461</t>
   </si>
   <si>
@@ -337,49 +337,55 @@
     <t>JOZILDO TARQUINO DE BRITO</t>
   </si>
   <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
     <t>FA-11519</t>
   </si>
   <si>
-    <t>FA-11464</t>
+    <t>FA-11416</t>
   </si>
   <si>
     <t>FA-11555</t>
   </si>
   <si>
-    <t>FA-11416</t>
+    <t>FA-11467</t>
   </si>
   <si>
     <t>FA-11553</t>
   </si>
   <si>
-    <t>FA-11467</t>
+    <t>FA-11490</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11520</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11394</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
     <t>FA-11396</t>
   </si>
   <si>
-    <t>FA-11394</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
     <t>FA-11354</t>
   </si>
   <si>
     <t>FA-11355</t>
   </si>
   <si>
-    <t>FA-11520</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11490</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
+    <t>FA-11370</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
   </si>
   <si>
     <t>FA-11501</t>
@@ -391,18 +397,21 @@
     <t>FA-11466</t>
   </si>
   <si>
-    <t>FA-11370</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
     <t>FA-11424</t>
   </si>
   <si>
     <t>OLIZIEL DA SILVA CARDOSO</t>
   </si>
   <si>
+    <t>FA-11409</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>FA-11469</t>
+  </si>
+  <si>
     <t>FA-11554</t>
   </si>
   <si>
@@ -412,13 +421,10 @@
     <t>FA-11465</t>
   </si>
   <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>FA-11409</t>
-  </si>
-  <si>
-    <t>FA-11469</t>
+    <t>FA-11326</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
   </si>
   <si>
     <t>FA-11468</t>
@@ -430,196 +436,7 @@
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11326</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
     <t>FA-11277</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11397</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>FA-11492</t>
-  </si>
-  <si>
-    <t>FA-11523</t>
-  </si>
-  <si>
-    <t>FA-11398</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FA-11371</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11502</t>
-  </si>
-  <si>
-    <t>FA-11432</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>FA-11327</t>
-  </si>
-  <si>
-    <t>FA-11267</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11372</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FA-11433</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FA-11268</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11563</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>FA-11494</t>
-  </si>
-  <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FA-11373</t>
-  </si>
-  <si>
-    <t>FA-11434</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>FA-11329</t>
   </si>
 </sst>
 </file>
@@ -762,7 +579,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S142"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -879,10 +696,10 @@
         <v>46086</v>
       </c>
       <c r="F6" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="G6" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -938,10 +755,10 @@
         <v>46113</v>
       </c>
       <c r="F7" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G7" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
@@ -997,10 +814,10 @@
         <v>25</v>
       </c>
       <c r="F8" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="G8" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>23</v>
@@ -1056,10 +873,10 @@
         <v>46086</v>
       </c>
       <c r="F9" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G9" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>23</v>
@@ -1115,10 +932,10 @@
         <v>46119</v>
       </c>
       <c r="F10" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G10" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>23</v>
@@ -1174,10 +991,10 @@
         <v>46087</v>
       </c>
       <c r="F11" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G11" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -1233,10 +1050,10 @@
         <v>46113</v>
       </c>
       <c r="F12" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G12" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>23</v>
@@ -1292,10 +1109,10 @@
         <v>46127</v>
       </c>
       <c r="F13" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G13" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>23</v>
@@ -1351,10 +1168,10 @@
         <v>25</v>
       </c>
       <c r="F14" s="8">
+        <v>-16</v>
+      </c>
+      <c r="G14" s="8">
         <v>-15</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-14</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>23</v>
@@ -1410,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="F15" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="G15" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>45</v>
@@ -1469,10 +1286,10 @@
         <v>25</v>
       </c>
       <c r="F16" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G16" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>23</v>
@@ -1528,10 +1345,10 @@
         <v>25</v>
       </c>
       <c r="F17" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G17" s="8">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>23</v>
@@ -1587,10 +1404,10 @@
         <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="G18" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>45</v>
@@ -1646,10 +1463,10 @@
         <v>25</v>
       </c>
       <c r="F19" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G19" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>23</v>
@@ -1705,10 +1522,10 @@
         <v>46127</v>
       </c>
       <c r="F20" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G20" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>23</v>
@@ -1764,10 +1581,10 @@
         <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G21" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>23</v>
@@ -1823,10 +1640,10 @@
         <v>25</v>
       </c>
       <c r="F22" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G22" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>23</v>
@@ -1882,10 +1699,10 @@
         <v>25</v>
       </c>
       <c r="F23" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G23" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>23</v>
@@ -1941,10 +1758,10 @@
         <v>46127</v>
       </c>
       <c r="F24" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G24" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>23</v>
@@ -2000,10 +1817,10 @@
         <v>46141</v>
       </c>
       <c r="F25" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>23</v>
@@ -2059,10 +1876,10 @@
         <v>46141</v>
       </c>
       <c r="F26" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G26" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>23</v>
@@ -2118,10 +1935,10 @@
         <v>46119</v>
       </c>
       <c r="F27" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>23</v>
@@ -2177,10 +1994,10 @@
         <v>46112</v>
       </c>
       <c r="F28" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>23</v>
@@ -2236,10 +2053,10 @@
         <v>46122</v>
       </c>
       <c r="F29" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G29" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>23</v>
@@ -2292,13 +2109,13 @@
         <v>46139</v>
       </c>
       <c r="E30" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F30" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>23</v>
@@ -2313,10 +2130,10 @@
         <v>25</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2331,7 +2148,7 @@
         <v>28</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S30" s="9">
         <v>680</v>
@@ -2351,13 +2168,13 @@
         <v>46139</v>
       </c>
       <c r="E31" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F31" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G31" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>23</v>
@@ -2390,7 +2207,7 @@
         <v>28</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S31" s="9">
         <v>680</v>
@@ -2410,13 +2227,13 @@
         <v>46139</v>
       </c>
       <c r="E32" s="7">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="F32" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G32" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>23</v>
@@ -2431,10 +2248,10 @@
         <v>25</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2449,7 +2266,7 @@
         <v>28</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S32" s="9">
         <v>680</v>
@@ -2472,10 +2289,10 @@
         <v>46119</v>
       </c>
       <c r="F33" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G33" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>23</v>
@@ -2484,13 +2301,13 @@
         <v>23</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>25</v>
@@ -2508,7 +2325,7 @@
         <v>28</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S33" s="9">
         <v>680</v>
@@ -2531,10 +2348,10 @@
         <v>46119</v>
       </c>
       <c r="F34" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G34" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>23</v>
@@ -2590,10 +2407,10 @@
         <v>25</v>
       </c>
       <c r="F35" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G35" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>23</v>
@@ -2649,10 +2466,10 @@
         <v>25</v>
       </c>
       <c r="F36" s="8">
+        <v>-9</v>
+      </c>
+      <c r="G36" s="8">
         <v>-8</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-7</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>23</v>
@@ -2708,10 +2525,10 @@
         <v>25</v>
       </c>
       <c r="F37" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>23</v>
@@ -2767,10 +2584,10 @@
         <v>25</v>
       </c>
       <c r="F38" s="8">
+        <v>-9</v>
+      </c>
+      <c r="G38" s="8">
         <v>-8</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-7</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>23</v>
@@ -2826,10 +2643,10 @@
         <v>25</v>
       </c>
       <c r="F39" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G39" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>23</v>
@@ -2885,10 +2702,10 @@
         <v>25</v>
       </c>
       <c r="F40" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G40" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>23</v>
@@ -2944,10 +2761,10 @@
         <v>25</v>
       </c>
       <c r="F41" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G41" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>23</v>
@@ -3003,10 +2820,10 @@
         <v>25</v>
       </c>
       <c r="F42" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G42" s="8">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>23</v>
@@ -3062,10 +2879,10 @@
         <v>46141</v>
       </c>
       <c r="F43" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -3121,10 +2938,10 @@
         <v>25</v>
       </c>
       <c r="F44" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G44" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>23</v>
@@ -3180,10 +2997,10 @@
         <v>25</v>
       </c>
       <c r="F45" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G45" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>23</v>
@@ -3239,10 +3056,10 @@
         <v>46097</v>
       </c>
       <c r="F46" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G46" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>23</v>
@@ -3298,10 +3115,10 @@
         <v>25</v>
       </c>
       <c r="F47" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G47" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>23</v>
@@ -3357,10 +3174,10 @@
         <v>25</v>
       </c>
       <c r="F48" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G48" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>23</v>
@@ -3416,10 +3233,10 @@
         <v>25</v>
       </c>
       <c r="F49" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G49" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>23</v>
@@ -3475,10 +3292,10 @@
         <v>25</v>
       </c>
       <c r="F50" s="8">
-        <v>-209</v>
+        <v>-210</v>
       </c>
       <c r="G50" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>95</v>
@@ -3534,10 +3351,10 @@
         <v>25</v>
       </c>
       <c r="F51" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G51" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>23</v>
@@ -3593,10 +3410,10 @@
         <v>46112</v>
       </c>
       <c r="F52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>23</v>
@@ -3649,13 +3466,13 @@
         <v>46146</v>
       </c>
       <c r="E53" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>23</v>
@@ -3670,10 +3487,10 @@
         <v>25</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>27</v>
@@ -3708,13 +3525,13 @@
         <v>46146</v>
       </c>
       <c r="E54" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>23</v>
@@ -3729,10 +3546,10 @@
         <v>25</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>27</v>
@@ -3764,19 +3581,19 @@
         <v>46146</v>
       </c>
       <c r="D55" s="7">
-        <v>46146</v>
+        <v>46111</v>
       </c>
       <c r="E55" s="7">
-        <v>46141</v>
+        <v>46118</v>
       </c>
       <c r="F55" s="8">
-        <v>-1</v>
+        <v>-37</v>
       </c>
       <c r="G55" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>23</v>
@@ -3788,10 +3605,10 @@
         <v>25</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N55" s="6" t="s">
         <v>27</v>
@@ -3823,19 +3640,19 @@
         <v>46146</v>
       </c>
       <c r="D56" s="7">
-        <v>46111</v>
+        <v>46146</v>
       </c>
       <c r="E56" s="7">
-        <v>46118</v>
+        <v>46141</v>
       </c>
       <c r="F56" s="8">
-        <v>-36</v>
+        <v>-2</v>
       </c>
       <c r="G56" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>23</v>
@@ -3847,10 +3664,10 @@
         <v>25</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>27</v>
@@ -3885,13 +3702,13 @@
         <v>46146</v>
       </c>
       <c r="E57" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F57" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G57" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>23</v>
@@ -3906,10 +3723,10 @@
         <v>25</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3924,7 +3741,7 @@
         <v>28</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S57" s="9">
         <v>620</v>
@@ -3944,13 +3761,13 @@
         <v>46146</v>
       </c>
       <c r="E58" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F58" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G58" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3965,10 +3782,10 @@
         <v>25</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3983,7 +3800,7 @@
         <v>28</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S58" s="9">
         <v>620</v>
@@ -4003,13 +3820,13 @@
         <v>46146</v>
       </c>
       <c r="E59" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G59" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -4024,7 +3841,7 @@
         <v>25</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>25</v>
@@ -4036,7 +3853,7 @@
         <v>27</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>28</v>
@@ -4062,13 +3879,13 @@
         <v>46146</v>
       </c>
       <c r="E60" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F60" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G60" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -4077,13 +3894,13 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>25</v>
@@ -4121,13 +3938,13 @@
         <v>46146</v>
       </c>
       <c r="E61" s="7">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="F61" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G61" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -4136,13 +3953,13 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>25</v>
@@ -4180,13 +3997,13 @@
         <v>46146</v>
       </c>
       <c r="E62" s="7">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="F62" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G62" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4195,13 +4012,13 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>25</v>
@@ -4239,13 +4056,13 @@
         <v>46146</v>
       </c>
       <c r="E63" s="7">
-        <v>46127</v>
+        <v>46100</v>
       </c>
       <c r="F63" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G63" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4254,13 +4071,13 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>25</v>
@@ -4298,13 +4115,13 @@
         <v>46146</v>
       </c>
       <c r="E64" s="7">
-        <v>46119</v>
+        <v>46100</v>
       </c>
       <c r="F64" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G64" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4313,13 +4130,13 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>25</v>
@@ -4331,7 +4148,7 @@
         <v>27</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>28</v>
@@ -4357,13 +4174,13 @@
         <v>46146</v>
       </c>
       <c r="E65" s="7">
-        <v>46127</v>
+        <v>46101</v>
       </c>
       <c r="F65" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G65" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4416,13 +4233,13 @@
         <v>46146</v>
       </c>
       <c r="E66" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F66" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G66" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4437,10 +4254,10 @@
         <v>25</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="N66" s="6" t="s">
         <v>27</v>
@@ -4475,13 +4292,13 @@
         <v>46146</v>
       </c>
       <c r="E67" s="7">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="F67" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G67" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4490,16 +4307,16 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>27</v>
@@ -4537,10 +4354,10 @@
         <v>25</v>
       </c>
       <c r="F68" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G68" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4593,13 +4410,13 @@
         <v>46146</v>
       </c>
       <c r="E69" s="7">
-        <v>46141</v>
+        <v>46113</v>
       </c>
       <c r="F69" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G69" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4614,10 +4431,10 @@
         <v>25</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N69" s="6" t="s">
         <v>27</v>
@@ -4632,7 +4449,7 @@
         <v>28</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S69" s="9">
         <v>680</v>
@@ -4649,16 +4466,16 @@
         <v>46146</v>
       </c>
       <c r="D70" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E70" s="7">
-        <v>46119</v>
+        <v>46100</v>
       </c>
       <c r="F70" s="8">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="G70" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4673,7 +4490,7 @@
         <v>25</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>25</v>
@@ -4691,7 +4508,7 @@
         <v>28</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S70" s="9">
         <v>680</v>
@@ -4714,10 +4531,10 @@
         <v>46119</v>
       </c>
       <c r="F71" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G71" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4732,7 +4549,7 @@
         <v>25</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>25</v>
@@ -4750,7 +4567,7 @@
         <v>28</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S71" s="9">
         <v>680</v>
@@ -4770,13 +4587,13 @@
         <v>46146</v>
       </c>
       <c r="E72" s="7">
-        <v>46100</v>
+        <v>46141</v>
       </c>
       <c r="F72" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G72" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4791,7 +4608,7 @@
         <v>25</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>25</v>
@@ -4809,7 +4626,7 @@
         <v>28</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S72" s="9">
         <v>680</v>
@@ -4826,16 +4643,16 @@
         <v>46146</v>
       </c>
       <c r="D73" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E73" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F73" s="8">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="G73" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4850,10 +4667,10 @@
         <v>25</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N73" s="6" t="s">
         <v>27</v>
@@ -4868,7 +4685,7 @@
         <v>28</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S73" s="9">
         <v>680</v>
@@ -4891,10 +4708,10 @@
         <v>46119</v>
       </c>
       <c r="F74" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G74" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4909,7 +4726,7 @@
         <v>25</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>25</v>
@@ -4927,7 +4744,7 @@
         <v>28</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S74" s="9">
         <v>680</v>
@@ -4947,13 +4764,13 @@
         <v>46146</v>
       </c>
       <c r="E75" s="7">
-        <v>46119</v>
+        <v>46099</v>
       </c>
       <c r="F75" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G75" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4968,7 +4785,7 @@
         <v>25</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>25</v>
@@ -4980,13 +4797,13 @@
         <v>27</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>28</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="S75" s="9">
         <v>700</v>
@@ -5006,13 +4823,13 @@
         <v>46146</v>
       </c>
       <c r="E76" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G76" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -5021,13 +4838,13 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>25</v>
@@ -5039,7 +4856,7 @@
         <v>27</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="Q76" s="6" t="s">
         <v>28</v>
@@ -5065,13 +4882,13 @@
         <v>46146</v>
       </c>
       <c r="E77" s="7">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="F77" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G77" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5104,7 +4921,7 @@
         <v>28</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S77" s="9">
         <v>700</v>
@@ -5127,16 +4944,16 @@
         <v>25</v>
       </c>
       <c r="F78" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G78" s="8">
         <v>-1</v>
       </c>
-      <c r="G78" s="8">
-        <v>0</v>
-      </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>134</v>
@@ -5154,7 +4971,7 @@
         <v>27</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>135</v>
+        <v>27</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>25</v>
@@ -5170,3779 +4987,62 @@
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
-      <c r="A79" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C79" s="7">
-        <v>46082</v>
-      </c>
-      <c r="D79" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E79" s="7">
-        <v>46097</v>
-      </c>
-      <c r="F79" s="8">
-        <v>6</v>
-      </c>
-      <c r="G79" s="8">
-        <v>6</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N79" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O79" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q79" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R79" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S79" s="9">
-        <v>146.55</v>
-      </c>
-    </row>
-    <row r="80" ht="23" customHeight="1">
-      <c r="A80" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C80" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D80" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E80" s="7">
-        <v>46112</v>
-      </c>
-      <c r="F80" s="8">
-        <v>6</v>
-      </c>
-      <c r="G80" s="8">
-        <v>6</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q80" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R80" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S80" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="81" ht="23" customHeight="1">
-      <c r="A81" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C81" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D81" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E81" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F81" s="8">
-        <v>6</v>
-      </c>
-      <c r="G81" s="8">
-        <v>6</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L81" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M81" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N81" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O81" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q81" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R81" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S81" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="82" ht="23" customHeight="1">
-      <c r="A82" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B82" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C82" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D82" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E82" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F82" s="8">
-        <v>6</v>
-      </c>
-      <c r="G82" s="8">
-        <v>6</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q82" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R82" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S82" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="83" ht="23" customHeight="1">
-      <c r="A83" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C83" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D83" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E83" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F83" s="8">
-        <v>6</v>
-      </c>
-      <c r="G83" s="8">
-        <v>6</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N83" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O83" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q83" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R83" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S83" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C84" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D84" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F84" s="8">
-        <v>6</v>
-      </c>
-      <c r="G84" s="8">
-        <v>6</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q84" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R84" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S84" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="85" ht="23" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C85" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D85" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F85" s="8">
-        <v>6</v>
-      </c>
-      <c r="G85" s="8">
-        <v>6</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M85" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N85" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q85" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R85" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S85" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="86" ht="23" customHeight="1">
-      <c r="A86" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B86" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C86" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D86" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F86" s="8">
-        <v>6</v>
-      </c>
-      <c r="G86" s="8">
-        <v>6</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q86" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R86" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S86" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="87" ht="23" customHeight="1">
-      <c r="A87" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C87" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D87" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F87" s="8">
-        <v>6</v>
-      </c>
-      <c r="G87" s="8">
-        <v>6</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q87" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S87" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="88" ht="23" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C88" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D88" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E88" s="7">
-        <v>46112</v>
-      </c>
-      <c r="F88" s="8">
-        <v>6</v>
-      </c>
-      <c r="G88" s="8">
-        <v>6</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q88" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S88" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="89" ht="23" customHeight="1">
-      <c r="A89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C89" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D89" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E89" s="7">
-        <v>46112</v>
-      </c>
-      <c r="F89" s="8">
-        <v>6</v>
-      </c>
-      <c r="G89" s="8">
-        <v>6</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q89" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R89" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S89" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="90" ht="23" customHeight="1">
-      <c r="A90" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F90" s="8">
-        <v>6</v>
-      </c>
-      <c r="G90" s="8">
-        <v>6</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q90" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R90" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S90" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="91" ht="23" customHeight="1">
-      <c r="A91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C91" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D91" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E91" s="7">
-        <v>46101</v>
-      </c>
-      <c r="F91" s="8">
-        <v>6</v>
-      </c>
-      <c r="G91" s="8">
-        <v>6</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S91" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="92" ht="23" customHeight="1">
-      <c r="A92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C92" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D92" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E92" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F92" s="8">
-        <v>6</v>
-      </c>
-      <c r="G92" s="8">
-        <v>6</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q92" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R92" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S92" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="93" ht="23" customHeight="1">
-      <c r="A93" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C93" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D93" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E93" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F93" s="8">
-        <v>6</v>
-      </c>
-      <c r="G93" s="8">
-        <v>6</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q93" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R93" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S93" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="94" ht="23" customHeight="1">
-      <c r="A94" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C94" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D94" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E94" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F94" s="8">
-        <v>6</v>
-      </c>
-      <c r="G94" s="8">
-        <v>6</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q94" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R94" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S94" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="95" ht="23" customHeight="1">
-      <c r="A95" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C95" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D95" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E95" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F95" s="8">
-        <v>6</v>
-      </c>
-      <c r="G95" s="8">
-        <v>6</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N95" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q95" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R95" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S95" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="96" ht="23" customHeight="1">
-      <c r="A96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C96" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D96" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E96" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F96" s="8">
-        <v>6</v>
-      </c>
-      <c r="G96" s="8">
-        <v>6</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q96" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R96" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S96" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="97" ht="23" customHeight="1">
-      <c r="A97" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C97" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D97" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E97" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F97" s="8">
-        <v>6</v>
-      </c>
-      <c r="G97" s="8">
-        <v>6</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q97" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R97" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S97" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="98" ht="23" customHeight="1">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C98" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D98" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E98" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F98" s="8">
-        <v>6</v>
-      </c>
-      <c r="G98" s="8">
-        <v>6</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R98" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S98" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="99" ht="23" customHeight="1">
-      <c r="A99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C99" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D99" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E99" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F99" s="8">
-        <v>6</v>
-      </c>
-      <c r="G99" s="8">
-        <v>6</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q99" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R99" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S99" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="100" ht="23" customHeight="1">
-      <c r="A100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C100" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D100" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E100" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F100" s="8">
-        <v>6</v>
-      </c>
-      <c r="G100" s="8">
-        <v>6</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N100" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q100" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R100" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S100" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="101" ht="23" customHeight="1">
-      <c r="A101" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101" s="7">
-        <v>46153</v>
-      </c>
-      <c r="C101" s="7">
-        <v>46153</v>
-      </c>
-      <c r="D101" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E101" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F101" s="8">
-        <v>6</v>
-      </c>
-      <c r="G101" s="8">
-        <v>6</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N101" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O101" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q101" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R101" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S101" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="102" ht="23" customHeight="1">
-      <c r="A102" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B102" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C102" s="7">
-        <v>46082</v>
-      </c>
-      <c r="D102" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E102" s="7">
-        <v>46097</v>
-      </c>
-      <c r="F102" s="8">
-        <v>13</v>
-      </c>
-      <c r="G102" s="8">
-        <v>13</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M102" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N102" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q102" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R102" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S102" s="9">
-        <v>146.55</v>
-      </c>
-    </row>
-    <row r="103" ht="23" customHeight="1">
-      <c r="A103" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C103" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D103" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E103" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F103" s="8">
-        <v>13</v>
-      </c>
-      <c r="G103" s="8">
-        <v>13</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M103" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N103" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O103" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P103" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q103" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R103" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S103" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="104" ht="23" customHeight="1">
-      <c r="A104" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B104" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C104" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D104" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E104" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F104" s="8">
-        <v>13</v>
-      </c>
-      <c r="G104" s="8">
-        <v>13</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="K104" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L104" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M104" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N104" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O104" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q104" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R104" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S104" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="105" ht="23" customHeight="1">
-      <c r="A105" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B105" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C105" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D105" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E105" s="7">
-        <v>46112</v>
-      </c>
-      <c r="F105" s="8">
-        <v>13</v>
-      </c>
-      <c r="G105" s="8">
-        <v>13</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="M105" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="N105" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O105" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q105" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R105" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S105" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="106" ht="23" customHeight="1">
-      <c r="A106" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C106" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D106" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E106" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F106" s="8">
-        <v>13</v>
-      </c>
-      <c r="G106" s="8">
-        <v>13</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L106" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N106" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q106" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R106" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S106" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="107" ht="23" customHeight="1">
-      <c r="A107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C107" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D107" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E107" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F107" s="8">
-        <v>13</v>
-      </c>
-      <c r="G107" s="8">
-        <v>13</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L107" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N107" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q107" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R107" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S107" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="108" ht="23" customHeight="1">
-      <c r="A108" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B108" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C108" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D108" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E108" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F108" s="8">
-        <v>13</v>
-      </c>
-      <c r="G108" s="8">
-        <v>13</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q108" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R108" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S108" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="109" ht="23" customHeight="1">
-      <c r="A109" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B109" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C109" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D109" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E109" s="7">
-        <v>46112</v>
-      </c>
-      <c r="F109" s="8">
-        <v>13</v>
-      </c>
-      <c r="G109" s="8">
-        <v>13</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L109" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N109" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q109" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R109" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S109" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="110" ht="23" customHeight="1">
-      <c r="A110" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B110" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C110" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D110" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E110" s="7">
-        <v>46112</v>
-      </c>
-      <c r="F110" s="8">
-        <v>13</v>
-      </c>
-      <c r="G110" s="8">
-        <v>13</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N110" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q110" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R110" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S110" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="111" ht="23" customHeight="1">
-      <c r="A111" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B111" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C111" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D111" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E111" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F111" s="8">
-        <v>13</v>
-      </c>
-      <c r="G111" s="8">
-        <v>13</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L111" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N111" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q111" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R111" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S111" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="112" ht="23" customHeight="1">
-      <c r="A112" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B112" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C112" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D112" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E112" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F112" s="8">
-        <v>13</v>
-      </c>
-      <c r="G112" s="8">
-        <v>13</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K112" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L112" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M112" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N112" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q112" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R112" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S112" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="113" ht="23" customHeight="1">
-      <c r="A113" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B113" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C113" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D113" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E113" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F113" s="8">
-        <v>13</v>
-      </c>
-      <c r="G113" s="8">
-        <v>13</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L113" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N113" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O113" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q113" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R113" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S113" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="114" ht="23" customHeight="1">
-      <c r="A114" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B114" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C114" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D114" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E114" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F114" s="8">
-        <v>13</v>
-      </c>
-      <c r="G114" s="8">
-        <v>13</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L114" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q114" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S114" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="115" ht="23" customHeight="1">
-      <c r="A115" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B115" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C115" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D115" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E115" s="7">
-        <v>46101</v>
-      </c>
-      <c r="F115" s="8">
-        <v>13</v>
-      </c>
-      <c r="G115" s="8">
-        <v>13</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L115" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N115" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O115" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q115" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S115" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="116" ht="23" customHeight="1">
-      <c r="A116" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B116" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C116" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D116" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E116" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F116" s="8">
-        <v>13</v>
-      </c>
-      <c r="G116" s="8">
-        <v>13</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J116" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L116" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N116" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q116" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R116" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S116" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="117" ht="23" customHeight="1">
-      <c r="A117" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B117" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C117" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D117" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E117" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F117" s="8">
-        <v>13</v>
-      </c>
-      <c r="G117" s="8">
-        <v>13</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L117" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="M117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N117" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O117" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q117" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R117" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S117" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="118" ht="23" customHeight="1">
-      <c r="A118" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B118" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C118" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D118" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E118" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F118" s="8">
-        <v>13</v>
-      </c>
-      <c r="G118" s="8">
-        <v>13</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J118" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L118" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N118" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O118" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q118" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R118" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S118" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="119" ht="23" customHeight="1">
-      <c r="A119" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B119" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C119" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D119" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E119" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F119" s="8">
-        <v>13</v>
-      </c>
-      <c r="G119" s="8">
-        <v>13</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J119" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="K119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L119" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N119" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O119" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q119" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R119" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S119" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="120" ht="23" customHeight="1">
-      <c r="A120" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B120" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C120" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D120" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E120" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F120" s="8">
-        <v>13</v>
-      </c>
-      <c r="G120" s="8">
-        <v>13</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J120" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L120" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N120" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q120" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R120" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S120" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="121" ht="23" customHeight="1">
-      <c r="A121" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B121" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C121" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D121" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E121" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F121" s="8">
-        <v>13</v>
-      </c>
-      <c r="G121" s="8">
-        <v>13</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J121" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="K121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L121" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N121" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O121" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q121" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R121" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S121" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="122" ht="23" customHeight="1">
-      <c r="A122" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B122" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C122" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D122" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E122" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F122" s="8">
-        <v>13</v>
-      </c>
-      <c r="G122" s="8">
-        <v>13</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L122" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="M122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N122" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q122" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R122" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S122" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="123" ht="23" customHeight="1">
-      <c r="A123" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B123" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C123" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D123" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E123" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F123" s="8">
-        <v>13</v>
-      </c>
-      <c r="G123" s="8">
-        <v>13</v>
-      </c>
-      <c r="H123" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J123" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="K123" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L123" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M123" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N123" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O123" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P123" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q123" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R123" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S123" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="124" ht="23" customHeight="1">
-      <c r="A124" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B124" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C124" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D124" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E124" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F124" s="8">
-        <v>13</v>
-      </c>
-      <c r="G124" s="8">
-        <v>13</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J124" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L124" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="M124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N124" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q124" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R124" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S124" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="125" ht="23" customHeight="1">
-      <c r="A125" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C125" s="7">
-        <v>46082</v>
-      </c>
-      <c r="D125" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E125" s="7">
-        <v>46097</v>
-      </c>
-      <c r="F125" s="8">
-        <v>20</v>
-      </c>
-      <c r="G125" s="8">
-        <v>20</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J125" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L125" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N125" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O125" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q125" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="R125" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S125" s="9">
-        <v>146.55</v>
-      </c>
-    </row>
-    <row r="126" ht="23" customHeight="1">
-      <c r="A126" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B126" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C126" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D126" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E126" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F126" s="8">
-        <v>20</v>
-      </c>
-      <c r="G126" s="8">
-        <v>20</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L126" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M126" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N126" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q126" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R126" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S126" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="127" ht="23" customHeight="1">
-      <c r="A127" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B127" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C127" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D127" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E127" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F127" s="8">
-        <v>20</v>
-      </c>
-      <c r="G127" s="8">
-        <v>20</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J127" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="K127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L127" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N127" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O127" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q127" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R127" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S127" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="128" ht="23" customHeight="1">
-      <c r="A128" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B128" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C128" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D128" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E128" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F128" s="8">
-        <v>20</v>
-      </c>
-      <c r="G128" s="8">
-        <v>20</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J128" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K128" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N128" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O128" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q128" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R128" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S128" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="129" ht="23" customHeight="1">
-      <c r="A129" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B129" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C129" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D129" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E129" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F129" s="8">
-        <v>20</v>
-      </c>
-      <c r="G129" s="8">
-        <v>20</v>
-      </c>
-      <c r="H129" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J129" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="K129" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L129" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M129" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N129" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O129" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P129" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q129" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R129" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S129" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="130" ht="23" customHeight="1">
-      <c r="A130" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B130" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C130" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D130" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E130" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F130" s="8">
-        <v>20</v>
-      </c>
-      <c r="G130" s="8">
-        <v>20</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I130" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J130" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="K130" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L130" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="M130" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N130" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O130" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q130" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R130" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S130" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="131" ht="23" customHeight="1">
-      <c r="A131" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B131" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C131" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D131" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E131" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F131" s="8">
-        <v>20</v>
-      </c>
-      <c r="G131" s="8">
-        <v>20</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J131" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="K131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L131" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N131" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O131" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q131" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R131" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S131" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="132" ht="23" customHeight="1">
-      <c r="A132" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B132" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C132" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D132" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E132" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F132" s="8">
-        <v>20</v>
-      </c>
-      <c r="G132" s="8">
-        <v>20</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J132" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="K132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L132" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="M132" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="N132" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O132" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q132" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R132" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S132" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="133" ht="23" customHeight="1">
-      <c r="A133" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B133" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C133" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D133" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E133" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F133" s="8">
-        <v>20</v>
-      </c>
-      <c r="G133" s="8">
-        <v>20</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="K133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L133" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N133" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O133" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q133" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R133" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S133" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="134" ht="23" customHeight="1">
-      <c r="A134" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B134" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C134" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D134" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E134" s="7">
-        <v>46101</v>
-      </c>
-      <c r="F134" s="8">
-        <v>20</v>
-      </c>
-      <c r="G134" s="8">
-        <v>20</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="K134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L134" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N134" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O134" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q134" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R134" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S134" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="135" ht="23" customHeight="1">
-      <c r="A135" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B135" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C135" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D135" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E135" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F135" s="8">
-        <v>20</v>
-      </c>
-      <c r="G135" s="8">
-        <v>20</v>
-      </c>
-      <c r="H135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J135" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="K135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L135" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="M135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N135" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O135" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q135" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R135" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S135" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="136" ht="23" customHeight="1">
-      <c r="A136" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B136" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C136" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D136" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E136" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F136" s="8">
-        <v>20</v>
-      </c>
-      <c r="G136" s="8">
-        <v>20</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J136" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="K136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L136" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M136" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N136" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O136" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q136" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R136" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S136" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="137" ht="23" customHeight="1">
-      <c r="A137" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B137" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C137" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D137" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E137" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F137" s="8">
-        <v>20</v>
-      </c>
-      <c r="G137" s="8">
-        <v>20</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J137" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="K137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L137" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N137" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O137" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q137" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R137" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S137" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="138" ht="23" customHeight="1">
-      <c r="A138" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B138" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C138" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D138" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E138" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F138" s="8">
-        <v>20</v>
-      </c>
-      <c r="G138" s="8">
-        <v>20</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J138" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L138" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N138" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O138" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q138" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R138" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S138" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="139" ht="23" customHeight="1">
-      <c r="A139" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B139" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C139" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D139" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E139" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F139" s="8">
-        <v>20</v>
-      </c>
-      <c r="G139" s="8">
-        <v>20</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J139" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="K139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L139" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N139" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O139" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q139" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R139" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S139" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="140" ht="23" customHeight="1">
-      <c r="A140" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B140" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C140" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D140" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E140" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F140" s="8">
-        <v>20</v>
-      </c>
-      <c r="G140" s="8">
-        <v>20</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J140" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="K140" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L140" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="M140" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N140" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O140" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q140" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R140" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S140" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="141" ht="23" customHeight="1">
-      <c r="A141" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B141" s="7">
-        <v>46172</v>
-      </c>
-      <c r="C141" s="7">
-        <v>45930</v>
-      </c>
-      <c r="D141" s="7">
-        <v>46172</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" s="8">
-        <v>25</v>
-      </c>
-      <c r="G141" s="8">
-        <v>25</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L141" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N141" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O141" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="P141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="S141" s="9">
-        <v>185.5</v>
-      </c>
-    </row>
-    <row r="142" ht="23" customHeight="1">
-      <c r="A142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C142" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D142" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E142" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G142" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="P142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R142" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="S142" s="13">
-        <f>SUM(S6:S141)</f>
+      <c r="A79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="R79" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S79" s="13">
+        <f>SUM(S6:S78)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$131</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 06/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 6 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 7 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -103,340 +103,517 @@
     <t>1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
   </si>
   <si>
+    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+  </si>
+  <si>
+    <t>FA-11240</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>VENCIDO</t>
+  </si>
+  <si>
+    <t>FATURA</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11240</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>VENCIDO</t>
-  </si>
-  <si>
-    <t>FATURA</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t>FA-11406</t>
+    <t>FA-11069</t>
+  </si>
+  <si>
+    <t>ALBERTO MANOEL DOS REIS</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11244</t>
+  </si>
+  <si>
+    <t>FA-11455</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11256</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11514</t>
+  </si>
+  <si>
+    <t>FA-11348</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11183</t>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>ND-11305</t>
+  </si>
+  <si>
+    <t>FA-11456</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11253</t>
+  </si>
+  <si>
+    <t>FA-11387</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11518</t>
+  </si>
+  <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
+    <t>FA-11352</t>
+  </si>
+  <si>
+    <t>FA-11390</t>
+  </si>
+  <si>
+    <t>FA-11516</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11462</t>
+  </si>
+  <si>
+    <t>FA-11550</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11552</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11463</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11459</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FA-11276</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11347</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11446</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>ND-11574</t>
+  </si>
+  <si>
+    <t>REGINALDO BENTO DA SILVA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11410</t>
   </si>
   <si>
     <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
   </si>
   <si>
-    <t>FA-11069</t>
-  </si>
-  <si>
-    <t>ALBERTO MANOEL DOS REIS</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11244</t>
-  </si>
-  <si>
-    <t>FA-11455</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11256</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11407</t>
-  </si>
-  <si>
-    <t>FA-11514</t>
-  </si>
-  <si>
-    <t>FA-11348</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
-  </si>
-  <si>
-    <t>FA-11183</t>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>ND-11305</t>
-  </si>
-  <si>
-    <t>FA-11456</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11253</t>
-  </si>
-  <si>
-    <t>FA-11387</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11518</t>
-  </si>
-  <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
-    <t>FA-11352</t>
-  </si>
-  <si>
-    <t>FA-11390</t>
-  </si>
-  <si>
-    <t>FA-11516</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11550</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11552</t>
-  </si>
-  <si>
-    <t>FA-11462</t>
-  </si>
-  <si>
-    <t>FA-11393</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11408</t>
-  </si>
-  <si>
-    <t>FA-11463</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11551</t>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11115</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11519</t>
+  </si>
+  <si>
+    <t>FA-11467</t>
+  </si>
+  <si>
+    <t>FA-11416</t>
+  </si>
+  <si>
+    <t>FA-11555</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11354</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>FA-11520</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11370</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11554</t>
   </si>
   <si>
     <t>ELSON VIEIRA DA SILVA</t>
   </si>
   <si>
-    <t>FA-11459</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FA-11276</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11347</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>ND-11574</t>
-  </si>
-  <si>
-    <t>REGINALDO BENTO DA SILVA</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11115</t>
-  </si>
-  <si>
-    <t>FA-11395</t>
+    <t>FA-11454</t>
+  </si>
+  <si>
+    <t>FA-11469</t>
+  </si>
+  <si>
+    <t>FA-11465</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11277</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11397</t>
   </si>
   <si>
     <t>JOZILDO TARQUINO DE BRITO</t>
   </si>
   <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11519</t>
-  </si>
-  <si>
-    <t>FA-11416</t>
-  </si>
-  <si>
-    <t>FA-11555</t>
-  </si>
-  <si>
-    <t>FA-11467</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>FA-11490</t>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>FA-11492</t>
   </si>
   <si>
     <t>ROSSILY PEREIRA DA SILVA</t>
   </si>
   <si>
-    <t>FA-11520</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11394</t>
+    <t>FA-11398</t>
   </si>
   <si>
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11354</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>FA-11370</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11501</t>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11502</t>
   </si>
   <si>
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11409</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>FA-11469</t>
-  </si>
-  <si>
-    <t>FA-11554</t>
-  </si>
-  <si>
-    <t>FA-11454</t>
-  </si>
-  <si>
-    <t>FA-11465</t>
-  </si>
-  <si>
-    <t>FA-11326</t>
+    <t>FA-11432</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11327</t>
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11266</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11277</t>
+    <t>FA-11599</t>
+  </si>
+  <si>
+    <t>FA-11575</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11589</t>
+  </si>
+  <si>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
+  </si>
+  <si>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11433</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FA-11268</t>
+  </si>
+  <si>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>FA-11600</t>
+  </si>
+  <si>
+    <t>FA-11590</t>
+  </si>
+  <si>
+    <t>FA-11577</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>FA-11494</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11434</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11329</t>
+  </si>
+  <si>
+    <t>FA-11601</t>
+  </si>
+  <si>
+    <t>FA-11578</t>
+  </si>
+  <si>
+    <t>FA-11591</t>
   </si>
 </sst>
 </file>
@@ -579,7 +756,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -696,10 +873,10 @@
         <v>46086</v>
       </c>
       <c r="F6" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G6" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -743,40 +920,40 @@
         <v>22</v>
       </c>
       <c r="B7" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="C7" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D7" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46113</v>
+        <v>46118</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F7" s="8">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="G7" s="8">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>27</v>
@@ -785,16 +962,16 @@
         <v>27</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S7" s="9">
-        <v>680</v>
+        <v>91.54</v>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
@@ -805,37 +982,37 @@
         <v>46132</v>
       </c>
       <c r="C8" s="7">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="D8" s="7">
-        <v>46118</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
+        <v>46132</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46086</v>
       </c>
       <c r="F8" s="8">
-        <v>-30</v>
+        <v>-17</v>
       </c>
       <c r="G8" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>27</v>
@@ -844,16 +1021,16 @@
         <v>27</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S8" s="9">
-        <v>91.54</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
@@ -870,19 +1047,19 @@
         <v>46132</v>
       </c>
       <c r="E9" s="7">
-        <v>46086</v>
+        <v>46119</v>
       </c>
       <c r="F9" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G9" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>35</v>
@@ -891,10 +1068,10 @@
         <v>25</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>27</v>
@@ -909,7 +1086,7 @@
         <v>28</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S9" s="9">
         <v>620</v>
@@ -929,31 +1106,31 @@
         <v>46132</v>
       </c>
       <c r="E10" s="7">
-        <v>46119</v>
+        <v>46087</v>
       </c>
       <c r="F10" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G10" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N10" s="6" t="s">
         <v>27</v>
@@ -968,10 +1145,10 @@
         <v>28</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S10" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1">
@@ -988,28 +1165,28 @@
         <v>46132</v>
       </c>
       <c r="E11" s="7">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="F11" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G11" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>25</v>
@@ -1021,7 +1198,7 @@
         <v>27</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>28</v>
@@ -1038,7 +1215,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C12" s="7">
         <v>46132</v>
@@ -1046,20 +1223,20 @@
       <c r="D12" s="7">
         <v>46132</v>
       </c>
-      <c r="E12" s="7">
-        <v>46113</v>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F12" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G12" s="8">
         <v>-16</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>41</v>
@@ -1068,10 +1245,10 @@
         <v>25</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>27</v>
@@ -1083,13 +1260,13 @@
         <v>25</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S12" s="9">
-        <v>680</v>
+        <v>107.71</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1097,19 +1274,19 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="C13" s="7">
-        <v>46132</v>
+        <v>46118</v>
       </c>
       <c r="D13" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46127</v>
+        <v>46111</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F13" s="8">
-        <v>-16</v>
+        <v>-38</v>
       </c>
       <c r="G13" s="8">
         <v>-16</v>
@@ -1118,16 +1295,16 @@
         <v>23</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>25</v>
@@ -1139,16 +1316,16 @@
         <v>27</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S13" s="9">
-        <v>680</v>
+        <v>321.17</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1156,31 +1333,31 @@
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="C14" s="7">
-        <v>46132</v>
+        <v>46082</v>
       </c>
       <c r="D14" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="8">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="G14" s="8">
         <v>-15</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>25</v>
@@ -1204,10 +1381,10 @@
         <v>25</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S14" s="9">
-        <v>107.71</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1215,28 +1392,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="C15" s="7">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="D15" s="7">
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="8">
-        <v>-37</v>
+        <v>-17</v>
       </c>
       <c r="G15" s="8">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>46</v>
@@ -1257,16 +1434,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S15" s="9">
-        <v>321.17</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1274,28 +1451,28 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="C16" s="7">
-        <v>46082</v>
+        <v>46111</v>
       </c>
       <c r="D16" s="7">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="8">
-        <v>-23</v>
+        <v>-38</v>
       </c>
       <c r="G16" s="8">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>48</v>
@@ -1304,7 +1481,7 @@
         <v>25</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>25</v>
@@ -1322,10 +1499,10 @@
         <v>25</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S16" s="9">
-        <v>79.05</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1333,28 +1510,28 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="C17" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D17" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="8">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="G17" s="8">
         <v>-13</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>49</v>
@@ -1375,7 +1552,7 @@
         <v>27</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>25</v>
@@ -1384,7 +1561,7 @@
         <v>29</v>
       </c>
       <c r="S17" s="9">
-        <v>650</v>
+        <v>302.72</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1392,28 +1569,28 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C18" s="7">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="D18" s="7">
-        <v>46111</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E18" s="7">
+        <v>46127</v>
       </c>
       <c r="F18" s="8">
-        <v>-37</v>
+        <v>-10</v>
       </c>
       <c r="G18" s="8">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>51</v>
@@ -1422,7 +1599,7 @@
         <v>25</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>25</v>
@@ -1434,16 +1611,16 @@
         <v>27</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S18" s="9">
-        <v>180</v>
+        <v>97.15</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1451,58 +1628,58 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="C19" s="7">
-        <v>46125</v>
+        <v>46082</v>
       </c>
       <c r="D19" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46097</v>
       </c>
       <c r="F19" s="8">
-        <v>-23</v>
+        <v>-10</v>
       </c>
       <c r="G19" s="8">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="R19" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S19" s="9">
-        <v>302.72</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1518,29 +1695,29 @@
       <c r="D20" s="7">
         <v>46139</v>
       </c>
-      <c r="E20" s="7">
-        <v>46127</v>
+      <c r="E20" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F20" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G20" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>25</v>
@@ -1552,16 +1729,16 @@
         <v>27</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>97.15</v>
+        <v>154.92</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1572,34 +1749,34 @@
         <v>46139</v>
       </c>
       <c r="C21" s="7">
-        <v>46082</v>
+        <v>46132</v>
       </c>
       <c r="D21" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46097</v>
+        <v>46132</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F21" s="8">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>25</v>
@@ -1614,13 +1791,13 @@
         <v>25</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S21" s="9">
-        <v>146.55</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1636,32 +1813,32 @@
       <c r="D22" s="7">
         <v>46139</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>25</v>
+      <c r="E22" s="7">
+        <v>46127</v>
       </c>
       <c r="F22" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="M22" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1673,13 +1850,13 @@
         <v>25</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S22" s="9">
-        <v>154.92</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1690,25 +1867,25 @@
         <v>46139</v>
       </c>
       <c r="C23" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="D23" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>25</v>
+        <v>46139</v>
+      </c>
+      <c r="E23" s="7">
+        <v>46119</v>
       </c>
       <c r="F23" s="8">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="G23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>57</v>
@@ -1717,10 +1894,10 @@
         <v>25</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1732,13 +1909,13 @@
         <v>25</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S23" s="9">
-        <v>500</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1755,19 +1932,19 @@
         <v>46139</v>
       </c>
       <c r="E24" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>58</v>
@@ -1779,7 +1956,7 @@
         <v>59</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1797,7 +1974,7 @@
         <v>29</v>
       </c>
       <c r="S24" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1817,16 +1994,16 @@
         <v>46141</v>
       </c>
       <c r="F25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>60</v>
@@ -1835,10 +2012,10 @@
         <v>25</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1870,34 +2047,34 @@
         <v>46139</v>
       </c>
       <c r="D26" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E26" s="7">
-        <v>46141</v>
+        <v>46122</v>
       </c>
       <c r="F26" s="8">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="G26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="M26" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1912,10 +2089,10 @@
         <v>28</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S26" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1935,16 +2112,16 @@
         <v>46119</v>
       </c>
       <c r="F27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>63</v>
@@ -1953,10 +2130,10 @@
         <v>25</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>27</v>
@@ -1971,10 +2148,10 @@
         <v>28</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1991,28 +2168,28 @@
         <v>46139</v>
       </c>
       <c r="E28" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>25</v>
@@ -2030,10 +2207,10 @@
         <v>28</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S28" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2047,31 +2224,31 @@
         <v>46139</v>
       </c>
       <c r="D29" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="7">
-        <v>46122</v>
+        <v>46119</v>
       </c>
       <c r="F29" s="8">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="G29" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>25</v>
@@ -2083,16 +2260,16 @@
         <v>27</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2100,40 +2277,40 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C30" s="7">
-        <v>46139</v>
+        <v>46082</v>
       </c>
       <c r="D30" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E30" s="7">
-        <v>46113</v>
+        <v>46132</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F30" s="8">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="G30" s="8">
         <v>-9</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2145,13 +2322,13 @@
         <v>25</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S30" s="9">
-        <v>680</v>
+        <v>104.04</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2159,7 +2336,7 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C31" s="7">
         <v>46139</v>
@@ -2167,30 +2344,30 @@
       <c r="D31" s="7">
         <v>46139</v>
       </c>
-      <c r="E31" s="7">
-        <v>46119</v>
+      <c r="E31" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F31" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G31" s="8">
         <v>-9</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K31" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="M31" s="6" t="s">
         <v>25</v>
       </c>
@@ -2204,13 +2381,13 @@
         <v>25</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S31" s="9">
-        <v>680</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2218,38 +2395,38 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C32" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D32" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E32" s="7">
-        <v>46141</v>
+        <v>46132</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="G32" s="8">
         <v>-9</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="M32" s="6" t="s">
         <v>25</v>
       </c>
@@ -2263,13 +2440,13 @@
         <v>25</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>680</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2277,7 +2454,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C33" s="7">
         <v>46139</v>
@@ -2285,29 +2462,29 @@
       <c r="D33" s="7">
         <v>46139</v>
       </c>
-      <c r="E33" s="7">
-        <v>46119</v>
+      <c r="E33" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F33" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G33" s="8">
         <v>-9</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>25</v>
@@ -2322,13 +2499,13 @@
         <v>25</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>680</v>
+        <v>202.27</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2336,37 +2513,37 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C34" s="7">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="D34" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46119</v>
+        <v>46125</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F34" s="8">
-        <v>-9</v>
+        <v>-24</v>
       </c>
       <c r="G34" s="8">
         <v>-9</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>25</v>
@@ -2378,16 +2555,16 @@
         <v>27</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S34" s="9">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2398,34 +2575,34 @@
         <v>46140</v>
       </c>
       <c r="C35" s="7">
-        <v>46082</v>
+        <v>46125</v>
       </c>
       <c r="D35" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="8">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="G35" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>25</v>
@@ -2443,10 +2620,10 @@
         <v>25</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S35" s="9">
-        <v>104.04</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2454,28 +2631,28 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C36" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D36" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="8">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="G36" s="8">
         <v>-8</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>74</v>
@@ -2487,7 +2664,7 @@
         <v>75</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2505,7 +2682,7 @@
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>120</v>
+        <v>626.62</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2513,38 +2690,38 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="C37" s="7">
-        <v>46132</v>
+        <v>45930</v>
       </c>
       <c r="D37" s="7">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="8">
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="G37" s="8">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="M37" s="6" t="s">
         <v>25</v>
       </c>
@@ -2561,10 +2738,10 @@
         <v>25</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S37" s="9">
-        <v>124.25</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2572,43 +2749,43 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C38" s="7">
-        <v>46139</v>
+        <v>46113</v>
       </c>
       <c r="D38" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>25</v>
+        <v>46150</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46141</v>
       </c>
       <c r="F38" s="8">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="G38" s="8">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="M38" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>27</v>
@@ -2617,13 +2794,13 @@
         <v>25</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="S38" s="9">
-        <v>202.27</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2631,40 +2808,40 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C39" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="D39" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="8">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="G39" s="8">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2679,10 +2856,10 @@
         <v>25</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>350</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2690,43 +2867,43 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C40" s="7">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="D40" s="7">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="8">
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="G40" s="8">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>27</v>
@@ -2738,10 +2915,10 @@
         <v>25</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>408.24</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2749,40 +2926,40 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="C41" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="D41" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="8">
-        <v>-16</v>
+        <v>-24</v>
       </c>
       <c r="G41" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2800,7 +2977,7 @@
         <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>626.62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2808,37 +2985,37 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="C42" s="7">
-        <v>45930</v>
+        <v>46082</v>
       </c>
       <c r="D42" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>25</v>
+        <v>46146</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46097</v>
       </c>
       <c r="F42" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>25</v>
@@ -2853,13 +3030,13 @@
         <v>25</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="S42" s="9">
-        <v>185.5</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2870,40 +3047,40 @@
         <v>46146</v>
       </c>
       <c r="C43" s="7">
-        <v>46113</v>
+        <v>46139</v>
       </c>
       <c r="D43" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46141</v>
+        <v>46139</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F43" s="8">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>27</v>
@@ -2912,13 +3089,13 @@
         <v>25</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>12.9</v>
+        <v>204.67</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2929,37 +3106,37 @@
         <v>46146</v>
       </c>
       <c r="C44" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D44" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F44" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -2977,7 +3154,7 @@
         <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>50</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -2997,25 +3174,25 @@
         <v>25</v>
       </c>
       <c r="F45" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>25</v>
@@ -3036,7 +3213,7 @@
         <v>29</v>
       </c>
       <c r="S45" s="9">
-        <v>80</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3047,37 +3224,37 @@
         <v>46146</v>
       </c>
       <c r="C46" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D46" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E46" s="7">
-        <v>46097</v>
+        <v>46139</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F46" s="8">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3089,13 +3266,13 @@
         <v>25</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>146.55</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3106,37 +3283,37 @@
         <v>46146</v>
       </c>
       <c r="C47" s="7">
-        <v>46139</v>
+        <v>45901</v>
       </c>
       <c r="D47" s="7">
-        <v>46139</v>
+        <v>45938</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="8">
-        <v>-9</v>
+        <v>-211</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>27</v>
@@ -3154,7 +3331,7 @@
         <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>204.67</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3165,34 +3342,34 @@
         <v>46146</v>
       </c>
       <c r="C48" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="D48" s="7">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F48" s="8">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>25</v>
@@ -3213,7 +3390,7 @@
         <v>29</v>
       </c>
       <c r="S48" s="9">
-        <v>250</v>
+        <v>550</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3224,37 +3401,37 @@
         <v>46146</v>
       </c>
       <c r="C49" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D49" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>25</v>
+        <v>46146</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>27</v>
@@ -3266,13 +3443,13 @@
         <v>25</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3283,25 +3460,25 @@
         <v>46146</v>
       </c>
       <c r="C50" s="7">
-        <v>45901</v>
+        <v>46146</v>
       </c>
       <c r="D50" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>25</v>
+        <v>46146</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46127</v>
       </c>
       <c r="F50" s="8">
-        <v>-210</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>96</v>
@@ -3310,10 +3487,10 @@
         <v>25</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>27</v>
@@ -3325,13 +3502,13 @@
         <v>25</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>363</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3342,37 +3519,37 @@
         <v>46146</v>
       </c>
       <c r="C51" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D51" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>25</v>
+        <v>46146</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G51" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>27</v>
@@ -3384,13 +3561,13 @@
         <v>25</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S51" s="9">
-        <v>550</v>
+        <v>620</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3404,34 +3581,34 @@
         <v>46146</v>
       </c>
       <c r="D52" s="7">
-        <v>46146</v>
+        <v>46111</v>
       </c>
       <c r="E52" s="7">
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="F52" s="8">
-        <v>-2</v>
+        <v>-38</v>
       </c>
       <c r="G52" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3449,7 +3626,7 @@
         <v>29</v>
       </c>
       <c r="S52" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3466,31 +3643,31 @@
         <v>46146</v>
       </c>
       <c r="E53" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>27</v>
@@ -3508,7 +3685,7 @@
         <v>29</v>
       </c>
       <c r="S53" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3525,22 +3702,22 @@
         <v>46146</v>
       </c>
       <c r="E54" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F54" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G54" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>25</v>
@@ -3549,7 +3726,7 @@
         <v>59</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>27</v>
@@ -3567,7 +3744,7 @@
         <v>29</v>
       </c>
       <c r="S54" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3581,31 +3758,31 @@
         <v>46146</v>
       </c>
       <c r="D55" s="7">
-        <v>46111</v>
+        <v>46146</v>
       </c>
       <c r="E55" s="7">
-        <v>46118</v>
+        <v>46112</v>
       </c>
       <c r="F55" s="8">
-        <v>-37</v>
+        <v>-3</v>
       </c>
       <c r="G55" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>25</v>
@@ -3626,7 +3803,7 @@
         <v>29</v>
       </c>
       <c r="S55" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3643,31 +3820,31 @@
         <v>46146</v>
       </c>
       <c r="E56" s="7">
-        <v>46141</v>
+        <v>46100</v>
       </c>
       <c r="F56" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G56" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>27</v>
@@ -3685,7 +3862,7 @@
         <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3702,31 +3879,31 @@
         <v>46146</v>
       </c>
       <c r="E57" s="7">
-        <v>46119</v>
+        <v>46100</v>
       </c>
       <c r="F57" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G57" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3741,10 +3918,10 @@
         <v>28</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3761,28 +3938,28 @@
         <v>46146</v>
       </c>
       <c r="E58" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F58" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G58" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>25</v>
@@ -3803,7 +3980,7 @@
         <v>29</v>
       </c>
       <c r="S58" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3823,28 +4000,28 @@
         <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G59" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3853,7 +4030,7 @@
         <v>27</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>28</v>
@@ -3862,7 +4039,7 @@
         <v>29</v>
       </c>
       <c r="S59" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3879,28 +4056,28 @@
         <v>46146</v>
       </c>
       <c r="E60" s="7">
-        <v>46127</v>
+        <v>46101</v>
       </c>
       <c r="F60" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G60" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>25</v>
@@ -3921,7 +4098,7 @@
         <v>29</v>
       </c>
       <c r="S60" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3932,34 +4109,34 @@
         <v>46146</v>
       </c>
       <c r="C61" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="D61" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E61" s="7">
-        <v>46112</v>
+        <v>46132</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F61" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G61" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>25</v>
@@ -3974,13 +4151,13 @@
         <v>25</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>630</v>
+        <v>655.21</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -3997,28 +4174,28 @@
         <v>46146</v>
       </c>
       <c r="E62" s="7">
-        <v>46112</v>
+        <v>46141</v>
       </c>
       <c r="F62" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G62" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>53</v>
+        <v>112</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>25</v>
@@ -4036,10 +4213,10 @@
         <v>28</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S62" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4053,31 +4230,31 @@
         <v>46146</v>
       </c>
       <c r="D63" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E63" s="7">
-        <v>46100</v>
+        <v>46119</v>
       </c>
       <c r="F63" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G63" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>25</v>
@@ -4095,10 +4272,10 @@
         <v>28</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S63" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4115,28 +4292,28 @@
         <v>46146</v>
       </c>
       <c r="E64" s="7">
-        <v>46100</v>
+        <v>46119</v>
       </c>
       <c r="F64" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G64" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>25</v>
@@ -4157,7 +4334,7 @@
         <v>29</v>
       </c>
       <c r="S64" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4174,28 +4351,28 @@
         <v>46146</v>
       </c>
       <c r="E65" s="7">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="F65" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G65" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>25</v>
@@ -4213,10 +4390,10 @@
         <v>28</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S65" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4233,28 +4410,28 @@
         <v>46146</v>
       </c>
       <c r="E66" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F66" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G66" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>25</v>
@@ -4266,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>28</v>
@@ -4275,7 +4452,7 @@
         <v>29</v>
       </c>
       <c r="S66" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4283,7 +4460,7 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C67" s="7">
         <v>46146</v>
@@ -4291,32 +4468,32 @@
       <c r="D67" s="7">
         <v>46146</v>
       </c>
-      <c r="E67" s="7">
-        <v>46119</v>
+      <c r="E67" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F67" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G67" s="8">
         <v>-2</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>27</v>
@@ -4328,13 +4505,13 @@
         <v>25</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S67" s="9">
-        <v>650</v>
+        <v>118.84</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4342,58 +4519,58 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C68" s="7">
-        <v>46132</v>
+        <v>46142</v>
       </c>
       <c r="D68" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>25</v>
+        <v>46142</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46148</v>
       </c>
       <c r="F68" s="8">
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="G68" s="8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J68" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R68" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="M68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R68" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S68" s="9">
-        <v>655.21</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4401,58 +4578,58 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C69" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D69" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E69" s="7">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="F69" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G69" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S69" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4460,46 +4637,46 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C70" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D70" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E70" s="7">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="F70" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G70" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>25</v>
@@ -4511,7 +4688,7 @@
         <v>29</v>
       </c>
       <c r="S70" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4519,46 +4696,46 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C71" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D71" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E71" s="7">
         <v>46119</v>
       </c>
       <c r="F71" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G71" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>25</v>
@@ -4570,7 +4747,7 @@
         <v>29</v>
       </c>
       <c r="S71" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4578,46 +4755,46 @@
         <v>22</v>
       </c>
       <c r="B72" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C72" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D72" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E72" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F72" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>25</v>
@@ -4626,10 +4803,10 @@
         <v>28</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S72" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4637,46 +4814,46 @@
         <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C73" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D73" s="7">
-        <v>46132</v>
+        <v>46153</v>
       </c>
       <c r="E73" s="7">
         <v>46119</v>
       </c>
       <c r="F73" s="8">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="G73" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>25</v>
@@ -4685,10 +4862,10 @@
         <v>28</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S73" s="9">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4696,46 +4873,46 @@
         <v>22</v>
       </c>
       <c r="B74" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C74" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D74" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E74" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F74" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G74" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>25</v>
@@ -4744,10 +4921,10 @@
         <v>28</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S74" s="9">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row r="75" ht="23" customHeight="1">
@@ -4755,46 +4932,46 @@
         <v>22</v>
       </c>
       <c r="B75" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C75" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D75" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E75" s="7">
-        <v>46099</v>
+        <v>46141</v>
       </c>
       <c r="F75" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G75" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>25</v>
@@ -4803,10 +4980,10 @@
         <v>28</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S75" s="9">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="76" ht="23" customHeight="1">
@@ -4814,49 +4991,49 @@
         <v>22</v>
       </c>
       <c r="B76" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C76" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D76" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E76" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F76" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G76" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="Q76" s="6" t="s">
         <v>28</v>
@@ -4865,7 +5042,7 @@
         <v>29</v>
       </c>
       <c r="S76" s="9">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="77" ht="23" customHeight="1">
@@ -4873,49 +5050,49 @@
         <v>22</v>
       </c>
       <c r="B77" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="C77" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D77" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E77" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F77" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G77" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q77" s="6" t="s">
         <v>28</v>
@@ -4924,7 +5101,7 @@
         <v>29</v>
       </c>
       <c r="S77" s="9">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78" ht="23" customHeight="1">
@@ -4932,117 +5109,3539 @@
         <v>22</v>
       </c>
       <c r="B78" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F78" s="8">
+        <v>4</v>
+      </c>
+      <c r="G78" s="8">
+        <v>4</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S78" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="79" ht="23" customHeight="1">
+      <c r="A79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F79" s="8">
+        <v>4</v>
+      </c>
+      <c r="G79" s="8">
+        <v>4</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S79" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="80" ht="23" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F80" s="8">
+        <v>4</v>
+      </c>
+      <c r="G80" s="8">
+        <v>4</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S80" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="81" ht="23" customHeight="1">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F81" s="8">
+        <v>4</v>
+      </c>
+      <c r="G81" s="8">
+        <v>4</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S81" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="82" ht="23" customHeight="1">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F82" s="8">
+        <v>4</v>
+      </c>
+      <c r="G82" s="8">
+        <v>4</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S82" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="83" ht="23" customHeight="1">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F83" s="8">
+        <v>4</v>
+      </c>
+      <c r="G83" s="8">
+        <v>4</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S83" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F84" s="8">
+        <v>4</v>
+      </c>
+      <c r="G84" s="8">
+        <v>4</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S84" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F85" s="8">
+        <v>4</v>
+      </c>
+      <c r="G85" s="8">
+        <v>4</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S85" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="86" ht="23" customHeight="1">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F86" s="8">
+        <v>4</v>
+      </c>
+      <c r="G86" s="8">
+        <v>4</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S86" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F87" s="8">
+        <v>4</v>
+      </c>
+      <c r="G87" s="8">
+        <v>4</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S87" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F88" s="8">
+        <v>4</v>
+      </c>
+      <c r="G88" s="8">
+        <v>4</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S88" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="89" ht="23" customHeight="1">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F89" s="8">
+        <v>4</v>
+      </c>
+      <c r="G89" s="8">
+        <v>4</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S89" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="90" ht="23" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F90" s="8">
+        <v>4</v>
+      </c>
+      <c r="G90" s="8">
+        <v>4</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S90" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="91" ht="23" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C91" s="7">
         <v>46147</v>
       </c>
-      <c r="C78" s="7">
-        <v>46146</v>
-      </c>
-      <c r="D78" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F78" s="8">
+      <c r="D91" s="7">
+        <v>46147</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F91" s="8">
         <v>-2</v>
       </c>
-      <c r="G78" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H78" s="6" t="s">
+      <c r="G91" s="8">
+        <v>4</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="S91" s="9">
+        <v>1028.57</v>
+      </c>
+    </row>
+    <row r="92" ht="23" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46153</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46153</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F92" s="8">
+        <v>4</v>
+      </c>
+      <c r="G92" s="8">
+        <v>4</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="S92" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E93" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F93" s="8">
+        <v>11</v>
+      </c>
+      <c r="G93" s="8">
+        <v>11</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S93" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="94" ht="23" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F94" s="8">
+        <v>11</v>
+      </c>
+      <c r="G94" s="8">
+        <v>11</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S94" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="95" ht="23" customHeight="1">
+      <c r="A95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C95" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D95" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E95" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F95" s="8">
+        <v>11</v>
+      </c>
+      <c r="G95" s="8">
+        <v>11</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S95" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="96" ht="23" customHeight="1">
+      <c r="A96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C96" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D96" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E96" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F96" s="8">
+        <v>11</v>
+      </c>
+      <c r="G96" s="8">
+        <v>11</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S96" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="97" ht="23" customHeight="1">
+      <c r="A97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C97" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D97" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F97" s="8">
+        <v>11</v>
+      </c>
+      <c r="G97" s="8">
+        <v>11</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S97" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="98" ht="23" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C98" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D98" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E98" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F98" s="8">
+        <v>11</v>
+      </c>
+      <c r="G98" s="8">
+        <v>11</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S98" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="99" ht="23" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C99" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D99" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E99" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F99" s="8">
+        <v>11</v>
+      </c>
+      <c r="G99" s="8">
+        <v>11</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S99" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="100" ht="23" customHeight="1">
+      <c r="A100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C100" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D100" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E100" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F100" s="8">
+        <v>11</v>
+      </c>
+      <c r="G100" s="8">
+        <v>11</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S100" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="101" ht="23" customHeight="1">
+      <c r="A101" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B101" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C101" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D101" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E101" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F101" s="8">
+        <v>11</v>
+      </c>
+      <c r="G101" s="8">
+        <v>11</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N101" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q101" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S101" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="102" ht="23" customHeight="1">
+      <c r="A102" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C102" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D102" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E102" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F102" s="8">
+        <v>11</v>
+      </c>
+      <c r="G102" s="8">
+        <v>11</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S102" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="103" ht="23" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C103" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D103" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E103" s="7">
+        <v>46112</v>
+      </c>
+      <c r="F103" s="8">
+        <v>11</v>
+      </c>
+      <c r="G103" s="8">
+        <v>11</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N103" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S103" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="104" ht="23" customHeight="1">
+      <c r="A104" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C104" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D104" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E104" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F104" s="8">
+        <v>11</v>
+      </c>
+      <c r="G104" s="8">
+        <v>11</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S104" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="105" ht="23" customHeight="1">
+      <c r="A105" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C105" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D105" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E105" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F105" s="8">
+        <v>11</v>
+      </c>
+      <c r="G105" s="8">
+        <v>11</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L105" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N105" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O105" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S105" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="106" ht="23" customHeight="1">
+      <c r="A106" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C106" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D106" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E106" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F106" s="8">
+        <v>11</v>
+      </c>
+      <c r="G106" s="8">
+        <v>11</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K106" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R106" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S106" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="107" ht="23" customHeight="1">
+      <c r="A107" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C107" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D107" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E107" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F107" s="8">
+        <v>11</v>
+      </c>
+      <c r="G107" s="8">
+        <v>11</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J107" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L107" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N107" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O107" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R107" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S107" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="108" ht="23" customHeight="1">
+      <c r="A108" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C108" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D108" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E108" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F108" s="8">
+        <v>11</v>
+      </c>
+      <c r="G108" s="8">
+        <v>11</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J108" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q108" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R108" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S108" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="109" ht="23" customHeight="1">
+      <c r="A109" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C109" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D109" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E109" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F109" s="8">
+        <v>11</v>
+      </c>
+      <c r="G109" s="8">
+        <v>11</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="K109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L109" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N109" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O109" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q109" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R109" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S109" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="110" ht="23" customHeight="1">
+      <c r="A110" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C110" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D110" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E110" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F110" s="8">
+        <v>11</v>
+      </c>
+      <c r="G110" s="8">
+        <v>11</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J110" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="K110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R110" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S110" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="111" ht="23" customHeight="1">
+      <c r="A111" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C111" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D111" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E111" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F111" s="8">
+        <v>11</v>
+      </c>
+      <c r="G111" s="8">
+        <v>11</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J111" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L111" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N111" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O111" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q111" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R111" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S111" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="112" ht="23" customHeight="1">
+      <c r="A112" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C112" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D112" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E112" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F112" s="8">
+        <v>11</v>
+      </c>
+      <c r="G112" s="8">
+        <v>11</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J112" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L112" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P112" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q112" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R112" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S112" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="113" ht="23" customHeight="1">
+      <c r="A113" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C113" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D113" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E113" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F113" s="8">
+        <v>11</v>
+      </c>
+      <c r="G113" s="8">
+        <v>11</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L113" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N113" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O113" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q113" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R113" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S113" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="114" ht="23" customHeight="1">
+      <c r="A114" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C114" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D114" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E114" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F114" s="8">
+        <v>11</v>
+      </c>
+      <c r="G114" s="8">
+        <v>11</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J114" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L114" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q114" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R114" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S114" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="115" ht="23" customHeight="1">
+      <c r="A115" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C115" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D115" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E115" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F115" s="8">
+        <v>11</v>
+      </c>
+      <c r="G115" s="8">
+        <v>11</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L115" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N115" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O115" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q115" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S115" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="116" ht="23" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C116" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D116" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E116" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F116" s="8">
+        <v>11</v>
+      </c>
+      <c r="G116" s="8">
+        <v>11</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q116" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R116" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="S116" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="117" ht="23" customHeight="1">
+      <c r="A117" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B117" s="7">
+        <v>46160</v>
+      </c>
+      <c r="C117" s="7">
+        <v>46160</v>
+      </c>
+      <c r="D117" s="7">
+        <v>46160</v>
+      </c>
+      <c r="E117" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F117" s="8">
+        <v>11</v>
+      </c>
+      <c r="G117" s="8">
+        <v>11</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L117" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N117" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O117" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q117" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R117" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="S117" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="118" ht="23" customHeight="1">
+      <c r="A118" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C118" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D118" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E118" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F118" s="8">
+        <v>18</v>
+      </c>
+      <c r="G118" s="8">
+        <v>18</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J118" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q118" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="R118" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S118" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="119" ht="23" customHeight="1">
+      <c r="A119" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C119" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D119" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E119" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F119" s="8">
+        <v>18</v>
+      </c>
+      <c r="G119" s="8">
+        <v>18</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J119" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K119" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L119" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M119" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N119" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O119" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P119" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q119" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R119" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S119" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="120" ht="23" customHeight="1">
+      <c r="A120" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C120" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D120" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E120" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F120" s="8">
+        <v>18</v>
+      </c>
+      <c r="G120" s="8">
+        <v>18</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I120" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J120" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K120" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L120" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q120" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R120" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S120" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="121" ht="23" customHeight="1">
+      <c r="A121" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B121" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C121" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D121" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E121" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F121" s="8">
+        <v>18</v>
+      </c>
+      <c r="G121" s="8">
+        <v>18</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J121" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="K121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L121" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N121" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O121" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q121" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R121" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S121" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="122" ht="23" customHeight="1">
+      <c r="A122" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B122" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C122" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D122" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E122" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F122" s="8">
+        <v>18</v>
+      </c>
+      <c r="G122" s="8">
+        <v>18</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I122" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J122" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="K122" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N122" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P122" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q122" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R122" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S122" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="123" ht="23" customHeight="1">
+      <c r="A123" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C123" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D123" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E123" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F123" s="8">
+        <v>18</v>
+      </c>
+      <c r="G123" s="8">
+        <v>18</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J123" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K123" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L123" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M123" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N123" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O123" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P123" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q123" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R123" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S123" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="124" ht="23" customHeight="1">
+      <c r="A124" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B124" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C124" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D124" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E124" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F124" s="8">
+        <v>18</v>
+      </c>
+      <c r="G124" s="8">
+        <v>18</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I124" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J124" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="K124" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P124" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q124" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R124" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S124" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="125" ht="23" customHeight="1">
+      <c r="A125" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C125" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D125" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E125" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F125" s="8">
+        <v>18</v>
+      </c>
+      <c r="G125" s="8">
+        <v>18</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="K125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L125" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M125" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N125" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O125" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R125" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S125" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="126" ht="23" customHeight="1">
+      <c r="A126" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B126" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C126" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D126" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E126" s="7">
+        <v>46092</v>
+      </c>
+      <c r="F126" s="8">
+        <v>18</v>
+      </c>
+      <c r="G126" s="8">
+        <v>18</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J126" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="K126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L126" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N126" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q126" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R126" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S126" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="127" ht="23" customHeight="1">
+      <c r="A127" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C127" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D127" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E127" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F127" s="8">
+        <v>18</v>
+      </c>
+      <c r="G127" s="8">
+        <v>18</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J127" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="K127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L127" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N127" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O127" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q127" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R127" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S127" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="128" ht="23" customHeight="1">
+      <c r="A128" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B128" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C128" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D128" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E128" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F128" s="8">
+        <v>18</v>
+      </c>
+      <c r="G128" s="8">
+        <v>18</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I128" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K128" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L128" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N128" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O128" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P128" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q128" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R128" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S128" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="129" ht="23" customHeight="1">
+      <c r="A129" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C129" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D129" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E129" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F129" s="8">
+        <v>18</v>
+      </c>
+      <c r="G129" s="8">
+        <v>18</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J129" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L129" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N129" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O129" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q129" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R129" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S129" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="130" ht="23" customHeight="1">
+      <c r="A130" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C130" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D130" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E130" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F130" s="8">
+        <v>18</v>
+      </c>
+      <c r="G130" s="8">
+        <v>18</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J130" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L130" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N130" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O130" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q130" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R130" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S130" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="131" ht="23" customHeight="1">
+      <c r="A131" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B131" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C131" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D131" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E131" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F131" s="8">
+        <v>18</v>
+      </c>
+      <c r="G131" s="8">
+        <v>18</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J131" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L131" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N131" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O131" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q131" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R131" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S131" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="132" ht="23" customHeight="1">
+      <c r="A132" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C132" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D132" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E132" s="7">
+        <v>46099</v>
+      </c>
+      <c r="F132" s="8">
+        <v>18</v>
+      </c>
+      <c r="G132" s="8">
+        <v>18</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J132" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="K132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L132" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N132" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q132" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R132" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S132" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="133" ht="23" customHeight="1">
+      <c r="A133" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B133" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C133" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D133" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E133" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F133" s="8">
+        <v>18</v>
+      </c>
+      <c r="G133" s="8">
+        <v>18</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J133" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L133" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N133" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O133" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q133" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R133" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S133" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="134" ht="23" customHeight="1">
+      <c r="A134" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C134" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D134" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E134" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F134" s="8">
+        <v>18</v>
+      </c>
+      <c r="G134" s="8">
+        <v>18</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J134" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L134" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N134" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O134" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q134" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R134" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="S134" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="135" ht="23" customHeight="1">
+      <c r="A135" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B135" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C135" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D135" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E135" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F135" s="8">
+        <v>18</v>
+      </c>
+      <c r="G135" s="8">
+        <v>18</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J135" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L135" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N135" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O135" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q135" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R135" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="S135" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="136" ht="23" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B136" s="7">
+        <v>46172</v>
+      </c>
+      <c r="C136" s="7">
+        <v>45930</v>
+      </c>
+      <c r="D136" s="7">
+        <v>46172</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F136" s="8">
         <v>23</v>
       </c>
-      <c r="I78" s="6" t="s">
+      <c r="G136" s="8">
         <v>23</v>
       </c>
-      <c r="J78" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R78" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S78" s="9">
-        <v>118.84</v>
-      </c>
-    </row>
-    <row r="79" ht="23" customHeight="1">
-      <c r="A79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R79" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="S79" s="13">
-        <f>SUM(S6:S78)</f>
+      <c r="H136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L136" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="M136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N136" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S136" s="9">
+        <v>185.5</v>
+      </c>
+    </row>
+    <row r="137" ht="23" customHeight="1">
+      <c r="A137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E137" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G137" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="N137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="R137" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S137" s="13">
+        <f>SUM(S6:S136)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$112</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sexta-feira, 8 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 11 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -184,243 +184,246 @@
     <t>REGINALDO BENTO DA SILVA</t>
   </si>
   <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11452</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11410</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
     <t>HOJE</t>
   </si>
   <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11452</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11555</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11354</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11397</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11398</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11492</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11502</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11432</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11327</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11599</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11575</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
   </si>
   <si>
     <t>A VENCER</t>
   </si>
   <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11555</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11554</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11354</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11397</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11398</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11492</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11523</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11502</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11432</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11327</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11267</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11599</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11575</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
     <t>FA-11400</t>
   </si>
   <si>
@@ -454,6 +457,9 @@
     <t>FA-11616</t>
   </si>
   <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
     <t>FA-11279</t>
   </si>
   <si>
@@ -518,6 +524,9 @@
   </si>
   <si>
     <t>FA-11617</t>
+  </si>
+  <si>
+    <t>FA-11621</t>
   </si>
   <si>
     <t>FA-11488</t>
@@ -705,7 +714,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S116"/>
+  <dimension ref="A1:S118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -822,10 +831,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-32</v>
+        <v>-35</v>
       </c>
       <c r="G6" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -881,10 +890,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="G7" s="8">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>25</v>
@@ -940,10 +949,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="G8" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -999,10 +1008,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="G9" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>25</v>
@@ -1058,10 +1067,10 @@
         <v>46127</v>
       </c>
       <c r="F10" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G10" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -1117,10 +1126,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G11" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>25</v>
@@ -1176,10 +1185,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G12" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>25</v>
@@ -1235,10 +1244,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G13" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>25</v>
@@ -1294,10 +1303,10 @@
         <v>46122</v>
       </c>
       <c r="F14" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G14" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>25</v>
@@ -1353,10 +1362,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G15" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1412,10 +1421,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="G16" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1471,10 +1480,10 @@
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="G17" s="8">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1530,13 +1539,13 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G18" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>25</v>
@@ -1554,7 +1563,7 @@
         <v>23</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>28</v>
@@ -1566,7 +1575,7 @@
         <v>40</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S18" s="9">
         <v>12.9</v>
@@ -1589,10 +1598,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G19" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>25</v>
@@ -1601,16 +1610,16 @@
         <v>25</v>
       </c>
       <c r="J19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="M19" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>28</v>
@@ -1648,10 +1657,10 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G20" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>23</v>
@@ -1660,19 +1669,19 @@
         <v>25</v>
       </c>
       <c r="J20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="6" t="s">
+      <c r="M20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>28</v>
@@ -1707,10 +1716,10 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="G21" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -1719,7 +1728,7 @@
         <v>25</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
@@ -1766,10 +1775,10 @@
         <v>46097</v>
       </c>
       <c r="F22" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G22" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1825,10 +1834,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G23" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1837,13 +1846,13 @@
         <v>25</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1884,10 +1893,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G24" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1896,16 +1905,16 @@
         <v>25</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>28</v>
@@ -1943,10 +1952,10 @@
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G25" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -1955,13 +1964,13 @@
         <v>25</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -2002,10 +2011,10 @@
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G26" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -2014,16 +2023,16 @@
         <v>25</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>28</v>
@@ -2061,25 +2070,25 @@
         <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-212</v>
+        <v>-215</v>
       </c>
       <c r="G27" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2120,10 +2129,10 @@
         <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G28" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2132,16 +2141,16 @@
         <v>25</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>28</v>
@@ -2179,10 +2188,10 @@
         <v>46141</v>
       </c>
       <c r="F29" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G29" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2191,7 +2200,7 @@
         <v>25</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
@@ -2238,10 +2247,10 @@
         <v>46141</v>
       </c>
       <c r="F30" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G30" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>25</v>
@@ -2250,13 +2259,13 @@
         <v>25</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2297,10 +2306,10 @@
         <v>46112</v>
       </c>
       <c r="F31" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G31" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>25</v>
@@ -2309,7 +2318,7 @@
         <v>25</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
@@ -2356,10 +2365,10 @@
         <v>46119</v>
       </c>
       <c r="F32" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G32" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2368,16 +2377,16 @@
         <v>25</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>28</v>
@@ -2415,10 +2424,10 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G33" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>25</v>
@@ -2427,13 +2436,13 @@
         <v>25</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2471,13 +2480,13 @@
         <v>46146</v>
       </c>
       <c r="E34" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F34" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G34" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2486,13 +2495,13 @@
         <v>25</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2504,16 +2513,16 @@
         <v>28</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S34" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2521,22 +2530,22 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C35" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D35" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E35" s="7">
-        <v>46119</v>
+        <v>46139</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="G35" s="8">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>25</v>
@@ -2545,13 +2554,13 @@
         <v>25</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2563,16 +2572,16 @@
         <v>28</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S35" s="9">
-        <v>700</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2583,19 +2592,19 @@
         <v>46147</v>
       </c>
       <c r="C36" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="D36" s="7">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="G36" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>25</v>
@@ -2604,13 +2613,13 @@
         <v>25</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2631,7 +2640,7 @@
         <v>30</v>
       </c>
       <c r="S36" s="9">
-        <v>103.36</v>
+        <v>124.27</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2639,7 +2648,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C37" s="7">
         <v>46146</v>
@@ -2651,10 +2660,10 @@
         <v>23</v>
       </c>
       <c r="F37" s="8">
+        <v>-7</v>
+      </c>
+      <c r="G37" s="8">
         <v>-4</v>
-      </c>
-      <c r="G37" s="8">
-        <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>25</v>
@@ -2663,7 +2672,7 @@
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
@@ -2690,7 +2699,7 @@
         <v>30</v>
       </c>
       <c r="S37" s="9">
-        <v>124.27</v>
+        <v>380</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2701,19 +2710,19 @@
         <v>46149</v>
       </c>
       <c r="C38" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="D38" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46142</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46148</v>
       </c>
       <c r="F38" s="8">
+        <v>-11</v>
+      </c>
+      <c r="G38" s="8">
         <v>-4</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-1</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>25</v>
@@ -2722,34 +2731,34 @@
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="6" t="s">
+      <c r="M38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R38" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R38" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="S38" s="9">
-        <v>380</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2757,22 +2766,22 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C39" s="7">
-        <v>46142</v>
+        <v>46125</v>
       </c>
       <c r="D39" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46148</v>
+        <v>46125</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="G39" s="8">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2802,13 +2811,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="S39" s="9">
-        <v>685.71</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2819,34 +2828,34 @@
         <v>46150</v>
       </c>
       <c r="C40" s="7">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="D40" s="7">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-25</v>
+        <v>-7</v>
       </c>
       <c r="G40" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2855,7 +2864,7 @@
         <v>28</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>23</v>
@@ -2867,7 +2876,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="9">
-        <v>53.82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2878,34 +2887,34 @@
         <v>46150</v>
       </c>
       <c r="C41" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D41" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-4</v>
+        <v>-28</v>
       </c>
       <c r="G41" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2914,7 +2923,7 @@
         <v>28</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>23</v>
@@ -2923,10 +2932,10 @@
         <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S41" s="9">
-        <v>170</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2937,34 +2946,34 @@
         <v>46150</v>
       </c>
       <c r="C42" s="7">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="D42" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46153</v>
       </c>
       <c r="F42" s="8">
-        <v>-25</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2973,19 +2982,19 @@
         <v>28</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S42" s="9">
-        <v>250</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -3005,10 +3014,10 @@
         <v>46097</v>
       </c>
       <c r="F43" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>23</v>
@@ -3029,10 +3038,10 @@
         <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>23</v>
@@ -3064,10 +3073,10 @@
         <v>46112</v>
       </c>
       <c r="F44" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>23</v>
@@ -3076,22 +3085,22 @@
         <v>23</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>92</v>
-      </c>
       <c r="M44" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
@@ -3123,10 +3132,10 @@
         <v>46119</v>
       </c>
       <c r="F45" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>23</v>
@@ -3135,22 +3144,22 @@
         <v>23</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
@@ -3182,10 +3191,10 @@
         <v>46127</v>
       </c>
       <c r="F46" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>23</v>
@@ -3194,22 +3203,22 @@
         <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K46" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="M46" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
@@ -3241,10 +3250,10 @@
         <v>46141</v>
       </c>
       <c r="F47" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>23</v>
@@ -3253,22 +3262,22 @@
         <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
@@ -3300,10 +3309,10 @@
         <v>46141</v>
       </c>
       <c r="F48" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>23</v>
@@ -3312,7 +3321,7 @@
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
@@ -3324,10 +3333,10 @@
         <v>43</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
@@ -3359,10 +3368,10 @@
         <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>23</v>
@@ -3371,22 +3380,22 @@
         <v>23</v>
       </c>
       <c r="J49" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="M49" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
@@ -3418,10 +3427,10 @@
         <v>46112</v>
       </c>
       <c r="F50" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G50" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>23</v>
@@ -3430,22 +3439,22 @@
         <v>23</v>
       </c>
       <c r="J50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
@@ -3477,10 +3486,10 @@
         <v>46112</v>
       </c>
       <c r="F51" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G51" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>23</v>
@@ -3489,7 +3498,7 @@
         <v>23</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
@@ -3501,10 +3510,10 @@
         <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
@@ -3536,10 +3545,10 @@
         <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>23</v>
@@ -3548,22 +3557,22 @@
         <v>23</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>29</v>
@@ -3595,10 +3604,10 @@
         <v>46127</v>
       </c>
       <c r="F53" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>23</v>
@@ -3607,22 +3616,22 @@
         <v>23</v>
       </c>
       <c r="J53" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="K53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
@@ -3654,10 +3663,10 @@
         <v>46150</v>
       </c>
       <c r="F54" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G54" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>23</v>
@@ -3666,22 +3675,22 @@
         <v>23</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3713,10 +3722,10 @@
         <v>46127</v>
       </c>
       <c r="F55" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>23</v>
@@ -3725,22 +3734,22 @@
         <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
@@ -3772,10 +3781,10 @@
         <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G56" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>23</v>
@@ -3784,22 +3793,22 @@
         <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3831,10 +3840,10 @@
         <v>46092</v>
       </c>
       <c r="F57" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>23</v>
@@ -3843,22 +3852,22 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="K57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3890,10 +3899,10 @@
         <v>46119</v>
       </c>
       <c r="F58" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3902,22 +3911,22 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>114</v>
-      </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -3949,10 +3958,10 @@
         <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3961,22 +3970,22 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="K59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -4008,10 +4017,10 @@
         <v>46119</v>
       </c>
       <c r="F60" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G60" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -4020,7 +4029,7 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
@@ -4032,10 +4041,10 @@
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4067,10 +4076,10 @@
         <v>46141</v>
       </c>
       <c r="F61" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -4079,22 +4088,22 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="K61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4126,10 +4135,10 @@
         <v>46119</v>
       </c>
       <c r="F62" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G62" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4144,16 +4153,16 @@
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>29</v>
@@ -4185,10 +4194,10 @@
         <v>46099</v>
       </c>
       <c r="F63" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4209,10 +4218,10 @@
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4244,10 +4253,10 @@
         <v>46092</v>
       </c>
       <c r="F64" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4268,10 +4277,10 @@
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4303,10 +4312,10 @@
         <v>46148</v>
       </c>
       <c r="F65" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4327,10 +4336,10 @@
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4339,7 +4348,7 @@
         <v>39</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S65" s="9">
         <v>800</v>
@@ -4362,10 +4371,10 @@
         <v>46148</v>
       </c>
       <c r="F66" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G66" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>25</v>
@@ -4389,7 +4398,7 @@
         <v>28</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4398,7 +4407,7 @@
         <v>39</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="S66" s="9">
         <v>1028.57</v>
@@ -4421,10 +4430,10 @@
         <v>23</v>
       </c>
       <c r="F67" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G67" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>25</v>
@@ -4439,16 +4448,16 @@
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4480,10 +4489,10 @@
         <v>46097</v>
       </c>
       <c r="F68" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G68" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4504,10 +4513,10 @@
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4539,10 +4548,10 @@
         <v>46112</v>
       </c>
       <c r="F69" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G69" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4551,22 +4560,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4598,10 +4607,10 @@
         <v>46119</v>
       </c>
       <c r="F70" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G70" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4610,22 +4619,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4657,10 +4666,10 @@
         <v>46127</v>
       </c>
       <c r="F71" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G71" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4669,22 +4678,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4716,10 +4725,10 @@
         <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G72" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4728,22 +4737,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4775,10 +4784,10 @@
         <v>46141</v>
       </c>
       <c r="F73" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G73" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4787,22 +4796,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4834,10 +4843,10 @@
         <v>46141</v>
       </c>
       <c r="F74" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G74" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4846,7 +4855,7 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
@@ -4858,10 +4867,10 @@
         <v>43</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4893,10 +4902,10 @@
         <v>46119</v>
       </c>
       <c r="F75" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G75" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4905,22 +4914,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>29</v>
@@ -4952,10 +4961,10 @@
         <v>46127</v>
       </c>
       <c r="F76" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G76" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4964,22 +4973,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5011,10 +5020,10 @@
         <v>46112</v>
       </c>
       <c r="F77" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G77" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5023,22 +5032,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5070,10 +5079,10 @@
         <v>46112</v>
       </c>
       <c r="F78" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G78" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5082,7 +5091,7 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
@@ -5094,10 +5103,10 @@
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5129,10 +5138,10 @@
         <v>46150</v>
       </c>
       <c r="F79" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G79" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5141,22 +5150,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5185,13 +5194,13 @@
         <v>46160</v>
       </c>
       <c r="E80" s="7">
-        <v>46092</v>
+        <v>46153</v>
       </c>
       <c r="F80" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G80" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5200,22 +5209,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5244,13 +5253,13 @@
         <v>46160</v>
       </c>
       <c r="E81" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F81" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G81" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5259,22 +5268,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5303,13 +5312,13 @@
         <v>46160</v>
       </c>
       <c r="E82" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F82" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G82" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5318,22 +5327,22 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5365,10 +5374,10 @@
         <v>46119</v>
       </c>
       <c r="F83" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G83" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5377,22 +5386,22 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5404,7 +5413,7 @@
         <v>30</v>
       </c>
       <c r="S83" s="9">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="84" ht="23" customHeight="1">
@@ -5421,13 +5430,13 @@
         <v>46160</v>
       </c>
       <c r="E84" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F84" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G84" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5436,22 +5445,22 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5463,7 +5472,7 @@
         <v>30</v>
       </c>
       <c r="S84" s="9">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="85" ht="23" customHeight="1">
@@ -5480,13 +5489,13 @@
         <v>46160</v>
       </c>
       <c r="E85" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F85" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G85" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5495,22 +5504,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5542,10 +5551,10 @@
         <v>46119</v>
       </c>
       <c r="F86" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G86" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5554,22 +5563,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5578,7 +5587,7 @@
         <v>39</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S86" s="9">
         <v>680</v>
@@ -5598,13 +5607,13 @@
         <v>46160</v>
       </c>
       <c r="E87" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F87" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G87" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5613,22 +5622,22 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5657,13 +5666,13 @@
         <v>46160</v>
       </c>
       <c r="E88" s="7">
-        <v>46092</v>
+        <v>46141</v>
       </c>
       <c r="F88" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G88" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5672,22 +5681,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5696,10 +5705,10 @@
         <v>39</v>
       </c>
       <c r="R88" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S88" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="89" ht="23" customHeight="1">
@@ -5716,13 +5725,13 @@
         <v>46160</v>
       </c>
       <c r="E89" s="7">
-        <v>46099</v>
+        <v>46092</v>
       </c>
       <c r="F89" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G89" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5731,22 +5740,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5755,7 +5764,7 @@
         <v>39</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S89" s="9">
         <v>700</v>
@@ -5775,13 +5784,13 @@
         <v>46160</v>
       </c>
       <c r="E90" s="7">
-        <v>46119</v>
+        <v>46099</v>
       </c>
       <c r="F90" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G90" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5790,31 +5799,31 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>59</v>
+        <v>121</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q90" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S90" s="9">
         <v>700</v>
@@ -5834,13 +5843,13 @@
         <v>46160</v>
       </c>
       <c r="E91" s="7">
-        <v>46148</v>
+        <v>46119</v>
       </c>
       <c r="F91" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G91" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5849,34 +5858,34 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q91" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="S91" s="9">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="92" ht="23" customHeight="1">
@@ -5896,10 +5905,10 @@
         <v>46148</v>
       </c>
       <c r="F92" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G92" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5908,22 +5917,22 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>23</v>
@@ -5932,10 +5941,10 @@
         <v>39</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="S92" s="9">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="93" ht="23" customHeight="1">
@@ -5955,10 +5964,10 @@
         <v>46148</v>
       </c>
       <c r="F93" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G93" s="8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -5967,22 +5976,22 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -5991,7 +6000,7 @@
         <v>39</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="S93" s="9">
         <v>1200</v>
@@ -6002,22 +6011,22 @@
         <v>22</v>
       </c>
       <c r="B94" s="7">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="C94" s="7">
-        <v>46113</v>
+        <v>46160</v>
       </c>
       <c r="D94" s="7">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="E94" s="7">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="F94" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G94" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6026,22 +6035,22 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6050,10 +6059,10 @@
         <v>39</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="S94" s="9">
-        <v>2100</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="95" ht="23" customHeight="1">
@@ -6061,58 +6070,58 @@
         <v>22</v>
       </c>
       <c r="B95" s="7">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="C95" s="7">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="D95" s="7">
-        <v>46167</v>
+        <v>46150</v>
       </c>
       <c r="E95" s="7">
-        <v>46097</v>
+        <v>46149</v>
       </c>
       <c r="F95" s="8">
-        <v>17</v>
+        <v>-3</v>
       </c>
       <c r="G95" s="8">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S95" s="9">
-        <v>146.55</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="96" ht="23" customHeight="1">
@@ -6123,19 +6132,19 @@
         <v>46167</v>
       </c>
       <c r="C96" s="7">
-        <v>46167</v>
+        <v>46082</v>
       </c>
       <c r="D96" s="7">
         <v>46167</v>
       </c>
       <c r="E96" s="7">
-        <v>46119</v>
+        <v>46097</v>
       </c>
       <c r="F96" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G96" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6144,34 +6153,34 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S96" s="9">
-        <v>600</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="97" ht="23" customHeight="1">
@@ -6188,13 +6197,13 @@
         <v>46167</v>
       </c>
       <c r="E97" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F97" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G97" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6203,22 +6212,22 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>23</v>
@@ -6230,7 +6239,7 @@
         <v>30</v>
       </c>
       <c r="S97" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="98" ht="23" customHeight="1">
@@ -6250,10 +6259,10 @@
         <v>46141</v>
       </c>
       <c r="F98" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G98" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6262,22 +6271,22 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>23</v>
@@ -6306,13 +6315,13 @@
         <v>46167</v>
       </c>
       <c r="E99" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F99" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G99" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6321,22 +6330,22 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6345,7 +6354,7 @@
         <v>39</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S99" s="9">
         <v>620</v>
@@ -6368,10 +6377,10 @@
         <v>46119</v>
       </c>
       <c r="F100" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G100" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>23</v>
@@ -6380,34 +6389,34 @@
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q100" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S100" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="101" ht="23" customHeight="1">
@@ -6424,13 +6433,13 @@
         <v>46167</v>
       </c>
       <c r="E101" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F101" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G101" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6439,25 +6448,25 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q101" s="6" t="s">
         <v>39</v>
@@ -6483,13 +6492,13 @@
         <v>46167</v>
       </c>
       <c r="E102" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F102" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G102" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>23</v>
@@ -6498,22 +6507,22 @@
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>23</v>
@@ -6525,7 +6534,7 @@
         <v>30</v>
       </c>
       <c r="S102" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="103" ht="23" customHeight="1">
@@ -6542,13 +6551,13 @@
         <v>46167</v>
       </c>
       <c r="E103" s="7">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="F103" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G103" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6557,22 +6566,22 @@
         <v>23</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6601,13 +6610,13 @@
         <v>46167</v>
       </c>
       <c r="E104" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F104" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G104" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6616,22 +6625,22 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>23</v>
@@ -6660,13 +6669,13 @@
         <v>46167</v>
       </c>
       <c r="E105" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F105" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G105" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6675,22 +6684,22 @@
         <v>23</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P105" s="6" t="s">
         <v>23</v>
@@ -6702,7 +6711,7 @@
         <v>30</v>
       </c>
       <c r="S105" s="9">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="106" ht="23" customHeight="1">
@@ -6719,13 +6728,13 @@
         <v>46167</v>
       </c>
       <c r="E106" s="7">
-        <v>46113</v>
+        <v>46092</v>
       </c>
       <c r="F106" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G106" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6734,22 +6743,22 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>23</v>
@@ -6761,7 +6770,7 @@
         <v>30</v>
       </c>
       <c r="S106" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="107" ht="23" customHeight="1">
@@ -6781,10 +6790,10 @@
         <v>46119</v>
       </c>
       <c r="F107" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G107" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6793,22 +6802,22 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P107" s="6" t="s">
         <v>23</v>
@@ -6820,7 +6829,7 @@
         <v>30</v>
       </c>
       <c r="S107" s="9">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="108" ht="23" customHeight="1">
@@ -6837,13 +6846,13 @@
         <v>46167</v>
       </c>
       <c r="E108" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F108" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G108" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6852,22 +6861,22 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>23</v>
@@ -6876,7 +6885,7 @@
         <v>39</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S108" s="9">
         <v>680</v>
@@ -6896,13 +6905,13 @@
         <v>46167</v>
       </c>
       <c r="E109" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F109" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G109" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6911,22 +6920,22 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>23</v>
@@ -6935,7 +6944,7 @@
         <v>39</v>
       </c>
       <c r="R109" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S109" s="9">
         <v>680</v>
@@ -6955,13 +6964,13 @@
         <v>46167</v>
       </c>
       <c r="E110" s="7">
-        <v>46099</v>
+        <v>46119</v>
       </c>
       <c r="F110" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G110" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -6970,22 +6979,22 @@
         <v>23</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="M110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>23</v>
@@ -6997,7 +7006,7 @@
         <v>33</v>
       </c>
       <c r="S110" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="111" ht="23" customHeight="1">
@@ -7014,13 +7023,13 @@
         <v>46167</v>
       </c>
       <c r="E111" s="7">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="F111" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G111" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7029,22 +7038,22 @@
         <v>23</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N111" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O111" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>23</v>
@@ -7053,10 +7062,10 @@
         <v>39</v>
       </c>
       <c r="R111" s="6" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="S111" s="9">
-        <v>800</v>
+        <v>680</v>
       </c>
     </row>
     <row r="112" ht="23" customHeight="1">
@@ -7073,13 +7082,13 @@
         <v>46167</v>
       </c>
       <c r="E112" s="7">
-        <v>46148</v>
+        <v>46099</v>
       </c>
       <c r="F112" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G112" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7088,22 +7097,22 @@
         <v>23</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>23</v>
@@ -7112,10 +7121,10 @@
         <v>39</v>
       </c>
       <c r="R112" s="6" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="S112" s="9">
-        <v>1200</v>
+        <v>700</v>
       </c>
     </row>
     <row r="113" ht="23" customHeight="1">
@@ -7135,10 +7144,10 @@
         <v>46148</v>
       </c>
       <c r="F113" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G113" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7147,22 +7156,22 @@
         <v>23</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N113" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>23</v>
@@ -7171,10 +7180,10 @@
         <v>39</v>
       </c>
       <c r="R113" s="6" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="S113" s="9">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="114" ht="23" customHeight="1">
@@ -7185,19 +7194,19 @@
         <v>46167</v>
       </c>
       <c r="C114" s="7">
-        <v>46113</v>
+        <v>46167</v>
       </c>
       <c r="D114" s="7">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="E114" s="7">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="F114" s="8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G114" s="8">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>23</v>
@@ -7206,22 +7215,22 @@
         <v>23</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>23</v>
@@ -7230,10 +7239,10 @@
         <v>39</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="S114" s="9">
-        <v>4400</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="115" ht="23" customHeight="1">
@@ -7241,117 +7250,235 @@
         <v>22</v>
       </c>
       <c r="B115" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C115" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D115" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E115" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F115" s="8">
+        <v>14</v>
+      </c>
+      <c r="G115" s="8">
+        <v>14</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J115" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N115" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O115" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q115" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="S115" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="116" ht="23" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C116" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D116" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E116" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F116" s="8">
+        <v>-3</v>
+      </c>
+      <c r="G116" s="8">
+        <v>14</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q116" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R116" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S116" s="9">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="117" ht="23" customHeight="1">
+      <c r="A117" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B117" s="7">
         <v>46172</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C117" s="7">
         <v>45930</v>
       </c>
-      <c r="D115" s="7">
+      <c r="D117" s="7">
         <v>46172</v>
       </c>
-      <c r="E115" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F115" s="8">
-        <v>22</v>
-      </c>
-      <c r="G115" s="8">
-        <v>22</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L115" s="6" t="s">
+      <c r="E117" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117" s="8">
+        <v>19</v>
+      </c>
+      <c r="G117" s="8">
+        <v>19</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N115" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="O115" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S115" s="9">
+      <c r="M117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N117" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O117" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="P117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S117" s="9">
         <v>185.5</v>
       </c>
     </row>
-    <row r="116" ht="23" customHeight="1">
-      <c r="A116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B116" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D116" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F116" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G116" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R116" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S116" s="13">
-        <f>SUM(S6:S115)</f>
+    <row r="118" ht="23" customHeight="1">
+      <c r="A118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R118" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S118" s="13">
+        <f>SUM(S6:S117)</f>
       </c>
     </row>
   </sheetData>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 11 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em terça-feira, 12 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -199,226 +199,226 @@
     <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
   </si>
   <si>
+    <t>FA-11255</t>
+  </si>
+  <si>
+    <t>FA-11461</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11460</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11464</t>
+  </si>
+  <si>
+    <t>FA-11555</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11468</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11354</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11397</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11398</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11492</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11523</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11502</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11432</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
+    <t>FA-11327</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11267</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11599</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11575</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
     <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11255</t>
-  </si>
-  <si>
-    <t>FA-11461</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11460</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11464</t>
-  </si>
-  <si>
-    <t>FA-11555</t>
-  </si>
-  <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11354</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11397</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11398</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11492</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11523</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11502</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11432</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11327</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11267</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11599</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11575</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
   </si>
   <si>
     <t>A VENCER</t>
@@ -831,10 +831,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G6" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -890,10 +890,10 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G7" s="8">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>25</v>
@@ -949,10 +949,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G8" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -1008,10 +1008,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G9" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>25</v>
@@ -1067,10 +1067,10 @@
         <v>46127</v>
       </c>
       <c r="F10" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G10" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>25</v>
@@ -1126,10 +1126,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G11" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>25</v>
@@ -1185,10 +1185,10 @@
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G12" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>25</v>
@@ -1244,10 +1244,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G13" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>25</v>
@@ -1303,10 +1303,10 @@
         <v>46122</v>
       </c>
       <c r="F14" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G14" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>25</v>
@@ -1362,10 +1362,10 @@
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G15" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>25</v>
@@ -1421,10 +1421,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G16" s="8">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>25</v>
@@ -1480,10 +1480,10 @@
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G17" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>25</v>
@@ -1539,10 +1539,10 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G18" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>25</v>
@@ -1598,10 +1598,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G19" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>25</v>
@@ -1657,13 +1657,13 @@
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G20" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>25</v>
@@ -1681,7 +1681,7 @@
         <v>54</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>28</v>
@@ -1716,10 +1716,10 @@
         <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G21" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>25</v>
@@ -1728,7 +1728,7 @@
         <v>25</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
@@ -1775,10 +1775,10 @@
         <v>46097</v>
       </c>
       <c r="F22" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G22" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>25</v>
@@ -1834,10 +1834,10 @@
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G23" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>25</v>
@@ -1846,13 +1846,13 @@
         <v>25</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1893,10 +1893,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G24" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>25</v>
@@ -1905,16 +1905,16 @@
         <v>25</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>28</v>
@@ -1952,10 +1952,10 @@
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G25" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>25</v>
@@ -1964,13 +1964,13 @@
         <v>25</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -2011,10 +2011,10 @@
         <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G26" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>25</v>
@@ -2023,7 +2023,7 @@
         <v>25</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
@@ -2070,25 +2070,25 @@
         <v>23</v>
       </c>
       <c r="F27" s="8">
-        <v>-215</v>
+        <v>-216</v>
       </c>
       <c r="G27" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H27" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="6" t="s">
+      <c r="K27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2129,10 +2129,10 @@
         <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G28" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>25</v>
@@ -2141,7 +2141,7 @@
         <v>25</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
@@ -2188,10 +2188,10 @@
         <v>46141</v>
       </c>
       <c r="F29" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G29" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>25</v>
@@ -2200,7 +2200,7 @@
         <v>25</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
@@ -2247,10 +2247,10 @@
         <v>46141</v>
       </c>
       <c r="F30" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G30" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>25</v>
@@ -2259,13 +2259,13 @@
         <v>25</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2306,10 +2306,10 @@
         <v>46112</v>
       </c>
       <c r="F31" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G31" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>25</v>
@@ -2318,7 +2318,7 @@
         <v>25</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
@@ -2365,10 +2365,10 @@
         <v>46119</v>
       </c>
       <c r="F32" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G32" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>25</v>
@@ -2377,16 +2377,16 @@
         <v>25</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>28</v>
@@ -2424,10 +2424,10 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G33" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>25</v>
@@ -2436,13 +2436,13 @@
         <v>25</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2483,10 +2483,10 @@
         <v>46119</v>
       </c>
       <c r="F34" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G34" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>25</v>
@@ -2495,13 +2495,13 @@
         <v>25</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2542,10 +2542,10 @@
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G35" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>25</v>
@@ -2554,13 +2554,13 @@
         <v>25</v>
       </c>
       <c r="J35" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2601,11 +2601,11 @@
         <v>23</v>
       </c>
       <c r="F36" s="8">
+        <v>-8</v>
+      </c>
+      <c r="G36" s="8">
         <v>-7</v>
       </c>
-      <c r="G36" s="8">
-        <v>-6</v>
-      </c>
       <c r="H36" s="6" t="s">
         <v>25</v>
       </c>
@@ -2613,13 +2613,13 @@
         <v>25</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2660,10 +2660,10 @@
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G37" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>25</v>
@@ -2672,13 +2672,13 @@
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2719,10 +2719,10 @@
         <v>46148</v>
       </c>
       <c r="F38" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G38" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>25</v>
@@ -2731,31 +2731,31 @@
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="6" t="s">
+      <c r="M38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R38" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R38" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="S38" s="9">
         <v>685.71</v>
@@ -2778,10 +2778,10 @@
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>25</v>
@@ -2790,13 +2790,13 @@
         <v>25</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2837,10 +2837,10 @@
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>25</v>
@@ -2849,13 +2849,13 @@
         <v>25</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2896,10 +2896,10 @@
         <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>25</v>
@@ -2908,7 +2908,7 @@
         <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
@@ -2955,10 +2955,10 @@
         <v>46153</v>
       </c>
       <c r="F42" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G42" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -2967,13 +2967,13 @@
         <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -3014,16 +3014,16 @@
         <v>46097</v>
       </c>
       <c r="F43" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G43" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>31</v>
@@ -3038,10 +3038,10 @@
         <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>23</v>
@@ -3073,34 +3073,34 @@
         <v>46112</v>
       </c>
       <c r="F44" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G44" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="M44" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
@@ -3132,19 +3132,19 @@
         <v>46119</v>
       </c>
       <c r="F45" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G45" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
@@ -3156,10 +3156,10 @@
         <v>52</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
@@ -3191,34 +3191,34 @@
         <v>46127</v>
       </c>
       <c r="F46" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G46" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="K46" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="M46" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
@@ -3250,34 +3250,34 @@
         <v>46141</v>
       </c>
       <c r="F47" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G47" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
@@ -3309,19 +3309,19 @@
         <v>46141</v>
       </c>
       <c r="F48" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G48" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
@@ -3333,10 +3333,10 @@
         <v>43</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
@@ -3368,34 +3368,34 @@
         <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G49" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J49" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="K49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="M49" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
@@ -3427,34 +3427,34 @@
         <v>46112</v>
       </c>
       <c r="F50" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G50" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J50" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>100</v>
-      </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
@@ -3486,19 +3486,19 @@
         <v>46112</v>
       </c>
       <c r="F51" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G51" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
@@ -3510,10 +3510,10 @@
         <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
@@ -3545,34 +3545,34 @@
         <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G52" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>29</v>
@@ -3604,34 +3604,34 @@
         <v>46127</v>
       </c>
       <c r="F53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J53" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>105</v>
-      </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
@@ -3663,34 +3663,34 @@
         <v>46150</v>
       </c>
       <c r="F54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3722,34 +3722,34 @@
         <v>46127</v>
       </c>
       <c r="F55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
@@ -3781,34 +3781,34 @@
         <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3840,34 +3840,34 @@
         <v>46092</v>
       </c>
       <c r="F57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J57" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="K57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3899,34 +3899,34 @@
         <v>46119</v>
       </c>
       <c r="F58" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G58" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J58" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -3958,34 +3958,34 @@
         <v>46119</v>
       </c>
       <c r="F59" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G59" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="K59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -4017,19 +4017,19 @@
         <v>46119</v>
       </c>
       <c r="F60" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G60" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
@@ -4041,10 +4041,10 @@
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4076,34 +4076,34 @@
         <v>46141</v>
       </c>
       <c r="F61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4135,34 +4135,34 @@
         <v>46119</v>
       </c>
       <c r="F62" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>29</v>
@@ -4194,34 +4194,34 @@
         <v>46099</v>
       </c>
       <c r="F63" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G63" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J63" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="K63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4253,34 +4253,34 @@
         <v>46092</v>
       </c>
       <c r="F64" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G64" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4312,34 +4312,34 @@
         <v>46148</v>
       </c>
       <c r="F65" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G65" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J65" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4371,26 +4371,26 @@
         <v>46148</v>
       </c>
       <c r="F66" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G66" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J66" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>28</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4407,7 +4407,7 @@
         <v>39</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S66" s="9">
         <v>1028.57</v>
@@ -4430,10 +4430,10 @@
         <v>23</v>
       </c>
       <c r="F67" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>25</v>
@@ -4442,22 +4442,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O67" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L67" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M67" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="N67" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O67" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4489,10 +4489,10 @@
         <v>46097</v>
       </c>
       <c r="F68" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G68" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4548,10 +4548,10 @@
         <v>46112</v>
       </c>
       <c r="F69" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G69" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4566,10 +4566,10 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N69" s="6" t="s">
         <v>129</v>
@@ -4607,10 +4607,10 @@
         <v>46119</v>
       </c>
       <c r="F70" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G70" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4666,10 +4666,10 @@
         <v>46127</v>
       </c>
       <c r="F71" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G71" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4684,10 +4684,10 @@
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N71" s="6" t="s">
         <v>129</v>
@@ -4725,10 +4725,10 @@
         <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G72" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4743,10 +4743,10 @@
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N72" s="6" t="s">
         <v>129</v>
@@ -4784,10 +4784,10 @@
         <v>46141</v>
       </c>
       <c r="F73" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G73" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4802,7 +4802,7 @@
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
@@ -4843,10 +4843,10 @@
         <v>46141</v>
       </c>
       <c r="F74" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G74" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4902,10 +4902,10 @@
         <v>46119</v>
       </c>
       <c r="F75" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G75" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4920,7 +4920,7 @@
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
@@ -4961,10 +4961,10 @@
         <v>46127</v>
       </c>
       <c r="F76" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G76" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4979,7 +4979,7 @@
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
@@ -5020,10 +5020,10 @@
         <v>46112</v>
       </c>
       <c r="F77" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G77" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5038,7 +5038,7 @@
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
@@ -5079,10 +5079,10 @@
         <v>46112</v>
       </c>
       <c r="F78" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G78" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5138,10 +5138,10 @@
         <v>46150</v>
       </c>
       <c r="F79" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G79" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5156,7 +5156,7 @@
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
@@ -5197,10 +5197,10 @@
         <v>46153</v>
       </c>
       <c r="F80" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G80" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5215,7 +5215,7 @@
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
@@ -5256,10 +5256,10 @@
         <v>46092</v>
       </c>
       <c r="F81" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G81" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5274,7 +5274,7 @@
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
@@ -5315,10 +5315,10 @@
         <v>46127</v>
       </c>
       <c r="F82" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G82" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5333,7 +5333,7 @@
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
@@ -5374,10 +5374,10 @@
         <v>46119</v>
       </c>
       <c r="F83" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G83" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5392,10 +5392,10 @@
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N83" s="6" t="s">
         <v>129</v>
@@ -5433,10 +5433,10 @@
         <v>46119</v>
       </c>
       <c r="F84" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G84" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5451,7 +5451,7 @@
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
@@ -5492,10 +5492,10 @@
         <v>46113</v>
       </c>
       <c r="F85" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G85" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5551,10 +5551,10 @@
         <v>46119</v>
       </c>
       <c r="F86" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G86" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5569,7 +5569,7 @@
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
@@ -5610,10 +5610,10 @@
         <v>46119</v>
       </c>
       <c r="F87" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G87" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5669,10 +5669,10 @@
         <v>46141</v>
       </c>
       <c r="F88" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G88" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5687,7 +5687,7 @@
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
@@ -5728,10 +5728,10 @@
         <v>46092</v>
       </c>
       <c r="F89" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G89" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5746,7 +5746,7 @@
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
@@ -5787,10 +5787,10 @@
         <v>46099</v>
       </c>
       <c r="F90" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G90" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5805,7 +5805,7 @@
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
@@ -5846,10 +5846,10 @@
         <v>46119</v>
       </c>
       <c r="F91" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G91" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5864,7 +5864,7 @@
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
@@ -5905,10 +5905,10 @@
         <v>46148</v>
       </c>
       <c r="F92" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G92" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5923,7 +5923,7 @@
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
@@ -5964,10 +5964,10 @@
         <v>46148</v>
       </c>
       <c r="F93" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G93" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -5982,25 +5982,25 @@
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R93" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R93" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="S93" s="9">
         <v>1200</v>
@@ -6023,10 +6023,10 @@
         <v>46148</v>
       </c>
       <c r="F94" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G94" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6041,7 +6041,7 @@
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>23</v>
@@ -6059,7 +6059,7 @@
         <v>39</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S94" s="9">
         <v>1200</v>
@@ -6082,10 +6082,10 @@
         <v>46149</v>
       </c>
       <c r="F95" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G95" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>25</v>
@@ -6141,10 +6141,10 @@
         <v>46097</v>
       </c>
       <c r="F96" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G96" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6200,10 +6200,10 @@
         <v>46119</v>
       </c>
       <c r="F97" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G97" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6259,10 +6259,10 @@
         <v>46141</v>
       </c>
       <c r="F98" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G98" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6277,7 +6277,7 @@
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>23</v>
@@ -6318,10 +6318,10 @@
         <v>46141</v>
       </c>
       <c r="F99" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G99" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6377,10 +6377,10 @@
         <v>46119</v>
       </c>
       <c r="F100" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G100" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>23</v>
@@ -6395,10 +6395,10 @@
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N100" s="6" t="s">
         <v>129</v>
@@ -6436,10 +6436,10 @@
         <v>46119</v>
       </c>
       <c r="F101" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G101" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6454,7 +6454,7 @@
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
@@ -6495,10 +6495,10 @@
         <v>46150</v>
       </c>
       <c r="F102" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G102" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>23</v>
@@ -6513,7 +6513,7 @@
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M102" s="6" t="s">
         <v>23</v>
@@ -6554,10 +6554,10 @@
         <v>46153</v>
       </c>
       <c r="F103" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G103" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6572,7 +6572,7 @@
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
@@ -6613,10 +6613,10 @@
         <v>46119</v>
       </c>
       <c r="F104" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G104" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6631,10 +6631,10 @@
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N104" s="6" t="s">
         <v>129</v>
@@ -6672,10 +6672,10 @@
         <v>46127</v>
       </c>
       <c r="F105" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G105" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6690,7 +6690,7 @@
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
@@ -6731,10 +6731,10 @@
         <v>46092</v>
       </c>
       <c r="F106" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G106" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6749,7 +6749,7 @@
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>23</v>
@@ -6790,10 +6790,10 @@
         <v>46119</v>
       </c>
       <c r="F107" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G107" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6808,7 +6808,7 @@
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
@@ -6849,10 +6849,10 @@
         <v>46113</v>
       </c>
       <c r="F108" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G108" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6908,10 +6908,10 @@
         <v>46119</v>
       </c>
       <c r="F109" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G109" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6926,7 +6926,7 @@
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
@@ -6967,10 +6967,10 @@
         <v>46119</v>
       </c>
       <c r="F110" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G110" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -7026,10 +7026,10 @@
         <v>46141</v>
       </c>
       <c r="F111" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G111" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7044,7 +7044,7 @@
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>23</v>
@@ -7085,10 +7085,10 @@
         <v>46099</v>
       </c>
       <c r="F112" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G112" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7103,7 +7103,7 @@
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
@@ -7144,10 +7144,10 @@
         <v>46148</v>
       </c>
       <c r="F113" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G113" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7162,7 +7162,7 @@
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
@@ -7203,10 +7203,10 @@
         <v>46148</v>
       </c>
       <c r="F114" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G114" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>23</v>
@@ -7221,25 +7221,25 @@
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q114" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R114" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q114" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="S114" s="9">
         <v>1200</v>
@@ -7262,10 +7262,10 @@
         <v>46148</v>
       </c>
       <c r="F115" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G115" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>23</v>
@@ -7280,7 +7280,7 @@
         <v>23</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>23</v>
@@ -7298,7 +7298,7 @@
         <v>39</v>
       </c>
       <c r="R115" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S115" s="9">
         <v>1200</v>
@@ -7321,10 +7321,10 @@
         <v>46149</v>
       </c>
       <c r="F116" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G116" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>25</v>
@@ -7380,10 +7380,10 @@
         <v>23</v>
       </c>
       <c r="F117" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G117" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>23</v>

--- a/docx_templates/CONTAS-A-RECEBER.xlsx
+++ b/docx_templates/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$73</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,7 +36,7 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 31/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 25/07/2025, Data Final: 18/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
@@ -262,256 +262,187 @@
     <t>RICARDO ARAUJO DE MIRANDA</t>
   </si>
   <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
+  </si>
+  <si>
+    <t>FA-11522</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11556</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11278</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11475</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11558</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11472</t>
+  </si>
+  <si>
     <t>FA-11496</t>
   </si>
   <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11523</t>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11400</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11526</t>
   </si>
   <si>
     <t>JONILSON JOSEMAR DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11267</t>
+    <t>FA-11493</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11401</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FA-11503</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11433</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11411</t>
+  </si>
+  <si>
+    <t>FA-11268</t>
   </si>
   <si>
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11433</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
+    <t>FA-11328</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
   </si>
   <si>
     <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11268</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11563</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>FA-11494</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>FA-11621</t>
-  </si>
-  <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FA-11434</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>FA-11329</t>
-  </si>
-  <si>
-    <t>FA-11613</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
   </si>
 </sst>
 </file>
@@ -654,7 +585,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S101"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -2473,22 +2404,22 @@
         <v>46150</v>
       </c>
       <c r="C35" s="7">
-        <v>46125</v>
+        <v>46150</v>
       </c>
       <c r="D35" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46153</v>
       </c>
       <c r="F35" s="8">
-        <v>-31</v>
+        <v>-6</v>
       </c>
       <c r="G35" s="8">
         <v>-6</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>25</v>
@@ -2515,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S35" s="9">
-        <v>250</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2529,37 +2460,37 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C36" s="7">
-        <v>46150</v>
+        <v>45901</v>
       </c>
       <c r="D36" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46153</v>
+        <v>45938</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-6</v>
+        <v>-218</v>
       </c>
       <c r="G36" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2574,13 +2505,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S36" s="9">
-        <v>278.57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2591,34 +2522,34 @@
         <v>46153</v>
       </c>
       <c r="C37" s="7">
-        <v>45901</v>
+        <v>46082</v>
       </c>
       <c r="D37" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46097</v>
       </c>
       <c r="F37" s="8">
-        <v>-218</v>
+        <v>-3</v>
       </c>
       <c r="G37" s="8">
         <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2633,13 +2564,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S37" s="9">
-        <v>30</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2650,16 +2581,16 @@
         <v>46153</v>
       </c>
       <c r="C38" s="7">
-        <v>46082</v>
+        <v>46139</v>
       </c>
       <c r="D38" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46097</v>
+        <v>46132</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-3</v>
+        <v>-24</v>
       </c>
       <c r="G38" s="8">
         <v>-3</v>
@@ -2671,13 +2602,13 @@
         <v>25</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2692,13 +2623,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S38" s="9">
-        <v>146.55</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2709,16 +2640,16 @@
         <v>46153</v>
       </c>
       <c r="C39" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="D39" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46119</v>
       </c>
       <c r="F39" s="8">
-        <v>-24</v>
+        <v>-3</v>
       </c>
       <c r="G39" s="8">
         <v>-3</v>
@@ -2736,10 +2667,10 @@
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>28</v>
@@ -2751,13 +2682,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S39" s="9">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2774,7 +2705,7 @@
         <v>46153</v>
       </c>
       <c r="E40" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F40" s="8">
         <v>-3</v>
@@ -2795,10 +2726,10 @@
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>28</v>
@@ -2833,7 +2764,7 @@
         <v>46153</v>
       </c>
       <c r="E41" s="7">
-        <v>46127</v>
+        <v>46119</v>
       </c>
       <c r="F41" s="8">
         <v>-3</v>
@@ -2848,16 +2779,16 @@
         <v>25</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>28</v>
@@ -2872,10 +2803,10 @@
         <v>39</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S41" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2907,7 +2838,7 @@
         <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
@@ -2966,16 +2897,16 @@
         <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>28</v>
@@ -3010,7 +2941,7 @@
         <v>46153</v>
       </c>
       <c r="E44" s="7">
-        <v>46119</v>
+        <v>46150</v>
       </c>
       <c r="F44" s="8">
         <v>-3</v>
@@ -3025,16 +2956,16 @@
         <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>28</v>
@@ -3049,10 +2980,10 @@
         <v>39</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S44" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3069,7 +3000,7 @@
         <v>46153</v>
       </c>
       <c r="E45" s="7">
-        <v>46127</v>
+        <v>46112</v>
       </c>
       <c r="F45" s="8">
         <v>-3</v>
@@ -3084,13 +3015,13 @@
         <v>25</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3128,7 +3059,7 @@
         <v>46153</v>
       </c>
       <c r="E46" s="7">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="F46" s="8">
         <v>-3</v>
@@ -3149,7 +3080,7 @@
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3170,7 +3101,7 @@
         <v>30</v>
       </c>
       <c r="S46" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3187,7 +3118,7 @@
         <v>46153</v>
       </c>
       <c r="E47" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F47" s="8">
         <v>-3</v>
@@ -3202,16 +3133,16 @@
         <v>25</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>28</v>
@@ -3229,7 +3160,7 @@
         <v>30</v>
       </c>
       <c r="S47" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3246,7 +3177,7 @@
         <v>46153</v>
       </c>
       <c r="E48" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F48" s="8">
         <v>-3</v>
@@ -3288,7 +3219,7 @@
         <v>30</v>
       </c>
       <c r="S48" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3326,10 +3257,10 @@
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>28</v>
@@ -3344,10 +3275,10 @@
         <v>39</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S49" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3364,7 +3295,7 @@
         <v>46153</v>
       </c>
       <c r="E50" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F50" s="8">
         <v>-3</v>
@@ -3403,7 +3334,7 @@
         <v>39</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S50" s="9">
         <v>680</v>
@@ -3444,7 +3375,7 @@
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3456,16 +3387,16 @@
         <v>28</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q51" s="6" t="s">
         <v>39</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S51" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3473,25 +3404,25 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C52" s="7">
-        <v>46153</v>
+        <v>46125</v>
       </c>
       <c r="D52" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E52" s="7">
-        <v>46141</v>
+        <v>46125</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-3</v>
+        <v>-31</v>
       </c>
       <c r="G52" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>25</v>
@@ -3503,7 +3434,7 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3518,13 +3449,13 @@
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S52" s="9">
-        <v>680</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3532,22 +3463,22 @@
         <v>22</v>
       </c>
       <c r="B53" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C53" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D53" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E53" s="7">
-        <v>46092</v>
+        <v>46146</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G53" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3556,13 +3487,13 @@
         <v>25</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3577,13 +3508,13 @@
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S53" s="9">
-        <v>700</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3591,22 +3522,22 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C54" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D54" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>-3</v>
+        <v>-24</v>
       </c>
       <c r="G54" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
@@ -3615,16 +3546,16 @@
         <v>25</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>28</v>
@@ -3633,16 +3564,16 @@
         <v>28</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S54" s="9">
-        <v>700</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3650,58 +3581,58 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C55" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D55" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46097</v>
       </c>
       <c r="F55" s="8">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="G55" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S55" s="9">
-        <v>280</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3709,58 +3640,58 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C56" s="7">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="D56" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>-24</v>
+        <v>4</v>
       </c>
       <c r="G56" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>30</v>
       </c>
       <c r="S56" s="9">
-        <v>317.54</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3771,13 +3702,13 @@
         <v>46160</v>
       </c>
       <c r="C57" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D57" s="7">
         <v>46160</v>
       </c>
       <c r="E57" s="7">
-        <v>46097</v>
+        <v>46112</v>
       </c>
       <c r="F57" s="8">
         <v>4</v>
@@ -3792,34 +3723,34 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S57" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3836,7 +3767,7 @@
         <v>46160</v>
       </c>
       <c r="E58" s="7">
-        <v>46112</v>
+        <v>46127</v>
       </c>
       <c r="F58" s="8">
         <v>4</v>
@@ -3851,22 +3782,22 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -3910,22 +3841,22 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -3934,10 +3865,10 @@
         <v>39</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S59" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3954,7 +3885,7 @@
         <v>46160</v>
       </c>
       <c r="E60" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F60" s="8">
         <v>4</v>
@@ -3969,22 +3900,22 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -3996,7 +3927,7 @@
         <v>30</v>
       </c>
       <c r="S60" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -4028,22 +3959,22 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4072,7 +4003,7 @@
         <v>46160</v>
       </c>
       <c r="E62" s="7">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="F62" s="8">
         <v>4</v>
@@ -4087,22 +4018,22 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4114,7 +4045,7 @@
         <v>30</v>
       </c>
       <c r="S62" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4131,7 +4062,7 @@
         <v>46160</v>
       </c>
       <c r="E63" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F63" s="8">
         <v>4</v>
@@ -4146,22 +4077,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4170,10 +4101,10 @@
         <v>39</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S63" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4190,7 +4121,7 @@
         <v>46160</v>
       </c>
       <c r="E64" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F64" s="8">
         <v>4</v>
@@ -4205,25 +4136,25 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q64" s="6" t="s">
         <v>39</v>
@@ -4264,22 +4195,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4308,7 +4239,7 @@
         <v>46160</v>
       </c>
       <c r="E66" s="7">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="F66" s="8">
         <v>4</v>
@@ -4329,19 +4260,19 @@
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>39</v>
@@ -4367,7 +4298,7 @@
         <v>46160</v>
       </c>
       <c r="E67" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F67" s="8">
         <v>4</v>
@@ -4382,22 +4313,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4409,7 +4340,7 @@
         <v>30</v>
       </c>
       <c r="S67" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4426,7 +4357,7 @@
         <v>46160</v>
       </c>
       <c r="E68" s="7">
-        <v>46150</v>
+        <v>46127</v>
       </c>
       <c r="F68" s="8">
         <v>4</v>
@@ -4441,22 +4372,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K68" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L68" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4468,7 +4399,7 @@
         <v>30</v>
       </c>
       <c r="S68" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4485,7 +4416,7 @@
         <v>46160</v>
       </c>
       <c r="E69" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F69" s="8">
         <v>4</v>
@@ -4506,16 +4437,16 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4544,7 +4475,7 @@
         <v>46160</v>
       </c>
       <c r="E70" s="7">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="F70" s="8">
         <v>4</v>
@@ -4565,16 +4496,16 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4603,7 +4534,7 @@
         <v>46160</v>
       </c>
       <c r="E71" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F71" s="8">
         <v>4</v>
@@ -4618,22 +4549,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K71" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L71" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4645,7 +4576,7 @@
         <v>30</v>
       </c>
       <c r="S71" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="72" ht="23" customHeight="1">
@@ -4662,7 +4593,7 @@
         <v>46160</v>
       </c>
       <c r="E72" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F72" s="8">
         <v>4</v>
@@ -4683,16 +4614,16 @@
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4701,10 +4632,10 @@
         <v>39</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S72" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4742,16 +4673,16 @@
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4763,7 +4694,7 @@
         <v>30</v>
       </c>
       <c r="S73" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4795,22 +4726,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4819,7 +4750,7 @@
         <v>39</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S74" s="9">
         <v>680</v>
@@ -4839,7 +4770,7 @@
         <v>46160</v>
       </c>
       <c r="E75" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F75" s="8">
         <v>4</v>
@@ -4854,22 +4785,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4878,7 +4809,7 @@
         <v>39</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="S75" s="9">
         <v>680</v>
@@ -4898,7 +4829,7 @@
         <v>46160</v>
       </c>
       <c r="E76" s="7">
-        <v>46113</v>
+        <v>46092</v>
       </c>
       <c r="F76" s="8">
         <v>4</v>
@@ -4913,22 +4844,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="K76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="M76" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4940,7 +4871,7 @@
         <v>30</v>
       </c>
       <c r="S76" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="77" ht="23" customHeight="1">
@@ -4957,7 +4888,7 @@
         <v>46160</v>
       </c>
       <c r="E77" s="7">
-        <v>46141</v>
+        <v>46099</v>
       </c>
       <c r="F77" s="8">
         <v>4</v>
@@ -4978,16 +4909,16 @@
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -4999,7 +4930,7 @@
         <v>33</v>
       </c>
       <c r="S77" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="78" ht="23" customHeight="1">
@@ -5031,7 +4962,7 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
@@ -5043,10 +4974,10 @@
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>29</v>
@@ -5062,1360 +4993,62 @@
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
-      <c r="A79" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C79" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D79" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E79" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F79" s="8">
-        <v>4</v>
-      </c>
-      <c r="G79" s="8">
-        <v>4</v>
-      </c>
-      <c r="H79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J79" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="K79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="M79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N79" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O79" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q79" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R79" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S79" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="80" ht="23" customHeight="1">
-      <c r="A80" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C80" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D80" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E80" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F80" s="8">
-        <v>4</v>
-      </c>
-      <c r="G80" s="8">
-        <v>4</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J80" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R80" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S80" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="81" ht="23" customHeight="1">
-      <c r="A81" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="7">
-        <v>46161</v>
-      </c>
-      <c r="C81" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D81" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E81" s="7">
-        <v>46149</v>
-      </c>
-      <c r="F81" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G81" s="8">
-        <v>5</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J81" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K81" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L81" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="M81" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="N81" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O81" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P81" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q81" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R81" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S81" s="9">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="82" ht="23" customHeight="1">
-      <c r="A82" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B82" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C82" s="7">
-        <v>46082</v>
-      </c>
-      <c r="D82" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E82" s="7">
-        <v>46097</v>
-      </c>
-      <c r="F82" s="8">
-        <v>11</v>
-      </c>
-      <c r="G82" s="8">
-        <v>11</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L82" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q82" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="R82" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S82" s="9">
-        <v>146.55</v>
-      </c>
-    </row>
-    <row r="83" ht="23" customHeight="1">
-      <c r="A83" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C83" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D83" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E83" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F83" s="8">
-        <v>11</v>
-      </c>
-      <c r="G83" s="8">
-        <v>11</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J83" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M83" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N83" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O83" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P83" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q83" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R83" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S83" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C84" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D84" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F84" s="8">
-        <v>11</v>
-      </c>
-      <c r="G84" s="8">
-        <v>11</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q84" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R84" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S84" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="85" ht="23" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C85" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D85" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F85" s="8">
-        <v>11</v>
-      </c>
-      <c r="G85" s="8">
-        <v>11</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M85" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="N85" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q85" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R85" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S85" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="86" ht="23" customHeight="1">
-      <c r="A86" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B86" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C86" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D86" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F86" s="8">
-        <v>11</v>
-      </c>
-      <c r="G86" s="8">
-        <v>11</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q86" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R86" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S86" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="87" ht="23" customHeight="1">
-      <c r="A87" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F87" s="8">
-        <v>11</v>
-      </c>
-      <c r="G87" s="8">
-        <v>11</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q87" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S87" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="88" ht="23" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E88" s="7">
-        <v>46150</v>
-      </c>
-      <c r="F88" s="8">
-        <v>11</v>
-      </c>
-      <c r="G88" s="8">
-        <v>11</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q88" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="89" ht="23" customHeight="1">
-      <c r="A89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E89" s="7">
-        <v>46153</v>
-      </c>
-      <c r="F89" s="8">
-        <v>11</v>
-      </c>
-      <c r="G89" s="8">
-        <v>11</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q89" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R89" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S89" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="90" ht="23" customHeight="1">
-      <c r="A90" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F90" s="8">
-        <v>11</v>
-      </c>
-      <c r="G90" s="8">
-        <v>11</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R90" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S90" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="91" ht="23" customHeight="1">
-      <c r="A91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E91" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F91" s="8">
-        <v>11</v>
-      </c>
-      <c r="G91" s="8">
-        <v>11</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S91" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="92" ht="23" customHeight="1">
-      <c r="A92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E92" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F92" s="8">
-        <v>11</v>
-      </c>
-      <c r="G92" s="8">
-        <v>11</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R92" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S92" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="93" ht="23" customHeight="1">
-      <c r="A93" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E93" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F93" s="8">
-        <v>11</v>
-      </c>
-      <c r="G93" s="8">
-        <v>11</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R93" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S93" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="94" ht="23" customHeight="1">
-      <c r="A94" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E94" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F94" s="8">
-        <v>11</v>
-      </c>
-      <c r="G94" s="8">
-        <v>11</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R94" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S94" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="95" ht="23" customHeight="1">
-      <c r="A95" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E95" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F95" s="8">
-        <v>11</v>
-      </c>
-      <c r="G95" s="8">
-        <v>11</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N95" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q95" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R95" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S95" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="96" ht="23" customHeight="1">
-      <c r="A96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E96" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F96" s="8">
-        <v>11</v>
-      </c>
-      <c r="G96" s="8">
-        <v>11</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q96" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R96" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S96" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="97" ht="23" customHeight="1">
-      <c r="A97" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E97" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F97" s="8">
-        <v>11</v>
-      </c>
-      <c r="G97" s="8">
-        <v>11</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q97" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R97" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S97" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="98" ht="23" customHeight="1">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E98" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F98" s="8">
-        <v>11</v>
-      </c>
-      <c r="G98" s="8">
-        <v>11</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R98" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S98" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="99" ht="23" customHeight="1">
-      <c r="A99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C99" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D99" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E99" s="7">
-        <v>46149</v>
-      </c>
-      <c r="F99" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G99" s="8">
-        <v>11</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q99" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="R99" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" s="9">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="100" ht="23" customHeight="1">
-      <c r="A100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="7">
-        <v>46172</v>
-      </c>
-      <c r="C100" s="7">
-        <v>45930</v>
-      </c>
-      <c r="D100" s="7">
-        <v>46172</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F100" s="8">
-        <v>16</v>
-      </c>
-      <c r="G100" s="8">
-        <v>16</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N100" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S100" s="9">
-        <v>185.5</v>
-      </c>
-    </row>
-    <row r="101" ht="23" customHeight="1">
-      <c r="A101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G101" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R101" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S101" s="13">
-        <f>SUM(S6:S100)</f>
+      <c r="A79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R79" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S79" s="13">
+        <f>SUM(S6:S78)</f>
       </c>
     </row>
   </sheetData>
